--- a/data/Enrollment_Tracker.xlsx
+++ b/data/Enrollment_Tracker.xlsx
@@ -1,16 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="30228"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="30326"/>
   <workbookPr defaultThemeVersion="202300"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://ahausa-my.sharepoint.com/personal/inicchitta_aha_org/Documents/Documents/Projects/Enrollment Tracking/project/data/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="83" documentId="13_ncr:1_{F42CCC4A-64CB-4D65-8DF8-D273176EBD5B}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{BB91D7FF-55DB-4C06-9584-7921D0551DB1}"/>
+  <xr:revisionPtr revIDLastSave="151" documentId="13_ncr:1_{F42CCC4A-64CB-4D65-8DF8-D273176EBD5B}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{0058E747-FF3B-4770-B6D4-5D7CBAAAB88A}"/>
   <bookViews>
-    <workbookView xWindow="57480" yWindow="-120" windowWidth="29040" windowHeight="15720" activeTab="1" xr2:uid="{ABF58F20-35C5-4B4F-8D44-F14F003A923B}"/>
+    <workbookView xWindow="28680" yWindow="-120" windowWidth="29040" windowHeight="15720" xr2:uid="{ABF58F20-35C5-4B4F-8D44-F14F003A923B}"/>
   </bookViews>
   <sheets>
     <sheet name="Mcaid" sheetId="1" r:id="rId1"/>
@@ -48,7 +48,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="3023" uniqueCount="157">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="3132" uniqueCount="157">
   <si>
     <t>Alaska</t>
   </si>
@@ -936,7 +936,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{FB264A2A-D604-4430-8789-DEB8BBE451DA}">
-  <dimension ref="A1:P313"/>
+  <dimension ref="A1:P365"/>
   <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
   <cols>
     <col min="1" max="1" width="18.6640625" bestFit="1" customWidth="1"/>
@@ -1007,7 +1007,7 @@
         <v>59</v>
       </c>
     </row>
-    <row r="2" spans="1:16" hidden="1" x14ac:dyDescent="0.3">
+    <row r="2" spans="1:16" x14ac:dyDescent="0.3">
       <c r="A2" t="s">
         <v>0</v>
       </c>
@@ -1060,7 +1060,7 @@
         <v>5658</v>
       </c>
     </row>
-    <row r="3" spans="1:16" hidden="1" x14ac:dyDescent="0.3">
+    <row r="3" spans="1:16" x14ac:dyDescent="0.3">
       <c r="A3" t="s">
         <v>1</v>
       </c>
@@ -1113,7 +1113,7 @@
         <v>2017</v>
       </c>
     </row>
-    <row r="4" spans="1:16" hidden="1" x14ac:dyDescent="0.3">
+    <row r="4" spans="1:16" x14ac:dyDescent="0.3">
       <c r="A4" t="s">
         <v>2</v>
       </c>
@@ -1166,7 +1166,7 @@
         <v>85</v>
       </c>
     </row>
-    <row r="5" spans="1:16" hidden="1" x14ac:dyDescent="0.3">
+    <row r="5" spans="1:16" x14ac:dyDescent="0.3">
       <c r="A5" t="s">
         <v>3</v>
       </c>
@@ -1219,7 +1219,7 @@
         <v>9159</v>
       </c>
     </row>
-    <row r="6" spans="1:16" hidden="1" x14ac:dyDescent="0.3">
+    <row r="6" spans="1:16" x14ac:dyDescent="0.3">
       <c r="A6" t="s">
         <v>4</v>
       </c>
@@ -1272,7 +1272,7 @@
         <v>210603</v>
       </c>
     </row>
-    <row r="7" spans="1:16" hidden="1" x14ac:dyDescent="0.3">
+    <row r="7" spans="1:16" x14ac:dyDescent="0.3">
       <c r="A7" t="s">
         <v>5</v>
       </c>
@@ -1325,7 +1325,7 @@
         <v>3046</v>
       </c>
     </row>
-    <row r="8" spans="1:16" hidden="1" x14ac:dyDescent="0.3">
+    <row r="8" spans="1:16" x14ac:dyDescent="0.3">
       <c r="A8" t="s">
         <v>6</v>
       </c>
@@ -1378,7 +1378,7 @@
         <v>4185</v>
       </c>
     </row>
-    <row r="9" spans="1:16" hidden="1" x14ac:dyDescent="0.3">
+    <row r="9" spans="1:16" x14ac:dyDescent="0.3">
       <c r="A9" t="s">
         <v>7</v>
       </c>
@@ -1431,7 +1431,7 @@
         <v>1069</v>
       </c>
     </row>
-    <row r="10" spans="1:16" hidden="1" x14ac:dyDescent="0.3">
+    <row r="10" spans="1:16" x14ac:dyDescent="0.3">
       <c r="A10" t="s">
         <v>8</v>
       </c>
@@ -1484,7 +1484,7 @@
         <v>321</v>
       </c>
     </row>
-    <row r="11" spans="1:16" hidden="1" x14ac:dyDescent="0.3">
+    <row r="11" spans="1:16" x14ac:dyDescent="0.3">
       <c r="A11" t="s">
         <v>9</v>
       </c>
@@ -1537,7 +1537,7 @@
         <v>24416</v>
       </c>
     </row>
-    <row r="12" spans="1:16" hidden="1" x14ac:dyDescent="0.3">
+    <row r="12" spans="1:16" x14ac:dyDescent="0.3">
       <c r="A12" t="s">
         <v>10</v>
       </c>
@@ -1590,7 +1590,7 @@
         <v>15061</v>
       </c>
     </row>
-    <row r="13" spans="1:16" hidden="1" x14ac:dyDescent="0.3">
+    <row r="13" spans="1:16" x14ac:dyDescent="0.3">
       <c r="A13" t="s">
         <v>11</v>
       </c>
@@ -1643,7 +1643,7 @@
         <v>905</v>
       </c>
     </row>
-    <row r="14" spans="1:16" hidden="1" x14ac:dyDescent="0.3">
+    <row r="14" spans="1:16" x14ac:dyDescent="0.3">
       <c r="A14" t="s">
         <v>12</v>
       </c>
@@ -1696,7 +1696,7 @@
         <v>2938</v>
       </c>
     </row>
-    <row r="15" spans="1:16" hidden="1" x14ac:dyDescent="0.3">
+    <row r="15" spans="1:16" x14ac:dyDescent="0.3">
       <c r="A15" t="s">
         <v>13</v>
       </c>
@@ -1749,7 +1749,7 @@
         <v>525</v>
       </c>
     </row>
-    <row r="16" spans="1:16" hidden="1" x14ac:dyDescent="0.3">
+    <row r="16" spans="1:16" x14ac:dyDescent="0.3">
       <c r="A16" t="s">
         <v>14</v>
       </c>
@@ -1802,7 +1802,7 @@
         <v>22014</v>
       </c>
     </row>
-    <row r="17" spans="1:16" hidden="1" x14ac:dyDescent="0.3">
+    <row r="17" spans="1:16" x14ac:dyDescent="0.3">
       <c r="A17" t="s">
         <v>15</v>
       </c>
@@ -1855,7 +1855,7 @@
         <v>29920</v>
       </c>
     </row>
-    <row r="18" spans="1:16" hidden="1" x14ac:dyDescent="0.3">
+    <row r="18" spans="1:16" x14ac:dyDescent="0.3">
       <c r="A18" t="s">
         <v>16</v>
       </c>
@@ -1908,7 +1908,7 @@
         <v>1281</v>
       </c>
     </row>
-    <row r="19" spans="1:16" hidden="1" x14ac:dyDescent="0.3">
+    <row r="19" spans="1:16" x14ac:dyDescent="0.3">
       <c r="A19" t="s">
         <v>17</v>
       </c>
@@ -1961,7 +1961,7 @@
         <v>314</v>
       </c>
     </row>
-    <row r="20" spans="1:16" hidden="1" x14ac:dyDescent="0.3">
+    <row r="20" spans="1:16" x14ac:dyDescent="0.3">
       <c r="A20" t="s">
         <v>18</v>
       </c>
@@ -2014,7 +2014,7 @@
         <v>12224</v>
       </c>
     </row>
-    <row r="21" spans="1:16" hidden="1" x14ac:dyDescent="0.3">
+    <row r="21" spans="1:16" x14ac:dyDescent="0.3">
       <c r="A21" t="s">
         <v>19</v>
       </c>
@@ -2067,7 +2067,7 @@
         <v>6252</v>
       </c>
     </row>
-    <row r="22" spans="1:16" hidden="1" x14ac:dyDescent="0.3">
+    <row r="22" spans="1:16" x14ac:dyDescent="0.3">
       <c r="A22" t="s">
         <v>20</v>
       </c>
@@ -2120,7 +2120,7 @@
         <v>4445</v>
       </c>
     </row>
-    <row r="23" spans="1:16" hidden="1" x14ac:dyDescent="0.3">
+    <row r="23" spans="1:16" x14ac:dyDescent="0.3">
       <c r="A23" t="s">
         <v>21</v>
       </c>
@@ -2173,7 +2173,7 @@
         <v>3537</v>
       </c>
     </row>
-    <row r="24" spans="1:16" hidden="1" x14ac:dyDescent="0.3">
+    <row r="24" spans="1:16" x14ac:dyDescent="0.3">
       <c r="A24" t="s">
         <v>22</v>
       </c>
@@ -2226,7 +2226,7 @@
         <v>16428</v>
       </c>
     </row>
-    <row r="25" spans="1:16" hidden="1" x14ac:dyDescent="0.3">
+    <row r="25" spans="1:16" x14ac:dyDescent="0.3">
       <c r="A25" t="s">
         <v>23</v>
       </c>
@@ -2279,7 +2279,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="26" spans="1:16" hidden="1" x14ac:dyDescent="0.3">
+    <row r="26" spans="1:16" x14ac:dyDescent="0.3">
       <c r="A26" t="s">
         <v>24</v>
       </c>
@@ -2332,7 +2332,7 @@
         <v>19091</v>
       </c>
     </row>
-    <row r="27" spans="1:16" hidden="1" x14ac:dyDescent="0.3">
+    <row r="27" spans="1:16" x14ac:dyDescent="0.3">
       <c r="A27" t="s">
         <v>25</v>
       </c>
@@ -2385,7 +2385,7 @@
         <v>25</v>
       </c>
     </row>
-    <row r="28" spans="1:16" hidden="1" x14ac:dyDescent="0.3">
+    <row r="28" spans="1:16" x14ac:dyDescent="0.3">
       <c r="A28" t="s">
         <v>26</v>
       </c>
@@ -2438,7 +2438,7 @@
         <v>4394</v>
       </c>
     </row>
-    <row r="29" spans="1:16" hidden="1" x14ac:dyDescent="0.3">
+    <row r="29" spans="1:16" x14ac:dyDescent="0.3">
       <c r="A29" t="s">
         <v>27</v>
       </c>
@@ -2491,7 +2491,7 @@
         <v>79636</v>
       </c>
     </row>
-    <row r="30" spans="1:16" hidden="1" x14ac:dyDescent="0.3">
+    <row r="30" spans="1:16" x14ac:dyDescent="0.3">
       <c r="A30" t="s">
         <v>28</v>
       </c>
@@ -2544,7 +2544,7 @@
         <v>1420</v>
       </c>
     </row>
-    <row r="31" spans="1:16" hidden="1" x14ac:dyDescent="0.3">
+    <row r="31" spans="1:16" x14ac:dyDescent="0.3">
       <c r="A31" t="s">
         <v>29</v>
       </c>
@@ -2597,7 +2597,7 @@
         <v>2860</v>
       </c>
     </row>
-    <row r="32" spans="1:16" hidden="1" x14ac:dyDescent="0.3">
+    <row r="32" spans="1:16" x14ac:dyDescent="0.3">
       <c r="A32" t="s">
         <v>30</v>
       </c>
@@ -2650,7 +2650,7 @@
         <v>1409</v>
       </c>
     </row>
-    <row r="33" spans="1:16" hidden="1" x14ac:dyDescent="0.3">
+    <row r="33" spans="1:16" x14ac:dyDescent="0.3">
       <c r="A33" t="s">
         <v>31</v>
       </c>
@@ -2703,7 +2703,7 @@
         <v>56023</v>
       </c>
     </row>
-    <row r="34" spans="1:16" hidden="1" x14ac:dyDescent="0.3">
+    <row r="34" spans="1:16" x14ac:dyDescent="0.3">
       <c r="A34" t="s">
         <v>32</v>
       </c>
@@ -2756,7 +2756,7 @@
         <v>1128</v>
       </c>
     </row>
-    <row r="35" spans="1:16" hidden="1" x14ac:dyDescent="0.3">
+    <row r="35" spans="1:16" x14ac:dyDescent="0.3">
       <c r="A35" t="s">
         <v>33</v>
       </c>
@@ -2809,7 +2809,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="36" spans="1:16" hidden="1" x14ac:dyDescent="0.3">
+    <row r="36" spans="1:16" x14ac:dyDescent="0.3">
       <c r="A36" t="s">
         <v>34</v>
       </c>
@@ -2862,7 +2862,7 @@
         <v>6400</v>
       </c>
     </row>
-    <row r="37" spans="1:16" hidden="1" x14ac:dyDescent="0.3">
+    <row r="37" spans="1:16" x14ac:dyDescent="0.3">
       <c r="A37" t="s">
         <v>35</v>
       </c>
@@ -2915,7 +2915,7 @@
         <v>24531</v>
       </c>
     </row>
-    <row r="38" spans="1:16" hidden="1" x14ac:dyDescent="0.3">
+    <row r="38" spans="1:16" x14ac:dyDescent="0.3">
       <c r="A38" t="s">
         <v>36</v>
       </c>
@@ -2968,7 +2968,7 @@
         <v>7702</v>
       </c>
     </row>
-    <row r="39" spans="1:16" hidden="1" x14ac:dyDescent="0.3">
+    <row r="39" spans="1:16" x14ac:dyDescent="0.3">
       <c r="A39" t="s">
         <v>37</v>
       </c>
@@ -3021,7 +3021,7 @@
         <v>184</v>
       </c>
     </row>
-    <row r="40" spans="1:16" hidden="1" x14ac:dyDescent="0.3">
+    <row r="40" spans="1:16" x14ac:dyDescent="0.3">
       <c r="A40" t="s">
         <v>38</v>
       </c>
@@ -3074,7 +3074,7 @@
         <v>84839</v>
       </c>
     </row>
-    <row r="41" spans="1:16" hidden="1" x14ac:dyDescent="0.3">
+    <row r="41" spans="1:16" x14ac:dyDescent="0.3">
       <c r="A41" t="s">
         <v>39</v>
       </c>
@@ -3127,7 +3127,7 @@
         <v>113</v>
       </c>
     </row>
-    <row r="42" spans="1:16" hidden="1" x14ac:dyDescent="0.3">
+    <row r="42" spans="1:16" x14ac:dyDescent="0.3">
       <c r="A42" t="s">
         <v>40</v>
       </c>
@@ -3180,7 +3180,7 @@
         <v>1178</v>
       </c>
     </row>
-    <row r="43" spans="1:16" hidden="1" x14ac:dyDescent="0.3">
+    <row r="43" spans="1:16" x14ac:dyDescent="0.3">
       <c r="A43" t="s">
         <v>41</v>
       </c>
@@ -3233,7 +3233,7 @@
         <v>242</v>
       </c>
     </row>
-    <row r="44" spans="1:16" hidden="1" x14ac:dyDescent="0.3">
+    <row r="44" spans="1:16" x14ac:dyDescent="0.3">
       <c r="A44" t="s">
         <v>42</v>
       </c>
@@ -3286,7 +3286,7 @@
         <v>333</v>
       </c>
     </row>
-    <row r="45" spans="1:16" hidden="1" x14ac:dyDescent="0.3">
+    <row r="45" spans="1:16" x14ac:dyDescent="0.3">
       <c r="A45" t="s">
         <v>43</v>
       </c>
@@ -3339,7 +3339,7 @@
         <v>18046</v>
       </c>
     </row>
-    <row r="46" spans="1:16" hidden="1" x14ac:dyDescent="0.3">
+    <row r="46" spans="1:16" x14ac:dyDescent="0.3">
       <c r="A46" t="s">
         <v>44</v>
       </c>
@@ -3392,7 +3392,7 @@
         <v>5736</v>
       </c>
     </row>
-    <row r="47" spans="1:16" hidden="1" x14ac:dyDescent="0.3">
+    <row r="47" spans="1:16" x14ac:dyDescent="0.3">
       <c r="A47" t="s">
         <v>45</v>
       </c>
@@ -3445,7 +3445,7 @@
         <v>5383</v>
       </c>
     </row>
-    <row r="48" spans="1:16" hidden="1" x14ac:dyDescent="0.3">
+    <row r="48" spans="1:16" x14ac:dyDescent="0.3">
       <c r="A48" t="s">
         <v>46</v>
       </c>
@@ -3498,7 +3498,7 @@
         <v>804</v>
       </c>
     </row>
-    <row r="49" spans="1:16" hidden="1" x14ac:dyDescent="0.3">
+    <row r="49" spans="1:16" x14ac:dyDescent="0.3">
       <c r="A49" t="s">
         <v>47</v>
       </c>
@@ -3551,7 +3551,7 @@
         <v>3916</v>
       </c>
     </row>
-    <row r="50" spans="1:16" hidden="1" x14ac:dyDescent="0.3">
+    <row r="50" spans="1:16" x14ac:dyDescent="0.3">
       <c r="A50" t="s">
         <v>48</v>
       </c>
@@ -3604,7 +3604,7 @@
         <v>4573</v>
       </c>
     </row>
-    <row r="51" spans="1:16" hidden="1" x14ac:dyDescent="0.3">
+    <row r="51" spans="1:16" x14ac:dyDescent="0.3">
       <c r="A51" t="s">
         <v>49</v>
       </c>
@@ -3657,7 +3657,7 @@
         <v>234</v>
       </c>
     </row>
-    <row r="52" spans="1:16" hidden="1" x14ac:dyDescent="0.3">
+    <row r="52" spans="1:16" x14ac:dyDescent="0.3">
       <c r="A52" t="s">
         <v>50</v>
       </c>
@@ -3710,7 +3710,7 @@
         <v>1142</v>
       </c>
     </row>
-    <row r="53" spans="1:16" s="1" customFormat="1" hidden="1" x14ac:dyDescent="0.3">
+    <row r="53" spans="1:16" s="1" customFormat="1" x14ac:dyDescent="0.3">
       <c r="A53" s="1" t="s">
         <v>63</v>
       </c>
@@ -3774,7 +3774,7 @@
         <v>707745</v>
       </c>
     </row>
-    <row r="54" spans="1:16" hidden="1" x14ac:dyDescent="0.3">
+    <row r="54" spans="1:16" x14ac:dyDescent="0.3">
       <c r="A54" t="s">
         <v>0</v>
       </c>
@@ -3827,7 +3827,7 @@
         <v>4997</v>
       </c>
     </row>
-    <row r="55" spans="1:16" hidden="1" x14ac:dyDescent="0.3">
+    <row r="55" spans="1:16" x14ac:dyDescent="0.3">
       <c r="A55" t="s">
         <v>1</v>
       </c>
@@ -3880,7 +3880,7 @@
         <v>1538</v>
       </c>
     </row>
-    <row r="56" spans="1:16" hidden="1" x14ac:dyDescent="0.3">
+    <row r="56" spans="1:16" x14ac:dyDescent="0.3">
       <c r="A56" t="s">
         <v>2</v>
       </c>
@@ -3933,7 +3933,7 @@
         <v>203</v>
       </c>
     </row>
-    <row r="57" spans="1:16" hidden="1" x14ac:dyDescent="0.3">
+    <row r="57" spans="1:16" x14ac:dyDescent="0.3">
       <c r="A57" t="s">
         <v>3</v>
       </c>
@@ -3986,7 +3986,7 @@
         <v>14620</v>
       </c>
     </row>
-    <row r="58" spans="1:16" hidden="1" x14ac:dyDescent="0.3">
+    <row r="58" spans="1:16" x14ac:dyDescent="0.3">
       <c r="A58" t="s">
         <v>4</v>
       </c>
@@ -4039,7 +4039,7 @@
         <v>315592</v>
       </c>
     </row>
-    <row r="59" spans="1:16" hidden="1" x14ac:dyDescent="0.3">
+    <row r="59" spans="1:16" x14ac:dyDescent="0.3">
       <c r="A59" t="s">
         <v>5</v>
       </c>
@@ -4092,7 +4092,7 @@
         <v>2460</v>
       </c>
     </row>
-    <row r="60" spans="1:16" hidden="1" x14ac:dyDescent="0.3">
+    <row r="60" spans="1:16" x14ac:dyDescent="0.3">
       <c r="A60" t="s">
         <v>6</v>
       </c>
@@ -4145,7 +4145,7 @@
         <v>3176</v>
       </c>
     </row>
-    <row r="61" spans="1:16" hidden="1" x14ac:dyDescent="0.3">
+    <row r="61" spans="1:16" x14ac:dyDescent="0.3">
       <c r="A61" t="s">
         <v>7</v>
       </c>
@@ -4198,7 +4198,7 @@
         <v>766</v>
       </c>
     </row>
-    <row r="62" spans="1:16" hidden="1" x14ac:dyDescent="0.3">
+    <row r="62" spans="1:16" x14ac:dyDescent="0.3">
       <c r="A62" t="s">
         <v>8</v>
       </c>
@@ -4251,7 +4251,7 @@
         <v>216</v>
       </c>
     </row>
-    <row r="63" spans="1:16" hidden="1" x14ac:dyDescent="0.3">
+    <row r="63" spans="1:16" x14ac:dyDescent="0.3">
       <c r="A63" t="s">
         <v>9</v>
       </c>
@@ -4304,7 +4304,7 @@
         <v>39011</v>
       </c>
     </row>
-    <row r="64" spans="1:16" hidden="1" x14ac:dyDescent="0.3">
+    <row r="64" spans="1:16" x14ac:dyDescent="0.3">
       <c r="A64" t="s">
         <v>10</v>
       </c>
@@ -4357,7 +4357,7 @@
         <v>16179</v>
       </c>
     </row>
-    <row r="65" spans="1:16" hidden="1" x14ac:dyDescent="0.3">
+    <row r="65" spans="1:16" x14ac:dyDescent="0.3">
       <c r="A65" t="s">
         <v>11</v>
       </c>
@@ -4410,7 +4410,7 @@
         <v>712</v>
       </c>
     </row>
-    <row r="66" spans="1:16" hidden="1" x14ac:dyDescent="0.3">
+    <row r="66" spans="1:16" x14ac:dyDescent="0.3">
       <c r="A66" t="s">
         <v>12</v>
       </c>
@@ -4463,7 +4463,7 @@
         <v>3138</v>
       </c>
     </row>
-    <row r="67" spans="1:16" hidden="1" x14ac:dyDescent="0.3">
+    <row r="67" spans="1:16" x14ac:dyDescent="0.3">
       <c r="A67" t="s">
         <v>13</v>
       </c>
@@ -4516,7 +4516,7 @@
         <v>748</v>
       </c>
     </row>
-    <row r="68" spans="1:16" hidden="1" x14ac:dyDescent="0.3">
+    <row r="68" spans="1:16" x14ac:dyDescent="0.3">
       <c r="A68" t="s">
         <v>14</v>
       </c>
@@ -4569,7 +4569,7 @@
         <v>17938</v>
       </c>
     </row>
-    <row r="69" spans="1:16" hidden="1" x14ac:dyDescent="0.3">
+    <row r="69" spans="1:16" x14ac:dyDescent="0.3">
       <c r="A69" t="s">
         <v>15</v>
       </c>
@@ -4622,7 +4622,7 @@
         <v>29969</v>
       </c>
     </row>
-    <row r="70" spans="1:16" hidden="1" x14ac:dyDescent="0.3">
+    <row r="70" spans="1:16" x14ac:dyDescent="0.3">
       <c r="A70" t="s">
         <v>16</v>
       </c>
@@ -4675,7 +4675,7 @@
         <v>1241</v>
       </c>
     </row>
-    <row r="71" spans="1:16" hidden="1" x14ac:dyDescent="0.3">
+    <row r="71" spans="1:16" x14ac:dyDescent="0.3">
       <c r="A71" t="s">
         <v>17</v>
       </c>
@@ -4728,7 +4728,7 @@
         <v>792</v>
       </c>
     </row>
-    <row r="72" spans="1:16" hidden="1" x14ac:dyDescent="0.3">
+    <row r="72" spans="1:16" x14ac:dyDescent="0.3">
       <c r="A72" t="s">
         <v>18</v>
       </c>
@@ -4781,7 +4781,7 @@
         <v>14017</v>
       </c>
     </row>
-    <row r="73" spans="1:16" hidden="1" x14ac:dyDescent="0.3">
+    <row r="73" spans="1:16" x14ac:dyDescent="0.3">
       <c r="A73" t="s">
         <v>19</v>
       </c>
@@ -4834,7 +4834,7 @@
         <v>2220</v>
       </c>
     </row>
-    <row r="74" spans="1:16" hidden="1" x14ac:dyDescent="0.3">
+    <row r="74" spans="1:16" x14ac:dyDescent="0.3">
       <c r="A74" t="s">
         <v>20</v>
       </c>
@@ -4887,7 +4887,7 @@
         <v>3637</v>
       </c>
     </row>
-    <row r="75" spans="1:16" hidden="1" x14ac:dyDescent="0.3">
+    <row r="75" spans="1:16" x14ac:dyDescent="0.3">
       <c r="A75" t="s">
         <v>21</v>
       </c>
@@ -4940,7 +4940,7 @@
         <v>3283</v>
       </c>
     </row>
-    <row r="76" spans="1:16" hidden="1" x14ac:dyDescent="0.3">
+    <row r="76" spans="1:16" x14ac:dyDescent="0.3">
       <c r="A76" t="s">
         <v>22</v>
       </c>
@@ -4993,7 +4993,7 @@
         <v>14536</v>
       </c>
     </row>
-    <row r="77" spans="1:16" hidden="1" x14ac:dyDescent="0.3">
+    <row r="77" spans="1:16" x14ac:dyDescent="0.3">
       <c r="A77" t="s">
         <v>23</v>
       </c>
@@ -5046,7 +5046,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="78" spans="1:16" hidden="1" x14ac:dyDescent="0.3">
+    <row r="78" spans="1:16" x14ac:dyDescent="0.3">
       <c r="A78" t="s">
         <v>24</v>
       </c>
@@ -5099,7 +5099,7 @@
         <v>26508</v>
       </c>
     </row>
-    <row r="79" spans="1:16" hidden="1" x14ac:dyDescent="0.3">
+    <row r="79" spans="1:16" x14ac:dyDescent="0.3">
       <c r="A79" t="s">
         <v>25</v>
       </c>
@@ -5152,7 +5152,7 @@
         <v>12</v>
       </c>
     </row>
-    <row r="80" spans="1:16" hidden="1" x14ac:dyDescent="0.3">
+    <row r="80" spans="1:16" x14ac:dyDescent="0.3">
       <c r="A80" t="s">
         <v>26</v>
       </c>
@@ -5205,7 +5205,7 @@
         <v>3575</v>
       </c>
     </row>
-    <row r="81" spans="1:16" hidden="1" x14ac:dyDescent="0.3">
+    <row r="81" spans="1:16" x14ac:dyDescent="0.3">
       <c r="A81" t="s">
         <v>27</v>
       </c>
@@ -5258,7 +5258,7 @@
         <v>90457</v>
       </c>
     </row>
-    <row r="82" spans="1:16" hidden="1" x14ac:dyDescent="0.3">
+    <row r="82" spans="1:16" x14ac:dyDescent="0.3">
       <c r="A82" t="s">
         <v>28</v>
       </c>
@@ -5311,7 +5311,7 @@
         <v>1895</v>
       </c>
     </row>
-    <row r="83" spans="1:16" hidden="1" x14ac:dyDescent="0.3">
+    <row r="83" spans="1:16" x14ac:dyDescent="0.3">
       <c r="A83" t="s">
         <v>29</v>
       </c>
@@ -5364,7 +5364,7 @@
         <v>2642</v>
       </c>
     </row>
-    <row r="84" spans="1:16" hidden="1" x14ac:dyDescent="0.3">
+    <row r="84" spans="1:16" x14ac:dyDescent="0.3">
       <c r="A84" t="s">
         <v>30</v>
       </c>
@@ -5417,7 +5417,7 @@
         <v>1447</v>
       </c>
     </row>
-    <row r="85" spans="1:16" hidden="1" x14ac:dyDescent="0.3">
+    <row r="85" spans="1:16" x14ac:dyDescent="0.3">
       <c r="A85" t="s">
         <v>31</v>
       </c>
@@ -5470,7 +5470,7 @@
         <v>54625</v>
       </c>
     </row>
-    <row r="86" spans="1:16" hidden="1" x14ac:dyDescent="0.3">
+    <row r="86" spans="1:16" x14ac:dyDescent="0.3">
       <c r="A86" t="s">
         <v>32</v>
       </c>
@@ -5523,7 +5523,7 @@
         <v>692</v>
       </c>
     </row>
-    <row r="87" spans="1:16" hidden="1" x14ac:dyDescent="0.3">
+    <row r="87" spans="1:16" x14ac:dyDescent="0.3">
       <c r="A87" t="s">
         <v>33</v>
       </c>
@@ -5576,7 +5576,7 @@
         <v>1429</v>
       </c>
     </row>
-    <row r="88" spans="1:16" hidden="1" x14ac:dyDescent="0.3">
+    <row r="88" spans="1:16" x14ac:dyDescent="0.3">
       <c r="A88" t="s">
         <v>34</v>
       </c>
@@ -5629,7 +5629,7 @@
         <v>6244</v>
       </c>
     </row>
-    <row r="89" spans="1:16" hidden="1" x14ac:dyDescent="0.3">
+    <row r="89" spans="1:16" x14ac:dyDescent="0.3">
       <c r="A89" t="s">
         <v>35</v>
       </c>
@@ -5682,7 +5682,7 @@
         <v>23280</v>
       </c>
     </row>
-    <row r="90" spans="1:16" hidden="1" x14ac:dyDescent="0.3">
+    <row r="90" spans="1:16" x14ac:dyDescent="0.3">
       <c r="A90" t="s">
         <v>36</v>
       </c>
@@ -5735,7 +5735,7 @@
         <v>5405</v>
       </c>
     </row>
-    <row r="91" spans="1:16" hidden="1" x14ac:dyDescent="0.3">
+    <row r="91" spans="1:16" x14ac:dyDescent="0.3">
       <c r="A91" t="s">
         <v>37</v>
       </c>
@@ -5788,7 +5788,7 @@
         <v>250</v>
       </c>
     </row>
-    <row r="92" spans="1:16" hidden="1" x14ac:dyDescent="0.3">
+    <row r="92" spans="1:16" x14ac:dyDescent="0.3">
       <c r="A92" t="s">
         <v>38</v>
       </c>
@@ -5841,7 +5841,7 @@
         <v>83870</v>
       </c>
     </row>
-    <row r="93" spans="1:16" hidden="1" x14ac:dyDescent="0.3">
+    <row r="93" spans="1:16" x14ac:dyDescent="0.3">
       <c r="A93" t="s">
         <v>39</v>
       </c>
@@ -5894,7 +5894,7 @@
         <v>94</v>
       </c>
     </row>
-    <row r="94" spans="1:16" hidden="1" x14ac:dyDescent="0.3">
+    <row r="94" spans="1:16" x14ac:dyDescent="0.3">
       <c r="A94" t="s">
         <v>40</v>
       </c>
@@ -5947,7 +5947,7 @@
         <v>1407</v>
       </c>
     </row>
-    <row r="95" spans="1:16" hidden="1" x14ac:dyDescent="0.3">
+    <row r="95" spans="1:16" x14ac:dyDescent="0.3">
       <c r="A95" t="s">
         <v>41</v>
       </c>
@@ -6000,7 +6000,7 @@
         <v>333</v>
       </c>
     </row>
-    <row r="96" spans="1:16" hidden="1" x14ac:dyDescent="0.3">
+    <row r="96" spans="1:16" x14ac:dyDescent="0.3">
       <c r="A96" t="s">
         <v>42</v>
       </c>
@@ -6053,7 +6053,7 @@
         <v>369</v>
       </c>
     </row>
-    <row r="97" spans="1:16" hidden="1" x14ac:dyDescent="0.3">
+    <row r="97" spans="1:16" x14ac:dyDescent="0.3">
       <c r="A97" t="s">
         <v>43</v>
       </c>
@@ -6106,7 +6106,7 @@
         <v>20975</v>
       </c>
     </row>
-    <row r="98" spans="1:16" hidden="1" x14ac:dyDescent="0.3">
+    <row r="98" spans="1:16" x14ac:dyDescent="0.3">
       <c r="A98" t="s">
         <v>44</v>
       </c>
@@ -6159,7 +6159,7 @@
         <v>5412</v>
       </c>
     </row>
-    <row r="99" spans="1:16" hidden="1" x14ac:dyDescent="0.3">
+    <row r="99" spans="1:16" x14ac:dyDescent="0.3">
       <c r="A99" t="s">
         <v>45</v>
       </c>
@@ -6212,7 +6212,7 @@
         <v>27048</v>
       </c>
     </row>
-    <row r="100" spans="1:16" hidden="1" x14ac:dyDescent="0.3">
+    <row r="100" spans="1:16" x14ac:dyDescent="0.3">
       <c r="A100" t="s">
         <v>46</v>
       </c>
@@ -6265,7 +6265,7 @@
         <v>881</v>
       </c>
     </row>
-    <row r="101" spans="1:16" hidden="1" x14ac:dyDescent="0.3">
+    <row r="101" spans="1:16" x14ac:dyDescent="0.3">
       <c r="A101" t="s">
         <v>47</v>
       </c>
@@ -6318,7 +6318,7 @@
         <v>894</v>
       </c>
     </row>
-    <row r="102" spans="1:16" hidden="1" x14ac:dyDescent="0.3">
+    <row r="102" spans="1:16" x14ac:dyDescent="0.3">
       <c r="A102" t="s">
         <v>48</v>
       </c>
@@ -6371,7 +6371,7 @@
         <v>4959</v>
       </c>
     </row>
-    <row r="103" spans="1:16" hidden="1" x14ac:dyDescent="0.3">
+    <row r="103" spans="1:16" x14ac:dyDescent="0.3">
       <c r="A103" t="s">
         <v>49</v>
       </c>
@@ -6424,7 +6424,7 @@
         <v>190</v>
       </c>
     </row>
-    <row r="104" spans="1:16" hidden="1" x14ac:dyDescent="0.3">
+    <row r="104" spans="1:16" x14ac:dyDescent="0.3">
       <c r="A104" t="s">
         <v>50</v>
       </c>
@@ -6477,7 +6477,7 @@
         <v>1288</v>
       </c>
     </row>
-    <row r="105" spans="1:16" s="1" customFormat="1" hidden="1" x14ac:dyDescent="0.3">
+    <row r="105" spans="1:16" s="1" customFormat="1" x14ac:dyDescent="0.3">
       <c r="A105" s="1" t="s">
         <v>63</v>
       </c>
@@ -6541,7 +6541,7 @@
         <v>857170</v>
       </c>
     </row>
-    <row r="106" spans="1:16" hidden="1" x14ac:dyDescent="0.3">
+    <row r="106" spans="1:16" x14ac:dyDescent="0.3">
       <c r="A106" t="s">
         <v>0</v>
       </c>
@@ -6594,7 +6594,7 @@
         <v>3851</v>
       </c>
     </row>
-    <row r="107" spans="1:16" hidden="1" x14ac:dyDescent="0.3">
+    <row r="107" spans="1:16" x14ac:dyDescent="0.3">
       <c r="A107" t="s">
         <v>1</v>
       </c>
@@ -6647,7 +6647,7 @@
         <v>1196</v>
       </c>
     </row>
-    <row r="108" spans="1:16" hidden="1" x14ac:dyDescent="0.3">
+    <row r="108" spans="1:16" x14ac:dyDescent="0.3">
       <c r="A108" t="s">
         <v>2</v>
       </c>
@@ -6700,7 +6700,7 @@
         <v>217</v>
       </c>
     </row>
-    <row r="109" spans="1:16" hidden="1" x14ac:dyDescent="0.3">
+    <row r="109" spans="1:16" x14ac:dyDescent="0.3">
       <c r="A109" t="s">
         <v>3</v>
       </c>
@@ -6753,7 +6753,7 @@
         <v>10354</v>
       </c>
     </row>
-    <row r="110" spans="1:16" hidden="1" x14ac:dyDescent="0.3">
+    <row r="110" spans="1:16" x14ac:dyDescent="0.3">
       <c r="A110" t="s">
         <v>4</v>
       </c>
@@ -6806,7 +6806,7 @@
         <v>225310</v>
       </c>
     </row>
-    <row r="111" spans="1:16" hidden="1" x14ac:dyDescent="0.3">
+    <row r="111" spans="1:16" x14ac:dyDescent="0.3">
       <c r="A111" t="s">
         <v>5</v>
       </c>
@@ -6859,7 +6859,7 @@
         <v>2280</v>
       </c>
     </row>
-    <row r="112" spans="1:16" hidden="1" x14ac:dyDescent="0.3">
+    <row r="112" spans="1:16" x14ac:dyDescent="0.3">
       <c r="A112" t="s">
         <v>6</v>
       </c>
@@ -6912,7 +6912,7 @@
         <v>3564</v>
       </c>
     </row>
-    <row r="113" spans="1:16" hidden="1" x14ac:dyDescent="0.3">
+    <row r="113" spans="1:16" x14ac:dyDescent="0.3">
       <c r="A113" t="s">
         <v>7</v>
       </c>
@@ -6965,7 +6965,7 @@
         <v>861</v>
       </c>
     </row>
-    <row r="114" spans="1:16" hidden="1" x14ac:dyDescent="0.3">
+    <row r="114" spans="1:16" x14ac:dyDescent="0.3">
       <c r="A114" t="s">
         <v>8</v>
       </c>
@@ -7018,7 +7018,7 @@
         <v>321</v>
       </c>
     </row>
-    <row r="115" spans="1:16" hidden="1" x14ac:dyDescent="0.3">
+    <row r="115" spans="1:16" x14ac:dyDescent="0.3">
       <c r="A115" t="s">
         <v>9</v>
       </c>
@@ -7071,7 +7071,7 @@
         <v>40538</v>
       </c>
     </row>
-    <row r="116" spans="1:16" hidden="1" x14ac:dyDescent="0.3">
+    <row r="116" spans="1:16" x14ac:dyDescent="0.3">
       <c r="A116" t="s">
         <v>10</v>
       </c>
@@ -7124,7 +7124,7 @@
         <v>17747</v>
       </c>
     </row>
-    <row r="117" spans="1:16" hidden="1" x14ac:dyDescent="0.3">
+    <row r="117" spans="1:16" x14ac:dyDescent="0.3">
       <c r="A117" t="s">
         <v>11</v>
       </c>
@@ -7177,7 +7177,7 @@
         <v>761</v>
       </c>
     </row>
-    <row r="118" spans="1:16" hidden="1" x14ac:dyDescent="0.3">
+    <row r="118" spans="1:16" x14ac:dyDescent="0.3">
       <c r="A118" t="s">
         <v>12</v>
       </c>
@@ -7230,7 +7230,7 @@
         <v>8186</v>
       </c>
     </row>
-    <row r="119" spans="1:16" hidden="1" x14ac:dyDescent="0.3">
+    <row r="119" spans="1:16" x14ac:dyDescent="0.3">
       <c r="A119" t="s">
         <v>13</v>
       </c>
@@ -7283,7 +7283,7 @@
         <v>23</v>
       </c>
     </row>
-    <row r="120" spans="1:16" hidden="1" x14ac:dyDescent="0.3">
+    <row r="120" spans="1:16" x14ac:dyDescent="0.3">
       <c r="A120" t="s">
         <v>14</v>
       </c>
@@ -7336,7 +7336,7 @@
         <v>22004</v>
       </c>
     </row>
-    <row r="121" spans="1:16" hidden="1" x14ac:dyDescent="0.3">
+    <row r="121" spans="1:16" x14ac:dyDescent="0.3">
       <c r="A121" t="s">
         <v>15</v>
       </c>
@@ -7389,7 +7389,7 @@
         <v>31203</v>
       </c>
     </row>
-    <row r="122" spans="1:16" hidden="1" x14ac:dyDescent="0.3">
+    <row r="122" spans="1:16" x14ac:dyDescent="0.3">
       <c r="A122" t="s">
         <v>16</v>
       </c>
@@ -7442,7 +7442,7 @@
         <v>733</v>
       </c>
     </row>
-    <row r="123" spans="1:16" hidden="1" x14ac:dyDescent="0.3">
+    <row r="123" spans="1:16" x14ac:dyDescent="0.3">
       <c r="A123" t="s">
         <v>17</v>
       </c>
@@ -7495,7 +7495,7 @@
         <v>758</v>
       </c>
     </row>
-    <row r="124" spans="1:16" hidden="1" x14ac:dyDescent="0.3">
+    <row r="124" spans="1:16" x14ac:dyDescent="0.3">
       <c r="A124" t="s">
         <v>18</v>
       </c>
@@ -7548,7 +7548,7 @@
         <v>21996</v>
       </c>
     </row>
-    <row r="125" spans="1:16" hidden="1" x14ac:dyDescent="0.3">
+    <row r="125" spans="1:16" x14ac:dyDescent="0.3">
       <c r="A125" t="s">
         <v>19</v>
       </c>
@@ -7601,7 +7601,7 @@
         <v>2837</v>
       </c>
     </row>
-    <row r="126" spans="1:16" hidden="1" x14ac:dyDescent="0.3">
+    <row r="126" spans="1:16" x14ac:dyDescent="0.3">
       <c r="A126" t="s">
         <v>20</v>
       </c>
@@ -7654,7 +7654,7 @@
         <v>3608</v>
       </c>
     </row>
-    <row r="127" spans="1:16" hidden="1" x14ac:dyDescent="0.3">
+    <row r="127" spans="1:16" x14ac:dyDescent="0.3">
       <c r="A127" t="s">
         <v>21</v>
       </c>
@@ -7707,7 +7707,7 @@
         <v>3713</v>
       </c>
     </row>
-    <row r="128" spans="1:16" hidden="1" x14ac:dyDescent="0.3">
+    <row r="128" spans="1:16" x14ac:dyDescent="0.3">
       <c r="A128" t="s">
         <v>22</v>
       </c>
@@ -7760,7 +7760,7 @@
         <v>16505</v>
       </c>
     </row>
-    <row r="129" spans="1:16" hidden="1" x14ac:dyDescent="0.3">
+    <row r="129" spans="1:16" x14ac:dyDescent="0.3">
       <c r="A129" t="s">
         <v>23</v>
       </c>
@@ -7813,7 +7813,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="130" spans="1:16" hidden="1" x14ac:dyDescent="0.3">
+    <row r="130" spans="1:16" x14ac:dyDescent="0.3">
       <c r="A130" t="s">
         <v>24</v>
       </c>
@@ -7866,7 +7866,7 @@
         <v>22726</v>
       </c>
     </row>
-    <row r="131" spans="1:16" hidden="1" x14ac:dyDescent="0.3">
+    <row r="131" spans="1:16" x14ac:dyDescent="0.3">
       <c r="A131" t="s">
         <v>25</v>
       </c>
@@ -7919,7 +7919,7 @@
         <v>21</v>
       </c>
     </row>
-    <row r="132" spans="1:16" hidden="1" x14ac:dyDescent="0.3">
+    <row r="132" spans="1:16" x14ac:dyDescent="0.3">
       <c r="A132" t="s">
         <v>26</v>
       </c>
@@ -7972,7 +7972,7 @@
         <v>3654</v>
       </c>
     </row>
-    <row r="133" spans="1:16" hidden="1" x14ac:dyDescent="0.3">
+    <row r="133" spans="1:16" x14ac:dyDescent="0.3">
       <c r="A133" t="s">
         <v>27</v>
       </c>
@@ -8025,7 +8025,7 @@
         <v>88290</v>
       </c>
     </row>
-    <row r="134" spans="1:16" hidden="1" x14ac:dyDescent="0.3">
+    <row r="134" spans="1:16" x14ac:dyDescent="0.3">
       <c r="A134" t="s">
         <v>28</v>
       </c>
@@ -8078,7 +8078,7 @@
         <v>2304</v>
       </c>
     </row>
-    <row r="135" spans="1:16" hidden="1" x14ac:dyDescent="0.3">
+    <row r="135" spans="1:16" x14ac:dyDescent="0.3">
       <c r="A135" t="s">
         <v>29</v>
       </c>
@@ -8131,7 +8131,7 @@
         <v>3168</v>
       </c>
     </row>
-    <row r="136" spans="1:16" hidden="1" x14ac:dyDescent="0.3">
+    <row r="136" spans="1:16" x14ac:dyDescent="0.3">
       <c r="A136" t="s">
         <v>30</v>
       </c>
@@ -8184,7 +8184,7 @@
         <v>885</v>
       </c>
     </row>
-    <row r="137" spans="1:16" hidden="1" x14ac:dyDescent="0.3">
+    <row r="137" spans="1:16" x14ac:dyDescent="0.3">
       <c r="A137" t="s">
         <v>31</v>
       </c>
@@ -8237,7 +8237,7 @@
         <v>41405</v>
       </c>
     </row>
-    <row r="138" spans="1:16" hidden="1" x14ac:dyDescent="0.3">
+    <row r="138" spans="1:16" x14ac:dyDescent="0.3">
       <c r="A138" t="s">
         <v>32</v>
       </c>
@@ -8290,7 +8290,7 @@
         <v>841</v>
       </c>
     </row>
-    <row r="139" spans="1:16" hidden="1" x14ac:dyDescent="0.3">
+    <row r="139" spans="1:16" x14ac:dyDescent="0.3">
       <c r="A139" t="s">
         <v>33</v>
       </c>
@@ -8343,7 +8343,7 @@
         <v>1884</v>
       </c>
     </row>
-    <row r="140" spans="1:16" hidden="1" x14ac:dyDescent="0.3">
+    <row r="140" spans="1:16" x14ac:dyDescent="0.3">
       <c r="A140" t="s">
         <v>34</v>
       </c>
@@ -8396,7 +8396,7 @@
         <v>7274</v>
       </c>
     </row>
-    <row r="141" spans="1:16" hidden="1" x14ac:dyDescent="0.3">
+    <row r="141" spans="1:16" x14ac:dyDescent="0.3">
       <c r="A141" t="s">
         <v>35</v>
       </c>
@@ -8449,7 +8449,7 @@
         <v>33293</v>
       </c>
     </row>
-    <row r="142" spans="1:16" hidden="1" x14ac:dyDescent="0.3">
+    <row r="142" spans="1:16" x14ac:dyDescent="0.3">
       <c r="A142" t="s">
         <v>36</v>
       </c>
@@ -8502,7 +8502,7 @@
         <v>4213</v>
       </c>
     </row>
-    <row r="143" spans="1:16" hidden="1" x14ac:dyDescent="0.3">
+    <row r="143" spans="1:16" x14ac:dyDescent="0.3">
       <c r="A143" t="s">
         <v>37</v>
       </c>
@@ -8555,7 +8555,7 @@
         <v>263</v>
       </c>
     </row>
-    <row r="144" spans="1:16" hidden="1" x14ac:dyDescent="0.3">
+    <row r="144" spans="1:16" x14ac:dyDescent="0.3">
       <c r="A144" t="s">
         <v>38</v>
       </c>
@@ -8608,7 +8608,7 @@
         <v>81813</v>
       </c>
     </row>
-    <row r="145" spans="1:16" hidden="1" x14ac:dyDescent="0.3">
+    <row r="145" spans="1:16" x14ac:dyDescent="0.3">
       <c r="A145" t="s">
         <v>39</v>
       </c>
@@ -8661,7 +8661,7 @@
         <v>90</v>
       </c>
     </row>
-    <row r="146" spans="1:16" hidden="1" x14ac:dyDescent="0.3">
+    <row r="146" spans="1:16" x14ac:dyDescent="0.3">
       <c r="A146" t="s">
         <v>40</v>
       </c>
@@ -8714,7 +8714,7 @@
         <v>1288</v>
       </c>
     </row>
-    <row r="147" spans="1:16" hidden="1" x14ac:dyDescent="0.3">
+    <row r="147" spans="1:16" x14ac:dyDescent="0.3">
       <c r="A147" t="s">
         <v>41</v>
       </c>
@@ -8767,7 +8767,7 @@
         <v>339</v>
       </c>
     </row>
-    <row r="148" spans="1:16" hidden="1" x14ac:dyDescent="0.3">
+    <row r="148" spans="1:16" x14ac:dyDescent="0.3">
       <c r="A148" t="s">
         <v>42</v>
       </c>
@@ -8820,7 +8820,7 @@
         <v>242</v>
       </c>
     </row>
-    <row r="149" spans="1:16" hidden="1" x14ac:dyDescent="0.3">
+    <row r="149" spans="1:16" x14ac:dyDescent="0.3">
       <c r="A149" t="s">
         <v>43</v>
       </c>
@@ -8873,7 +8873,7 @@
         <v>18494</v>
       </c>
     </row>
-    <row r="150" spans="1:16" hidden="1" x14ac:dyDescent="0.3">
+    <row r="150" spans="1:16" x14ac:dyDescent="0.3">
       <c r="A150" t="s">
         <v>44</v>
       </c>
@@ -8926,7 +8926,7 @@
         <v>5555</v>
       </c>
     </row>
-    <row r="151" spans="1:16" hidden="1" x14ac:dyDescent="0.3">
+    <row r="151" spans="1:16" x14ac:dyDescent="0.3">
       <c r="A151" t="s">
         <v>45</v>
       </c>
@@ -8979,7 +8979,7 @@
         <v>1356</v>
       </c>
     </row>
-    <row r="152" spans="1:16" hidden="1" x14ac:dyDescent="0.3">
+    <row r="152" spans="1:16" x14ac:dyDescent="0.3">
       <c r="A152" t="s">
         <v>46</v>
       </c>
@@ -9032,7 +9032,7 @@
         <v>1108</v>
       </c>
     </row>
-    <row r="153" spans="1:16" hidden="1" x14ac:dyDescent="0.3">
+    <row r="153" spans="1:16" x14ac:dyDescent="0.3">
       <c r="A153" t="s">
         <v>47</v>
       </c>
@@ -9085,7 +9085,7 @@
         <v>1154</v>
       </c>
     </row>
-    <row r="154" spans="1:16" hidden="1" x14ac:dyDescent="0.3">
+    <row r="154" spans="1:16" x14ac:dyDescent="0.3">
       <c r="A154" t="s">
         <v>48</v>
       </c>
@@ -9138,7 +9138,7 @@
         <v>5592</v>
       </c>
     </row>
-    <row r="155" spans="1:16" hidden="1" x14ac:dyDescent="0.3">
+    <row r="155" spans="1:16" x14ac:dyDescent="0.3">
       <c r="A155" t="s">
         <v>49</v>
       </c>
@@ -9191,7 +9191,7 @@
         <v>341</v>
       </c>
     </row>
-    <row r="156" spans="1:16" hidden="1" x14ac:dyDescent="0.3">
+    <row r="156" spans="1:16" x14ac:dyDescent="0.3">
       <c r="A156" t="s">
         <v>50</v>
       </c>
@@ -9244,7 +9244,7 @@
         <v>544</v>
       </c>
     </row>
-    <row r="157" spans="1:16" s="1" customFormat="1" hidden="1" x14ac:dyDescent="0.3">
+    <row r="157" spans="1:16" s="1" customFormat="1" x14ac:dyDescent="0.3">
       <c r="A157" s="1" t="s">
         <v>63</v>
       </c>
@@ -9308,7 +9308,7 @@
         <v>746703</v>
       </c>
     </row>
-    <row r="158" spans="1:16" hidden="1" x14ac:dyDescent="0.3">
+    <row r="158" spans="1:16" x14ac:dyDescent="0.3">
       <c r="A158" t="s">
         <v>0</v>
       </c>
@@ -9361,7 +9361,7 @@
         <v>3966</v>
       </c>
     </row>
-    <row r="159" spans="1:16" hidden="1" x14ac:dyDescent="0.3">
+    <row r="159" spans="1:16" x14ac:dyDescent="0.3">
       <c r="A159" t="s">
         <v>1</v>
       </c>
@@ -9414,7 +9414,7 @@
         <v>986</v>
       </c>
     </row>
-    <row r="160" spans="1:16" hidden="1" x14ac:dyDescent="0.3">
+    <row r="160" spans="1:16" x14ac:dyDescent="0.3">
       <c r="A160" t="s">
         <v>2</v>
       </c>
@@ -9467,7 +9467,7 @@
         <v>114</v>
       </c>
     </row>
-    <row r="161" spans="1:16" hidden="1" x14ac:dyDescent="0.3">
+    <row r="161" spans="1:16" x14ac:dyDescent="0.3">
       <c r="A161" t="s">
         <v>3</v>
       </c>
@@ -9520,7 +9520,7 @@
         <v>12130</v>
       </c>
     </row>
-    <row r="162" spans="1:16" hidden="1" x14ac:dyDescent="0.3">
+    <row r="162" spans="1:16" x14ac:dyDescent="0.3">
       <c r="A162" t="s">
         <v>4</v>
       </c>
@@ -9573,7 +9573,7 @@
         <v>229831</v>
       </c>
     </row>
-    <row r="163" spans="1:16" hidden="1" x14ac:dyDescent="0.3">
+    <row r="163" spans="1:16" x14ac:dyDescent="0.3">
       <c r="A163" t="s">
         <v>5</v>
       </c>
@@ -9626,7 +9626,7 @@
         <v>2178</v>
       </c>
     </row>
-    <row r="164" spans="1:16" hidden="1" x14ac:dyDescent="0.3">
+    <row r="164" spans="1:16" x14ac:dyDescent="0.3">
       <c r="A164" t="s">
         <v>6</v>
       </c>
@@ -9679,7 +9679,7 @@
         <v>3497</v>
       </c>
     </row>
-    <row r="165" spans="1:16" hidden="1" x14ac:dyDescent="0.3">
+    <row r="165" spans="1:16" x14ac:dyDescent="0.3">
       <c r="A165" t="s">
         <v>7</v>
       </c>
@@ -9732,7 +9732,7 @@
         <v>1875</v>
       </c>
     </row>
-    <row r="166" spans="1:16" hidden="1" x14ac:dyDescent="0.3">
+    <row r="166" spans="1:16" x14ac:dyDescent="0.3">
       <c r="A166" t="s">
         <v>8</v>
       </c>
@@ -9785,7 +9785,7 @@
         <v>247</v>
       </c>
     </row>
-    <row r="167" spans="1:16" hidden="1" x14ac:dyDescent="0.3">
+    <row r="167" spans="1:16" x14ac:dyDescent="0.3">
       <c r="A167" t="s">
         <v>9</v>
       </c>
@@ -9838,7 +9838,7 @@
         <v>37401</v>
       </c>
     </row>
-    <row r="168" spans="1:16" hidden="1" x14ac:dyDescent="0.3">
+    <row r="168" spans="1:16" x14ac:dyDescent="0.3">
       <c r="A168" t="s">
         <v>10</v>
       </c>
@@ -9891,7 +9891,7 @@
         <v>17591</v>
       </c>
     </row>
-    <row r="169" spans="1:16" hidden="1" x14ac:dyDescent="0.3">
+    <row r="169" spans="1:16" x14ac:dyDescent="0.3">
       <c r="A169" t="s">
         <v>11</v>
       </c>
@@ -9944,7 +9944,7 @@
         <v>1018</v>
       </c>
     </row>
-    <row r="170" spans="1:16" hidden="1" x14ac:dyDescent="0.3">
+    <row r="170" spans="1:16" x14ac:dyDescent="0.3">
       <c r="A170" t="s">
         <v>12</v>
       </c>
@@ -9997,7 +9997,7 @@
         <v>2490</v>
       </c>
     </row>
-    <row r="171" spans="1:16" hidden="1" x14ac:dyDescent="0.3">
+    <row r="171" spans="1:16" x14ac:dyDescent="0.3">
       <c r="A171" t="s">
         <v>13</v>
       </c>
@@ -10050,7 +10050,7 @@
         <v>466</v>
       </c>
     </row>
-    <row r="172" spans="1:16" hidden="1" x14ac:dyDescent="0.3">
+    <row r="172" spans="1:16" x14ac:dyDescent="0.3">
       <c r="A172" t="s">
         <v>14</v>
       </c>
@@ -10103,7 +10103,7 @@
         <v>23661</v>
       </c>
     </row>
-    <row r="173" spans="1:16" hidden="1" x14ac:dyDescent="0.3">
+    <row r="173" spans="1:16" x14ac:dyDescent="0.3">
       <c r="A173" t="s">
         <v>15</v>
       </c>
@@ -10156,7 +10156,7 @@
         <v>35484</v>
       </c>
     </row>
-    <row r="174" spans="1:16" hidden="1" x14ac:dyDescent="0.3">
+    <row r="174" spans="1:16" x14ac:dyDescent="0.3">
       <c r="A174" t="s">
         <v>16</v>
       </c>
@@ -10209,7 +10209,7 @@
         <v>1394</v>
       </c>
     </row>
-    <row r="175" spans="1:16" hidden="1" x14ac:dyDescent="0.3">
+    <row r="175" spans="1:16" x14ac:dyDescent="0.3">
       <c r="A175" t="s">
         <v>17</v>
       </c>
@@ -10262,7 +10262,7 @@
         <v>1068</v>
       </c>
     </row>
-    <row r="176" spans="1:16" hidden="1" x14ac:dyDescent="0.3">
+    <row r="176" spans="1:16" x14ac:dyDescent="0.3">
       <c r="A176" t="s">
         <v>18</v>
       </c>
@@ -10315,7 +10315,7 @@
         <v>16545</v>
       </c>
     </row>
-    <row r="177" spans="1:16" hidden="1" x14ac:dyDescent="0.3">
+    <row r="177" spans="1:16" x14ac:dyDescent="0.3">
       <c r="A177" t="s">
         <v>19</v>
       </c>
@@ -10368,7 +10368,7 @@
         <v>1510</v>
       </c>
     </row>
-    <row r="178" spans="1:16" hidden="1" x14ac:dyDescent="0.3">
+    <row r="178" spans="1:16" x14ac:dyDescent="0.3">
       <c r="A178" t="s">
         <v>20</v>
       </c>
@@ -10421,7 +10421,7 @@
         <v>3955</v>
       </c>
     </row>
-    <row r="179" spans="1:16" hidden="1" x14ac:dyDescent="0.3">
+    <row r="179" spans="1:16" x14ac:dyDescent="0.3">
       <c r="A179" t="s">
         <v>21</v>
       </c>
@@ -10474,7 +10474,7 @@
         <v>2988</v>
       </c>
     </row>
-    <row r="180" spans="1:16" hidden="1" x14ac:dyDescent="0.3">
+    <row r="180" spans="1:16" x14ac:dyDescent="0.3">
       <c r="A180" t="s">
         <v>22</v>
       </c>
@@ -10527,7 +10527,7 @@
         <v>13068</v>
       </c>
     </row>
-    <row r="181" spans="1:16" hidden="1" x14ac:dyDescent="0.3">
+    <row r="181" spans="1:16" x14ac:dyDescent="0.3">
       <c r="A181" t="s">
         <v>23</v>
       </c>
@@ -10580,7 +10580,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="182" spans="1:16" hidden="1" x14ac:dyDescent="0.3">
+    <row r="182" spans="1:16" x14ac:dyDescent="0.3">
       <c r="A182" t="s">
         <v>24</v>
       </c>
@@ -10633,7 +10633,7 @@
         <v>27723</v>
       </c>
     </row>
-    <row r="183" spans="1:16" hidden="1" x14ac:dyDescent="0.3">
+    <row r="183" spans="1:16" x14ac:dyDescent="0.3">
       <c r="A183" t="s">
         <v>25</v>
       </c>
@@ -10686,7 +10686,7 @@
         <v>24</v>
       </c>
     </row>
-    <row r="184" spans="1:16" hidden="1" x14ac:dyDescent="0.3">
+    <row r="184" spans="1:16" x14ac:dyDescent="0.3">
       <c r="A184" t="s">
         <v>26</v>
       </c>
@@ -10739,7 +10739,7 @@
         <v>4224</v>
       </c>
     </row>
-    <row r="185" spans="1:16" hidden="1" x14ac:dyDescent="0.3">
+    <row r="185" spans="1:16" x14ac:dyDescent="0.3">
       <c r="A185" t="s">
         <v>27</v>
       </c>
@@ -10792,7 +10792,7 @@
         <v>98044</v>
       </c>
     </row>
-    <row r="186" spans="1:16" hidden="1" x14ac:dyDescent="0.3">
+    <row r="186" spans="1:16" x14ac:dyDescent="0.3">
       <c r="A186" t="s">
         <v>28</v>
       </c>
@@ -10845,7 +10845,7 @@
         <v>2294</v>
       </c>
     </row>
-    <row r="187" spans="1:16" hidden="1" x14ac:dyDescent="0.3">
+    <row r="187" spans="1:16" x14ac:dyDescent="0.3">
       <c r="A187" t="s">
         <v>29</v>
       </c>
@@ -10898,7 +10898,7 @@
         <v>2770</v>
       </c>
     </row>
-    <row r="188" spans="1:16" hidden="1" x14ac:dyDescent="0.3">
+    <row r="188" spans="1:16" x14ac:dyDescent="0.3">
       <c r="A188" t="s">
         <v>30</v>
       </c>
@@ -10951,7 +10951,7 @@
         <v>610</v>
       </c>
     </row>
-    <row r="189" spans="1:16" hidden="1" x14ac:dyDescent="0.3">
+    <row r="189" spans="1:16" x14ac:dyDescent="0.3">
       <c r="A189" t="s">
         <v>31</v>
       </c>
@@ -11004,7 +11004,7 @@
         <v>43962</v>
       </c>
     </row>
-    <row r="190" spans="1:16" hidden="1" x14ac:dyDescent="0.3">
+    <row r="190" spans="1:16" x14ac:dyDescent="0.3">
       <c r="A190" t="s">
         <v>32</v>
       </c>
@@ -11057,7 +11057,7 @@
         <v>768</v>
       </c>
     </row>
-    <row r="191" spans="1:16" hidden="1" x14ac:dyDescent="0.3">
+    <row r="191" spans="1:16" x14ac:dyDescent="0.3">
       <c r="A191" t="s">
         <v>33</v>
       </c>
@@ -11110,7 +11110,7 @@
         <v>3563</v>
       </c>
     </row>
-    <row r="192" spans="1:16" hidden="1" x14ac:dyDescent="0.3">
+    <row r="192" spans="1:16" x14ac:dyDescent="0.3">
       <c r="A192" t="s">
         <v>34</v>
       </c>
@@ -11163,7 +11163,7 @@
         <v>6066</v>
       </c>
     </row>
-    <row r="193" spans="1:16" hidden="1" x14ac:dyDescent="0.3">
+    <row r="193" spans="1:16" x14ac:dyDescent="0.3">
       <c r="A193" t="s">
         <v>35</v>
       </c>
@@ -11216,7 +11216,7 @@
         <v>32909</v>
       </c>
     </row>
-    <row r="194" spans="1:16" hidden="1" x14ac:dyDescent="0.3">
+    <row r="194" spans="1:16" x14ac:dyDescent="0.3">
       <c r="A194" t="s">
         <v>36</v>
       </c>
@@ -11269,7 +11269,7 @@
         <v>3895</v>
       </c>
     </row>
-    <row r="195" spans="1:16" hidden="1" x14ac:dyDescent="0.3">
+    <row r="195" spans="1:16" x14ac:dyDescent="0.3">
       <c r="A195" t="s">
         <v>37</v>
       </c>
@@ -11322,7 +11322,7 @@
         <v>230</v>
       </c>
     </row>
-    <row r="196" spans="1:16" hidden="1" x14ac:dyDescent="0.3">
+    <row r="196" spans="1:16" x14ac:dyDescent="0.3">
       <c r="A196" t="s">
         <v>38</v>
       </c>
@@ -11375,7 +11375,7 @@
         <v>69126</v>
       </c>
     </row>
-    <row r="197" spans="1:16" hidden="1" x14ac:dyDescent="0.3">
+    <row r="197" spans="1:16" x14ac:dyDescent="0.3">
       <c r="A197" t="s">
         <v>39</v>
       </c>
@@ -11428,7 +11428,7 @@
         <v>72</v>
       </c>
     </row>
-    <row r="198" spans="1:16" hidden="1" x14ac:dyDescent="0.3">
+    <row r="198" spans="1:16" x14ac:dyDescent="0.3">
       <c r="A198" t="s">
         <v>40</v>
       </c>
@@ -11481,7 +11481,7 @@
         <v>1096</v>
       </c>
     </row>
-    <row r="199" spans="1:16" hidden="1" x14ac:dyDescent="0.3">
+    <row r="199" spans="1:16" x14ac:dyDescent="0.3">
       <c r="A199" t="s">
         <v>41</v>
       </c>
@@ -11534,7 +11534,7 @@
         <v>174</v>
       </c>
     </row>
-    <row r="200" spans="1:16" hidden="1" x14ac:dyDescent="0.3">
+    <row r="200" spans="1:16" x14ac:dyDescent="0.3">
       <c r="A200" t="s">
         <v>42</v>
       </c>
@@ -11587,7 +11587,7 @@
         <v>315</v>
       </c>
     </row>
-    <row r="201" spans="1:16" hidden="1" x14ac:dyDescent="0.3">
+    <row r="201" spans="1:16" x14ac:dyDescent="0.3">
       <c r="A201" t="s">
         <v>43</v>
       </c>
@@ -11640,7 +11640,7 @@
         <v>16538</v>
       </c>
     </row>
-    <row r="202" spans="1:16" hidden="1" x14ac:dyDescent="0.3">
+    <row r="202" spans="1:16" x14ac:dyDescent="0.3">
       <c r="A202" t="s">
         <v>44</v>
       </c>
@@ -11693,7 +11693,7 @@
         <v>5431</v>
       </c>
     </row>
-    <row r="203" spans="1:16" hidden="1" x14ac:dyDescent="0.3">
+    <row r="203" spans="1:16" x14ac:dyDescent="0.3">
       <c r="A203" t="s">
         <v>45</v>
       </c>
@@ -11746,7 +11746,7 @@
         <v>3581</v>
       </c>
     </row>
-    <row r="204" spans="1:16" hidden="1" x14ac:dyDescent="0.3">
+    <row r="204" spans="1:16" x14ac:dyDescent="0.3">
       <c r="A204" t="s">
         <v>46</v>
       </c>
@@ -11799,7 +11799,7 @@
         <v>1497</v>
       </c>
     </row>
-    <row r="205" spans="1:16" hidden="1" x14ac:dyDescent="0.3">
+    <row r="205" spans="1:16" x14ac:dyDescent="0.3">
       <c r="A205" t="s">
         <v>47</v>
       </c>
@@ -11852,7 +11852,7 @@
         <v>757</v>
       </c>
     </row>
-    <row r="206" spans="1:16" hidden="1" x14ac:dyDescent="0.3">
+    <row r="206" spans="1:16" x14ac:dyDescent="0.3">
       <c r="A206" t="s">
         <v>48</v>
       </c>
@@ -11905,7 +11905,7 @@
         <v>6121</v>
       </c>
     </row>
-    <row r="207" spans="1:16" hidden="1" x14ac:dyDescent="0.3">
+    <row r="207" spans="1:16" x14ac:dyDescent="0.3">
       <c r="A207" t="s">
         <v>49</v>
       </c>
@@ -11958,7 +11958,7 @@
         <v>297</v>
       </c>
     </row>
-    <row r="208" spans="1:16" hidden="1" x14ac:dyDescent="0.3">
+    <row r="208" spans="1:16" x14ac:dyDescent="0.3">
       <c r="A208" t="s">
         <v>50</v>
       </c>
@@ -12011,7 +12011,7 @@
         <v>526</v>
       </c>
     </row>
-    <row r="209" spans="1:16" s="1" customFormat="1" hidden="1" x14ac:dyDescent="0.3">
+    <row r="209" spans="1:16" s="1" customFormat="1" x14ac:dyDescent="0.3">
       <c r="A209" s="1" t="s">
         <v>63</v>
       </c>
@@ -14874,21 +14874,21 @@
         <v>11950</v>
       </c>
       <c r="K262" s="11">
-        <f t="shared" ref="K262:K313" si="25">J262/F262</f>
+        <f t="shared" ref="K262:K325" si="25">J262/F262</f>
         <v>0.38909872362594428</v>
       </c>
       <c r="L262">
         <v>2325</v>
       </c>
       <c r="M262" s="11">
-        <f t="shared" ref="M262:M313" si="26">L262/J262</f>
+        <f t="shared" ref="M262:M312" si="26">L262/J262</f>
         <v>0.19456066945606695</v>
       </c>
       <c r="N262">
         <v>9625</v>
       </c>
       <c r="O262" s="14">
-        <f t="shared" ref="O262:O313" si="27">N262/J262</f>
+        <f t="shared" ref="O262:O312" si="27">N262/J262</f>
         <v>0.80543933054393302</v>
       </c>
       <c r="P262">
@@ -17553,35 +17553,35 @@
         <v>46143</v>
       </c>
       <c r="C313" s="1">
-        <f>SUM(C262:C312)</f>
+        <f t="shared" ref="C313:J313" si="28">SUM(C262:C312)</f>
         <v>66388522</v>
       </c>
       <c r="D313" s="1">
-        <f>SUM(D262:D312)</f>
+        <f t="shared" si="28"/>
         <v>38307835</v>
       </c>
       <c r="E313" s="1">
-        <f>SUM(E262:E312)</f>
+        <f t="shared" si="28"/>
         <v>5651661</v>
       </c>
       <c r="F313" s="1">
-        <f>SUM(F262:F312)</f>
+        <f t="shared" si="28"/>
         <v>5657983</v>
       </c>
       <c r="G313" s="1">
-        <f>SUM(G262:G312)</f>
+        <f t="shared" si="28"/>
         <v>3840100</v>
       </c>
       <c r="H313" s="1">
-        <f>SUM(H262:H312)</f>
+        <f t="shared" si="28"/>
         <v>2698346</v>
       </c>
       <c r="I313" s="1">
-        <f>SUM(I262:I312)</f>
+        <f t="shared" si="28"/>
         <v>1141754</v>
       </c>
       <c r="J313" s="1">
-        <f>SUM(J262:J312)</f>
+        <f t="shared" si="28"/>
         <v>1099403</v>
       </c>
       <c r="K313" s="9">
@@ -17607,6 +17607,2772 @@
       <c r="P313" s="1">
         <f>SUM(P262:P312)</f>
         <v>718480</v>
+      </c>
+    </row>
+    <row r="314" spans="1:16" x14ac:dyDescent="0.3">
+      <c r="A314" t="s">
+        <v>0</v>
+      </c>
+      <c r="B314" s="3">
+        <v>46174</v>
+      </c>
+      <c r="C314">
+        <v>194353</v>
+      </c>
+      <c r="D314">
+        <v>123216</v>
+      </c>
+      <c r="E314">
+        <v>16655</v>
+      </c>
+      <c r="F314">
+        <v>15924</v>
+      </c>
+      <c r="G314">
+        <v>7158</v>
+      </c>
+      <c r="H314">
+        <v>4303</v>
+      </c>
+      <c r="I314">
+        <v>2855</v>
+      </c>
+      <c r="J314">
+        <v>5108</v>
+      </c>
+      <c r="K314" s="11">
+        <f t="shared" si="25"/>
+        <v>0.3207736749560412</v>
+      </c>
+      <c r="L314">
+        <v>1824</v>
+      </c>
+      <c r="M314" s="11">
+        <f t="shared" ref="M314:M365" si="29">L314/J314</f>
+        <v>0.35708692247454971</v>
+      </c>
+      <c r="N314">
+        <v>3284</v>
+      </c>
+      <c r="O314" s="13">
+        <f t="shared" ref="O314:O364" si="30">N314/J314</f>
+        <v>0.64291307752545024</v>
+      </c>
+      <c r="P314">
+        <v>3658</v>
+      </c>
+    </row>
+    <row r="315" spans="1:16" x14ac:dyDescent="0.3">
+      <c r="A315" t="s">
+        <v>1</v>
+      </c>
+      <c r="B315" s="3">
+        <v>46174</v>
+      </c>
+      <c r="C315">
+        <v>731936</v>
+      </c>
+      <c r="D315">
+        <v>262269</v>
+      </c>
+      <c r="E315">
+        <v>105218</v>
+      </c>
+      <c r="F315">
+        <v>105959</v>
+      </c>
+      <c r="G315">
+        <v>75532</v>
+      </c>
+      <c r="H315">
+        <v>37848</v>
+      </c>
+      <c r="I315">
+        <v>37684</v>
+      </c>
+      <c r="J315">
+        <v>28531</v>
+      </c>
+      <c r="K315" s="11">
+        <f t="shared" si="25"/>
+        <v>0.26926452684528923</v>
+      </c>
+      <c r="L315">
+        <v>12808</v>
+      </c>
+      <c r="M315" s="11">
+        <f t="shared" si="29"/>
+        <v>0.4489152150292664</v>
+      </c>
+      <c r="N315">
+        <v>15723</v>
+      </c>
+      <c r="O315" s="13">
+        <f t="shared" si="30"/>
+        <v>0.55108478497073354</v>
+      </c>
+      <c r="P315">
+        <v>1896</v>
+      </c>
+    </row>
+    <row r="316" spans="1:16" x14ac:dyDescent="0.3">
+      <c r="A316" t="s">
+        <v>2</v>
+      </c>
+      <c r="B316" s="3">
+        <v>46174</v>
+      </c>
+      <c r="C316">
+        <v>694776</v>
+      </c>
+      <c r="D316">
+        <v>375511</v>
+      </c>
+      <c r="E316">
+        <v>51197</v>
+      </c>
+      <c r="F316">
+        <v>53431</v>
+      </c>
+      <c r="G316">
+        <v>44072</v>
+      </c>
+      <c r="H316">
+        <v>38596</v>
+      </c>
+      <c r="I316">
+        <v>5476</v>
+      </c>
+      <c r="J316">
+        <v>9228</v>
+      </c>
+      <c r="K316" s="11">
+        <f t="shared" si="25"/>
+        <v>0.17270872714341862</v>
+      </c>
+      <c r="L316">
+        <v>1175</v>
+      </c>
+      <c r="M316" s="11">
+        <f t="shared" si="29"/>
+        <v>0.12732986562635457</v>
+      </c>
+      <c r="N316">
+        <v>8053</v>
+      </c>
+      <c r="O316" s="13">
+        <f t="shared" si="30"/>
+        <v>0.87267013437364538</v>
+      </c>
+      <c r="P316">
+        <v>131</v>
+      </c>
+    </row>
+    <row r="317" spans="1:16" x14ac:dyDescent="0.3">
+      <c r="A317" t="s">
+        <v>3</v>
+      </c>
+      <c r="B317" s="3">
+        <v>46174</v>
+      </c>
+      <c r="C317">
+        <v>1500834</v>
+      </c>
+      <c r="D317">
+        <v>907687</v>
+      </c>
+      <c r="E317">
+        <v>131259</v>
+      </c>
+      <c r="F317">
+        <v>98446</v>
+      </c>
+      <c r="G317">
+        <v>72126</v>
+      </c>
+      <c r="H317">
+        <v>58656</v>
+      </c>
+      <c r="I317">
+        <v>13470</v>
+      </c>
+      <c r="J317">
+        <v>22371</v>
+      </c>
+      <c r="K317" s="11">
+        <f t="shared" si="25"/>
+        <v>0.22724133027243362</v>
+      </c>
+      <c r="L317">
+        <v>16150</v>
+      </c>
+      <c r="M317" s="11">
+        <f t="shared" si="29"/>
+        <v>0.72191676724330611</v>
+      </c>
+      <c r="N317">
+        <v>6221</v>
+      </c>
+      <c r="O317" s="13">
+        <f t="shared" si="30"/>
+        <v>0.27808323275669394</v>
+      </c>
+      <c r="P317">
+        <v>3949</v>
+      </c>
+    </row>
+    <row r="318" spans="1:16" x14ac:dyDescent="0.3">
+      <c r="A318" t="s">
+        <v>4</v>
+      </c>
+      <c r="B318" s="3">
+        <v>46174</v>
+      </c>
+      <c r="C318">
+        <v>10396710</v>
+      </c>
+      <c r="D318">
+        <v>7215654</v>
+      </c>
+      <c r="E318">
+        <v>892223</v>
+      </c>
+      <c r="F318">
+        <v>901120</v>
+      </c>
+      <c r="G318">
+        <v>541675</v>
+      </c>
+      <c r="H318">
+        <v>397900</v>
+      </c>
+      <c r="I318">
+        <v>143775</v>
+      </c>
+      <c r="J318">
+        <v>157272</v>
+      </c>
+      <c r="K318" s="11">
+        <f t="shared" si="25"/>
+        <v>0.17452947443181818</v>
+      </c>
+      <c r="L318">
+        <v>14336</v>
+      </c>
+      <c r="M318" s="11">
+        <f t="shared" si="29"/>
+        <v>9.1154178747647391E-2</v>
+      </c>
+      <c r="N318">
+        <v>142936</v>
+      </c>
+      <c r="O318" s="13">
+        <f t="shared" si="30"/>
+        <v>0.90884582125235258</v>
+      </c>
+      <c r="P318">
+        <v>202173</v>
+      </c>
+    </row>
+    <row r="319" spans="1:16" x14ac:dyDescent="0.3">
+      <c r="A319" t="s">
+        <v>5</v>
+      </c>
+      <c r="B319" s="3">
+        <v>46174</v>
+      </c>
+      <c r="C319">
+        <v>1051860</v>
+      </c>
+      <c r="D319">
+        <v>662481</v>
+      </c>
+      <c r="E319">
+        <v>85193</v>
+      </c>
+      <c r="F319">
+        <v>85937</v>
+      </c>
+      <c r="G319">
+        <v>69131</v>
+      </c>
+      <c r="H319">
+        <v>52244</v>
+      </c>
+      <c r="I319">
+        <v>16887</v>
+      </c>
+      <c r="J319">
+        <v>13291</v>
+      </c>
+      <c r="K319" s="11">
+        <f t="shared" si="25"/>
+        <v>0.15465980892979742</v>
+      </c>
+      <c r="L319">
+        <v>5559</v>
+      </c>
+      <c r="M319" s="11">
+        <f t="shared" si="29"/>
+        <v>0.41825295312617561</v>
+      </c>
+      <c r="N319">
+        <v>7732</v>
+      </c>
+      <c r="O319" s="13">
+        <f t="shared" si="30"/>
+        <v>0.58174704687382439</v>
+      </c>
+      <c r="P319">
+        <v>3515</v>
+      </c>
+    </row>
+    <row r="320" spans="1:16" x14ac:dyDescent="0.3">
+      <c r="A320" t="s">
+        <v>6</v>
+      </c>
+      <c r="B320" s="3">
+        <v>46174</v>
+      </c>
+      <c r="C320">
+        <v>870026</v>
+      </c>
+      <c r="D320">
+        <v>533659</v>
+      </c>
+      <c r="E320">
+        <v>97413</v>
+      </c>
+      <c r="F320">
+        <v>83450</v>
+      </c>
+      <c r="G320">
+        <v>71745</v>
+      </c>
+      <c r="H320">
+        <v>68055</v>
+      </c>
+      <c r="I320">
+        <v>3690</v>
+      </c>
+      <c r="J320">
+        <v>7542</v>
+      </c>
+      <c r="K320" s="11">
+        <f t="shared" si="25"/>
+        <v>9.0377471539844212E-2</v>
+      </c>
+      <c r="L320">
+        <v>3941</v>
+      </c>
+      <c r="M320" s="11">
+        <f t="shared" si="29"/>
+        <v>0.522540440201538</v>
+      </c>
+      <c r="N320">
+        <v>3601</v>
+      </c>
+      <c r="O320" s="13">
+        <f t="shared" si="30"/>
+        <v>0.47745955979846194</v>
+      </c>
+      <c r="P320">
+        <v>4163</v>
+      </c>
+    </row>
+    <row r="321" spans="1:16" x14ac:dyDescent="0.3">
+      <c r="A321" t="s">
+        <v>7</v>
+      </c>
+      <c r="B321" s="3">
+        <v>46174</v>
+      </c>
+      <c r="C321">
+        <v>221470</v>
+      </c>
+      <c r="D321">
+        <v>144819</v>
+      </c>
+      <c r="E321">
+        <v>19437</v>
+      </c>
+      <c r="F321">
+        <v>16766</v>
+      </c>
+      <c r="G321">
+        <v>12639</v>
+      </c>
+      <c r="H321">
+        <v>11816</v>
+      </c>
+      <c r="I321">
+        <v>823</v>
+      </c>
+      <c r="J321">
+        <v>2590</v>
+      </c>
+      <c r="K321" s="11">
+        <f t="shared" si="25"/>
+        <v>0.15447930335202195</v>
+      </c>
+      <c r="L321">
+        <v>145</v>
+      </c>
+      <c r="M321" s="11">
+        <f t="shared" si="29"/>
+        <v>5.5984555984555984E-2</v>
+      </c>
+      <c r="N321">
+        <v>2445</v>
+      </c>
+      <c r="O321" s="13">
+        <f t="shared" si="30"/>
+        <v>0.94401544401544402</v>
+      </c>
+      <c r="P321">
+        <v>1537</v>
+      </c>
+    </row>
+    <row r="322" spans="1:16" x14ac:dyDescent="0.3">
+      <c r="A322" t="s">
+        <v>8</v>
+      </c>
+      <c r="B322" s="3">
+        <v>46174</v>
+      </c>
+      <c r="C322">
+        <v>221175</v>
+      </c>
+      <c r="D322">
+        <v>130875</v>
+      </c>
+      <c r="E322">
+        <v>15994</v>
+      </c>
+      <c r="F322">
+        <v>15157</v>
+      </c>
+      <c r="G322">
+        <v>9256</v>
+      </c>
+      <c r="H322">
+        <v>5501</v>
+      </c>
+      <c r="I322">
+        <v>3755</v>
+      </c>
+      <c r="J322">
+        <v>5403</v>
+      </c>
+      <c r="K322" s="11">
+        <f t="shared" si="25"/>
+        <v>0.35646895823711816</v>
+      </c>
+      <c r="L322">
+        <v>1568</v>
+      </c>
+      <c r="M322" s="11">
+        <f t="shared" si="29"/>
+        <v>0.29020914306866558</v>
+      </c>
+      <c r="N322">
+        <v>3835</v>
+      </c>
+      <c r="O322" s="13">
+        <f t="shared" si="30"/>
+        <v>0.70979085693133448</v>
+      </c>
+      <c r="P322">
+        <v>498</v>
+      </c>
+    </row>
+    <row r="323" spans="1:16" x14ac:dyDescent="0.3">
+      <c r="A323" t="s">
+        <v>9</v>
+      </c>
+      <c r="B323" s="3">
+        <v>46174</v>
+      </c>
+      <c r="C323">
+        <v>3396650</v>
+      </c>
+      <c r="D323">
+        <v>1281373</v>
+      </c>
+      <c r="E323">
+        <v>161339</v>
+      </c>
+      <c r="F323">
+        <v>171927</v>
+      </c>
+      <c r="G323">
+        <v>115138</v>
+      </c>
+      <c r="H323">
+        <v>38444</v>
+      </c>
+      <c r="I323">
+        <v>76694</v>
+      </c>
+      <c r="J323">
+        <v>31707</v>
+      </c>
+      <c r="K323" s="11">
+        <f t="shared" si="25"/>
+        <v>0.18442129508454169</v>
+      </c>
+      <c r="L323">
+        <v>12983</v>
+      </c>
+      <c r="M323" s="11">
+        <f t="shared" si="29"/>
+        <v>0.4094679408332545</v>
+      </c>
+      <c r="N323">
+        <v>18724</v>
+      </c>
+      <c r="O323" s="13">
+        <f t="shared" si="30"/>
+        <v>0.59053205916674556</v>
+      </c>
+      <c r="P323">
+        <v>25082</v>
+      </c>
+    </row>
+    <row r="324" spans="1:16" x14ac:dyDescent="0.3">
+      <c r="A324" t="s">
+        <v>10</v>
+      </c>
+      <c r="B324" s="3">
+        <v>46174</v>
+      </c>
+      <c r="C324">
+        <v>1644619</v>
+      </c>
+      <c r="D324">
+        <v>545289</v>
+      </c>
+      <c r="E324">
+        <v>122390</v>
+      </c>
+      <c r="F324">
+        <v>231064</v>
+      </c>
+      <c r="G324">
+        <v>140375</v>
+      </c>
+      <c r="H324">
+        <v>103866</v>
+      </c>
+      <c r="I324">
+        <v>36509</v>
+      </c>
+      <c r="J324">
+        <v>64554</v>
+      </c>
+      <c r="K324" s="11">
+        <f t="shared" si="25"/>
+        <v>0.27937714226361526</v>
+      </c>
+      <c r="L324">
+        <v>25518</v>
+      </c>
+      <c r="M324" s="11">
+        <f t="shared" si="29"/>
+        <v>0.39529696068407844</v>
+      </c>
+      <c r="N324">
+        <v>39036</v>
+      </c>
+      <c r="O324" s="13">
+        <f t="shared" si="30"/>
+        <v>0.60470303931592151</v>
+      </c>
+      <c r="P324">
+        <v>26135</v>
+      </c>
+    </row>
+    <row r="325" spans="1:16" x14ac:dyDescent="0.3">
+      <c r="A325" t="s">
+        <v>11</v>
+      </c>
+      <c r="B325" s="3">
+        <v>46174</v>
+      </c>
+      <c r="C325">
+        <v>365106</v>
+      </c>
+      <c r="D325">
+        <v>236198</v>
+      </c>
+      <c r="E325">
+        <v>35319</v>
+      </c>
+      <c r="F325">
+        <v>36142</v>
+      </c>
+      <c r="G325">
+        <v>31838</v>
+      </c>
+      <c r="H325">
+        <v>26918</v>
+      </c>
+      <c r="I325">
+        <v>4920</v>
+      </c>
+      <c r="J325">
+        <v>3289</v>
+      </c>
+      <c r="K325" s="11">
+        <f t="shared" si="25"/>
+        <v>9.1002158153948312E-2</v>
+      </c>
+      <c r="L325">
+        <v>587</v>
+      </c>
+      <c r="M325" s="11">
+        <f t="shared" si="29"/>
+        <v>0.17847370021283065</v>
+      </c>
+      <c r="N325">
+        <v>2702</v>
+      </c>
+      <c r="O325" s="13">
+        <f t="shared" si="30"/>
+        <v>0.8215262997871694</v>
+      </c>
+      <c r="P325">
+        <v>1015</v>
+      </c>
+    </row>
+    <row r="326" spans="1:16" x14ac:dyDescent="0.3">
+      <c r="A326" t="s">
+        <v>12</v>
+      </c>
+      <c r="B326" s="3">
+        <v>46174</v>
+      </c>
+      <c r="C326">
+        <v>592144</v>
+      </c>
+      <c r="D326">
+        <v>342528</v>
+      </c>
+      <c r="E326">
+        <v>61190</v>
+      </c>
+      <c r="F326">
+        <v>50176</v>
+      </c>
+      <c r="G326">
+        <v>40740</v>
+      </c>
+      <c r="H326">
+        <v>29594</v>
+      </c>
+      <c r="I326">
+        <v>11146</v>
+      </c>
+      <c r="J326">
+        <v>6917</v>
+      </c>
+      <c r="K326" s="11">
+        <f t="shared" ref="K326:K364" si="31">J326/F326</f>
+        <v>0.1378547512755102</v>
+      </c>
+      <c r="L326">
+        <v>1337</v>
+      </c>
+      <c r="M326" s="11">
+        <f t="shared" si="29"/>
+        <v>0.19329188954749169</v>
+      </c>
+      <c r="N326">
+        <v>5580</v>
+      </c>
+      <c r="O326" s="13">
+        <f t="shared" si="30"/>
+        <v>0.80670811045250834</v>
+      </c>
+      <c r="P326">
+        <v>2519</v>
+      </c>
+    </row>
+    <row r="327" spans="1:16" x14ac:dyDescent="0.3">
+      <c r="A327" t="s">
+        <v>13</v>
+      </c>
+      <c r="B327" s="3">
+        <v>46174</v>
+      </c>
+      <c r="C327">
+        <v>287984</v>
+      </c>
+      <c r="D327">
+        <v>158547</v>
+      </c>
+      <c r="E327">
+        <v>20145</v>
+      </c>
+      <c r="F327">
+        <v>19476</v>
+      </c>
+      <c r="G327">
+        <v>14129</v>
+      </c>
+      <c r="H327">
+        <v>9870</v>
+      </c>
+      <c r="I327">
+        <v>4259</v>
+      </c>
+      <c r="J327">
+        <v>5220</v>
+      </c>
+      <c r="K327" s="11">
+        <f t="shared" si="31"/>
+        <v>0.26802218114602588</v>
+      </c>
+      <c r="L327">
+        <v>1013</v>
+      </c>
+      <c r="M327" s="11">
+        <f t="shared" si="29"/>
+        <v>0.19406130268199234</v>
+      </c>
+      <c r="N327">
+        <v>4207</v>
+      </c>
+      <c r="O327" s="13">
+        <f t="shared" si="30"/>
+        <v>0.80593869731800771</v>
+      </c>
+      <c r="P327">
+        <v>127</v>
+      </c>
+    </row>
+    <row r="328" spans="1:16" x14ac:dyDescent="0.3">
+      <c r="A328" t="s">
+        <v>14</v>
+      </c>
+      <c r="B328" s="3">
+        <v>46174</v>
+      </c>
+      <c r="C328">
+        <v>2566240</v>
+      </c>
+      <c r="D328">
+        <v>1614595</v>
+      </c>
+      <c r="E328">
+        <v>240527</v>
+      </c>
+      <c r="F328">
+        <v>201287</v>
+      </c>
+      <c r="G328">
+        <v>161809</v>
+      </c>
+      <c r="H328">
+        <v>132556</v>
+      </c>
+      <c r="I328">
+        <v>29253</v>
+      </c>
+      <c r="J328">
+        <v>21457</v>
+      </c>
+      <c r="K328" s="11">
+        <f t="shared" si="31"/>
+        <v>0.10659903520843372</v>
+      </c>
+      <c r="L328">
+        <v>4500</v>
+      </c>
+      <c r="M328" s="11">
+        <f t="shared" si="29"/>
+        <v>0.20972176911963461</v>
+      </c>
+      <c r="N328">
+        <v>16957</v>
+      </c>
+      <c r="O328" s="13">
+        <f t="shared" si="30"/>
+        <v>0.79027823088036542</v>
+      </c>
+      <c r="P328">
+        <v>18021</v>
+      </c>
+    </row>
+    <row r="329" spans="1:16" x14ac:dyDescent="0.3">
+      <c r="A329" t="s">
+        <v>15</v>
+      </c>
+      <c r="B329" s="3">
+        <v>46174</v>
+      </c>
+      <c r="C329">
+        <v>1242736</v>
+      </c>
+      <c r="D329">
+        <v>714773</v>
+      </c>
+      <c r="E329">
+        <v>104753</v>
+      </c>
+      <c r="F329">
+        <v>110131</v>
+      </c>
+      <c r="G329">
+        <v>23529</v>
+      </c>
+      <c r="H329">
+        <v>8481</v>
+      </c>
+      <c r="I329">
+        <v>15048</v>
+      </c>
+      <c r="J329">
+        <v>49216</v>
+      </c>
+      <c r="K329" s="11">
+        <f t="shared" si="31"/>
+        <v>0.44688598124052265</v>
+      </c>
+      <c r="L329">
+        <v>1269</v>
+      </c>
+      <c r="M329" s="11">
+        <f t="shared" si="29"/>
+        <v>2.5784297789336802E-2</v>
+      </c>
+      <c r="N329">
+        <v>47947</v>
+      </c>
+      <c r="O329" s="13">
+        <f t="shared" si="30"/>
+        <v>0.97421570221066323</v>
+      </c>
+      <c r="P329">
+        <v>37386</v>
+      </c>
+    </row>
+    <row r="330" spans="1:16" x14ac:dyDescent="0.3">
+      <c r="A330" t="s">
+        <v>16</v>
+      </c>
+      <c r="B330" s="3">
+        <v>46174</v>
+      </c>
+      <c r="C330">
+        <v>323066</v>
+      </c>
+      <c r="D330">
+        <v>120047</v>
+      </c>
+      <c r="E330">
+        <v>32450</v>
+      </c>
+      <c r="F330">
+        <v>40362</v>
+      </c>
+      <c r="G330">
+        <v>32897</v>
+      </c>
+      <c r="H330">
+        <v>19188</v>
+      </c>
+      <c r="I330">
+        <v>13709</v>
+      </c>
+      <c r="J330">
+        <v>6213</v>
+      </c>
+      <c r="K330" s="11">
+        <f t="shared" si="31"/>
+        <v>0.1539319161587632</v>
+      </c>
+      <c r="L330">
+        <v>3742</v>
+      </c>
+      <c r="M330" s="11">
+        <f t="shared" si="29"/>
+        <v>0.60228553033961052</v>
+      </c>
+      <c r="N330">
+        <v>2471</v>
+      </c>
+      <c r="O330" s="13">
+        <f t="shared" si="30"/>
+        <v>0.39771446966038948</v>
+      </c>
+      <c r="P330">
+        <v>1252</v>
+      </c>
+    </row>
+    <row r="331" spans="1:16" x14ac:dyDescent="0.3">
+      <c r="A331" t="s">
+        <v>17</v>
+      </c>
+      <c r="B331" s="3">
+        <v>46174</v>
+      </c>
+      <c r="C331">
+        <v>1147774</v>
+      </c>
+      <c r="D331">
+        <v>714608</v>
+      </c>
+      <c r="E331">
+        <v>51576</v>
+      </c>
+      <c r="F331">
+        <v>56235</v>
+      </c>
+      <c r="G331">
+        <v>50982</v>
+      </c>
+      <c r="H331">
+        <v>47629</v>
+      </c>
+      <c r="I331">
+        <v>3353</v>
+      </c>
+      <c r="J331">
+        <v>4998</v>
+      </c>
+      <c r="K331" s="11">
+        <f t="shared" si="31"/>
+        <v>8.8877033875700187E-2</v>
+      </c>
+      <c r="L331">
+        <v>1156</v>
+      </c>
+      <c r="M331" s="11">
+        <f t="shared" si="29"/>
+        <v>0.23129251700680273</v>
+      </c>
+      <c r="N331">
+        <v>3842</v>
+      </c>
+      <c r="O331" s="13">
+        <f t="shared" si="30"/>
+        <v>0.76870748299319724</v>
+      </c>
+      <c r="P331">
+        <v>255</v>
+      </c>
+    </row>
+    <row r="332" spans="1:16" x14ac:dyDescent="0.3">
+      <c r="A332" t="s">
+        <v>18</v>
+      </c>
+      <c r="B332" s="3">
+        <v>46174</v>
+      </c>
+      <c r="C332">
+        <v>1136776</v>
+      </c>
+      <c r="D332">
+        <v>631261</v>
+      </c>
+      <c r="E332">
+        <v>92620</v>
+      </c>
+      <c r="F332">
+        <v>96868</v>
+      </c>
+      <c r="G332">
+        <v>58729</v>
+      </c>
+      <c r="H332">
+        <v>40381</v>
+      </c>
+      <c r="I332">
+        <v>18348</v>
+      </c>
+      <c r="J332">
+        <v>22605</v>
+      </c>
+      <c r="K332" s="11">
+        <f t="shared" si="31"/>
+        <v>0.23335879753891894</v>
+      </c>
+      <c r="L332">
+        <v>2896</v>
+      </c>
+      <c r="M332" s="11">
+        <f t="shared" si="29"/>
+        <v>0.12811324928113249</v>
+      </c>
+      <c r="N332">
+        <v>19709</v>
+      </c>
+      <c r="O332" s="13">
+        <f t="shared" si="30"/>
+        <v>0.87188675071886745</v>
+      </c>
+      <c r="P332">
+        <v>15534</v>
+      </c>
+    </row>
+    <row r="333" spans="1:16" x14ac:dyDescent="0.3">
+      <c r="A333" t="s">
+        <v>19</v>
+      </c>
+      <c r="B333" s="3">
+        <v>46174</v>
+      </c>
+      <c r="C333">
+        <v>1352133</v>
+      </c>
+      <c r="D333">
+        <v>868179</v>
+      </c>
+      <c r="E333">
+        <v>73656</v>
+      </c>
+      <c r="F333">
+        <v>72366</v>
+      </c>
+      <c r="G333">
+        <v>58019</v>
+      </c>
+      <c r="H333">
+        <v>45670</v>
+      </c>
+      <c r="I333">
+        <v>12349</v>
+      </c>
+      <c r="J333">
+        <v>12417</v>
+      </c>
+      <c r="K333" s="11">
+        <f t="shared" si="31"/>
+        <v>0.17158610397147833</v>
+      </c>
+      <c r="L333">
+        <v>3151</v>
+      </c>
+      <c r="M333" s="11">
+        <f t="shared" si="29"/>
+        <v>0.25376499959732624</v>
+      </c>
+      <c r="N333">
+        <v>9266</v>
+      </c>
+      <c r="O333" s="13">
+        <f t="shared" si="30"/>
+        <v>0.74623500040267376</v>
+      </c>
+      <c r="P333">
+        <v>1930</v>
+      </c>
+    </row>
+    <row r="334" spans="1:16" x14ac:dyDescent="0.3">
+      <c r="A334" t="s">
+        <v>20</v>
+      </c>
+      <c r="B334" s="3">
+        <v>46174</v>
+      </c>
+      <c r="C334">
+        <v>1187872</v>
+      </c>
+      <c r="D334">
+        <v>721028</v>
+      </c>
+      <c r="E334">
+        <v>103208</v>
+      </c>
+      <c r="F334">
+        <v>99593</v>
+      </c>
+      <c r="G334">
+        <v>71697</v>
+      </c>
+      <c r="H334">
+        <v>55389</v>
+      </c>
+      <c r="I334">
+        <v>16308</v>
+      </c>
+      <c r="J334">
+        <v>24505</v>
+      </c>
+      <c r="K334" s="11">
+        <f t="shared" si="31"/>
+        <v>0.24605142931732149</v>
+      </c>
+      <c r="L334">
+        <v>2896</v>
+      </c>
+      <c r="M334" s="11">
+        <f t="shared" si="29"/>
+        <v>0.11817996327280147</v>
+      </c>
+      <c r="N334">
+        <v>21609</v>
+      </c>
+      <c r="O334" s="13">
+        <f t="shared" si="30"/>
+        <v>0.88182003672719855</v>
+      </c>
+      <c r="P334">
+        <v>3391</v>
+      </c>
+    </row>
+    <row r="335" spans="1:16" x14ac:dyDescent="0.3">
+      <c r="A335" t="s">
+        <v>21</v>
+      </c>
+      <c r="B335" s="3">
+        <v>46174</v>
+      </c>
+      <c r="C335">
+        <v>308056</v>
+      </c>
+      <c r="D335">
+        <v>190437</v>
+      </c>
+      <c r="E335">
+        <v>34006</v>
+      </c>
+      <c r="F335">
+        <v>24181</v>
+      </c>
+      <c r="G335">
+        <v>19378</v>
+      </c>
+      <c r="H335">
+        <v>18657</v>
+      </c>
+      <c r="I335">
+        <v>721</v>
+      </c>
+      <c r="J335">
+        <v>1881</v>
+      </c>
+      <c r="K335" s="11">
+        <f t="shared" si="31"/>
+        <v>7.7788346222240595E-2</v>
+      </c>
+      <c r="L335">
+        <v>281</v>
+      </c>
+      <c r="M335" s="11">
+        <f t="shared" si="29"/>
+        <v>0.1493886230728336</v>
+      </c>
+      <c r="N335">
+        <v>1600</v>
+      </c>
+      <c r="O335" s="13">
+        <f t="shared" si="30"/>
+        <v>0.85061137692716637</v>
+      </c>
+      <c r="P335">
+        <v>2922</v>
+      </c>
+    </row>
+    <row r="336" spans="1:16" x14ac:dyDescent="0.3">
+      <c r="A336" t="s">
+        <v>22</v>
+      </c>
+      <c r="B336" s="3">
+        <v>46174</v>
+      </c>
+      <c r="C336">
+        <v>1969218</v>
+      </c>
+      <c r="D336">
+        <v>1265592</v>
+      </c>
+      <c r="E336">
+        <v>183390</v>
+      </c>
+      <c r="F336">
+        <v>171546</v>
+      </c>
+      <c r="G336">
+        <v>133113</v>
+      </c>
+      <c r="H336">
+        <v>104735</v>
+      </c>
+      <c r="I336">
+        <v>28378</v>
+      </c>
+      <c r="J336">
+        <v>29296</v>
+      </c>
+      <c r="K336" s="11">
+        <f t="shared" si="31"/>
+        <v>0.17077635153253354</v>
+      </c>
+      <c r="L336">
+        <v>2934</v>
+      </c>
+      <c r="M336" s="11">
+        <f t="shared" si="29"/>
+        <v>0.10015019115237575</v>
+      </c>
+      <c r="N336">
+        <v>26362</v>
+      </c>
+      <c r="O336" s="13">
+        <f t="shared" si="30"/>
+        <v>0.89984980884762422</v>
+      </c>
+      <c r="P336">
+        <v>9137</v>
+      </c>
+    </row>
+    <row r="337" spans="1:16" x14ac:dyDescent="0.3">
+      <c r="A337" t="s">
+        <v>23</v>
+      </c>
+      <c r="B337" s="3">
+        <v>46174</v>
+      </c>
+      <c r="C337">
+        <v>1124825</v>
+      </c>
+      <c r="D337">
+        <v>535429</v>
+      </c>
+      <c r="E337">
+        <v>73956</v>
+      </c>
+      <c r="F337">
+        <v>78765</v>
+      </c>
+      <c r="G337">
+        <v>66680</v>
+      </c>
+      <c r="H337">
+        <v>57905</v>
+      </c>
+      <c r="I337">
+        <v>8775</v>
+      </c>
+      <c r="J337">
+        <v>12085</v>
+      </c>
+      <c r="K337" s="11">
+        <f t="shared" si="31"/>
+        <v>0.1534310924903193</v>
+      </c>
+      <c r="L337">
+        <v>1827</v>
+      </c>
+      <c r="M337" s="11">
+        <f t="shared" si="29"/>
+        <v>0.151179147703765</v>
+      </c>
+      <c r="N337">
+        <v>10258</v>
+      </c>
+      <c r="O337" s="13">
+        <f t="shared" si="30"/>
+        <v>0.84882085229623505</v>
+      </c>
+      <c r="P337">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="338" spans="1:16" x14ac:dyDescent="0.3">
+      <c r="A338" t="s">
+        <v>24</v>
+      </c>
+      <c r="B338" s="3">
+        <v>46174</v>
+      </c>
+      <c r="C338">
+        <v>1107992</v>
+      </c>
+      <c r="D338">
+        <v>677490</v>
+      </c>
+      <c r="E338">
+        <v>93507</v>
+      </c>
+      <c r="F338">
+        <v>85970</v>
+      </c>
+      <c r="G338">
+        <v>60771</v>
+      </c>
+      <c r="H338">
+        <v>48024</v>
+      </c>
+      <c r="I338">
+        <v>12747</v>
+      </c>
+      <c r="J338">
+        <v>16382</v>
+      </c>
+      <c r="K338" s="11">
+        <f t="shared" si="31"/>
+        <v>0.19055484471327208</v>
+      </c>
+      <c r="L338">
+        <v>1794</v>
+      </c>
+      <c r="M338" s="11">
+        <f t="shared" si="29"/>
+        <v>0.10951043828592358</v>
+      </c>
+      <c r="N338">
+        <v>14588</v>
+      </c>
+      <c r="O338" s="13">
+        <f t="shared" si="30"/>
+        <v>0.89048956171407645</v>
+      </c>
+      <c r="P338">
+        <v>8817</v>
+      </c>
+    </row>
+    <row r="339" spans="1:16" x14ac:dyDescent="0.3">
+      <c r="A339" t="s">
+        <v>25</v>
+      </c>
+      <c r="B339" s="3">
+        <v>46174</v>
+      </c>
+      <c r="C339">
+        <v>500660</v>
+      </c>
+      <c r="D339">
+        <v>195623</v>
+      </c>
+      <c r="E339">
+        <v>43686</v>
+      </c>
+      <c r="F339">
+        <v>51701</v>
+      </c>
+      <c r="G339">
+        <v>44845</v>
+      </c>
+      <c r="H339">
+        <v>22380</v>
+      </c>
+      <c r="I339">
+        <v>22465</v>
+      </c>
+      <c r="J339">
+        <v>6822</v>
+      </c>
+      <c r="K339" s="11">
+        <f t="shared" si="31"/>
+        <v>0.13195102609233864</v>
+      </c>
+      <c r="L339">
+        <v>1296</v>
+      </c>
+      <c r="M339" s="11">
+        <f t="shared" si="29"/>
+        <v>0.18997361477572558</v>
+      </c>
+      <c r="N339">
+        <v>5526</v>
+      </c>
+      <c r="O339" s="13">
+        <f t="shared" si="30"/>
+        <v>0.81002638522427439</v>
+      </c>
+      <c r="P339">
+        <v>34</v>
+      </c>
+    </row>
+    <row r="340" spans="1:16" x14ac:dyDescent="0.3">
+      <c r="A340" t="s">
+        <v>26</v>
+      </c>
+      <c r="B340" s="3">
+        <v>46174</v>
+      </c>
+      <c r="C340">
+        <v>184685</v>
+      </c>
+      <c r="D340">
+        <v>116181</v>
+      </c>
+      <c r="E340">
+        <v>12806</v>
+      </c>
+      <c r="F340">
+        <v>11225</v>
+      </c>
+      <c r="G340">
+        <v>5877</v>
+      </c>
+      <c r="H340">
+        <v>4447</v>
+      </c>
+      <c r="I340">
+        <v>1430</v>
+      </c>
+      <c r="J340">
+        <v>2193</v>
+      </c>
+      <c r="K340" s="11">
+        <f t="shared" si="31"/>
+        <v>0.19536748329621381</v>
+      </c>
+      <c r="L340">
+        <v>588</v>
+      </c>
+      <c r="M340" s="11">
+        <f t="shared" si="29"/>
+        <v>0.26812585499316005</v>
+      </c>
+      <c r="N340">
+        <v>1605</v>
+      </c>
+      <c r="O340" s="13">
+        <f t="shared" si="30"/>
+        <v>0.73187414500683989</v>
+      </c>
+      <c r="P340">
+        <v>3155</v>
+      </c>
+    </row>
+    <row r="341" spans="1:16" x14ac:dyDescent="0.3">
+      <c r="A341" t="s">
+        <v>27</v>
+      </c>
+      <c r="B341" s="3">
+        <v>46174</v>
+      </c>
+      <c r="C341">
+        <v>2461148</v>
+      </c>
+      <c r="D341">
+        <v>1453281</v>
+      </c>
+      <c r="E341">
+        <v>211040</v>
+      </c>
+      <c r="F341">
+        <v>241394</v>
+      </c>
+      <c r="G341">
+        <v>133072</v>
+      </c>
+      <c r="H341">
+        <v>131979</v>
+      </c>
+      <c r="I341">
+        <v>1093</v>
+      </c>
+      <c r="J341">
+        <v>17721</v>
+      </c>
+      <c r="K341" s="11">
+        <f t="shared" si="31"/>
+        <v>7.3411103838537828E-2</v>
+      </c>
+      <c r="L341">
+        <v>6763</v>
+      </c>
+      <c r="M341" s="11">
+        <f t="shared" si="29"/>
+        <v>0.38163760510129224</v>
+      </c>
+      <c r="N341">
+        <v>10958</v>
+      </c>
+      <c r="O341" s="13">
+        <f t="shared" si="30"/>
+        <v>0.6183623948987077</v>
+      </c>
+      <c r="P341">
+        <v>90601</v>
+      </c>
+    </row>
+    <row r="342" spans="1:16" x14ac:dyDescent="0.3">
+      <c r="A342" t="s">
+        <v>28</v>
+      </c>
+      <c r="B342" s="3">
+        <v>46174</v>
+      </c>
+      <c r="C342">
+        <v>98789</v>
+      </c>
+      <c r="D342">
+        <v>53441</v>
+      </c>
+      <c r="E342">
+        <v>8598</v>
+      </c>
+      <c r="F342">
+        <v>9175</v>
+      </c>
+      <c r="G342">
+        <v>6335</v>
+      </c>
+      <c r="H342">
+        <v>3382</v>
+      </c>
+      <c r="I342">
+        <v>2953</v>
+      </c>
+      <c r="J342">
+        <v>2160</v>
+      </c>
+      <c r="K342" s="11">
+        <f t="shared" si="31"/>
+        <v>0.23542234332425069</v>
+      </c>
+      <c r="L342">
+        <v>811</v>
+      </c>
+      <c r="M342" s="11">
+        <f t="shared" si="29"/>
+        <v>0.37546296296296294</v>
+      </c>
+      <c r="N342">
+        <v>1349</v>
+      </c>
+      <c r="O342" s="13">
+        <f t="shared" si="30"/>
+        <v>0.624537037037037</v>
+      </c>
+      <c r="P342">
+        <v>680</v>
+      </c>
+    </row>
+    <row r="343" spans="1:16" x14ac:dyDescent="0.3">
+      <c r="A343" t="s">
+        <v>29</v>
+      </c>
+      <c r="B343" s="3">
+        <v>46174</v>
+      </c>
+      <c r="C343">
+        <v>293464</v>
+      </c>
+      <c r="D343">
+        <v>160805</v>
+      </c>
+      <c r="E343">
+        <v>24757</v>
+      </c>
+      <c r="F343">
+        <v>26789</v>
+      </c>
+      <c r="G343">
+        <v>18792</v>
+      </c>
+      <c r="H343">
+        <v>16532</v>
+      </c>
+      <c r="I343">
+        <v>2260</v>
+      </c>
+      <c r="J343">
+        <v>4675</v>
+      </c>
+      <c r="K343" s="11">
+        <f t="shared" si="31"/>
+        <v>0.17451192653701145</v>
+      </c>
+      <c r="L343">
+        <v>2464</v>
+      </c>
+      <c r="M343" s="11">
+        <f t="shared" si="29"/>
+        <v>0.5270588235294118</v>
+      </c>
+      <c r="N343">
+        <v>2211</v>
+      </c>
+      <c r="O343" s="13">
+        <f t="shared" si="30"/>
+        <v>0.47294117647058825</v>
+      </c>
+      <c r="P343">
+        <v>3322</v>
+      </c>
+    </row>
+    <row r="344" spans="1:16" x14ac:dyDescent="0.3">
+      <c r="A344" t="s">
+        <v>30</v>
+      </c>
+      <c r="B344" s="3">
+        <v>46174</v>
+      </c>
+      <c r="C344">
+        <v>148981</v>
+      </c>
+      <c r="D344">
+        <v>83647</v>
+      </c>
+      <c r="E344">
+        <v>9866</v>
+      </c>
+      <c r="F344">
+        <v>11656</v>
+      </c>
+      <c r="G344">
+        <v>7396</v>
+      </c>
+      <c r="H344">
+        <v>4089</v>
+      </c>
+      <c r="I344">
+        <v>3307</v>
+      </c>
+      <c r="J344">
+        <v>3384</v>
+      </c>
+      <c r="K344" s="11">
+        <f t="shared" si="31"/>
+        <v>0.29032258064516131</v>
+      </c>
+      <c r="L344">
+        <v>517</v>
+      </c>
+      <c r="M344" s="11">
+        <f t="shared" si="29"/>
+        <v>0.15277777777777779</v>
+      </c>
+      <c r="N344">
+        <v>2867</v>
+      </c>
+      <c r="O344" s="13">
+        <f t="shared" si="30"/>
+        <v>0.84722222222222221</v>
+      </c>
+      <c r="P344">
+        <v>876</v>
+      </c>
+    </row>
+    <row r="345" spans="1:16" x14ac:dyDescent="0.3">
+      <c r="A345" t="s">
+        <v>31</v>
+      </c>
+      <c r="B345" s="3">
+        <v>46174</v>
+      </c>
+      <c r="C345">
+        <v>1463549</v>
+      </c>
+      <c r="D345">
+        <v>926234</v>
+      </c>
+      <c r="E345">
+        <v>135064</v>
+      </c>
+      <c r="F345">
+        <v>129916</v>
+      </c>
+      <c r="G345">
+        <v>65899</v>
+      </c>
+      <c r="H345">
+        <v>50294</v>
+      </c>
+      <c r="I345">
+        <v>15605</v>
+      </c>
+      <c r="J345">
+        <v>11658</v>
+      </c>
+      <c r="K345" s="11">
+        <f t="shared" si="31"/>
+        <v>8.9734905631331019E-2</v>
+      </c>
+      <c r="L345">
+        <v>5196</v>
+      </c>
+      <c r="M345" s="11">
+        <f t="shared" si="29"/>
+        <v>0.44570252187339165</v>
+      </c>
+      <c r="N345">
+        <v>6462</v>
+      </c>
+      <c r="O345" s="13">
+        <f t="shared" si="30"/>
+        <v>0.55429747812660835</v>
+      </c>
+      <c r="P345">
+        <v>52359</v>
+      </c>
+    </row>
+    <row r="346" spans="1:16" x14ac:dyDescent="0.3">
+      <c r="A346" t="s">
+        <v>32</v>
+      </c>
+      <c r="B346" s="3">
+        <v>46174</v>
+      </c>
+      <c r="C346">
+        <v>630932</v>
+      </c>
+      <c r="D346">
+        <v>369108</v>
+      </c>
+      <c r="E346">
+        <v>32329</v>
+      </c>
+      <c r="F346">
+        <v>57868</v>
+      </c>
+      <c r="G346">
+        <v>47815</v>
+      </c>
+      <c r="H346">
+        <v>39089</v>
+      </c>
+      <c r="I346">
+        <v>8726</v>
+      </c>
+      <c r="J346">
+        <v>9155</v>
+      </c>
+      <c r="K346" s="11">
+        <f t="shared" si="31"/>
+        <v>0.15820488007188774</v>
+      </c>
+      <c r="L346">
+        <v>1047</v>
+      </c>
+      <c r="M346" s="11">
+        <f t="shared" si="29"/>
+        <v>0.11436373566357182</v>
+      </c>
+      <c r="N346">
+        <v>8108</v>
+      </c>
+      <c r="O346" s="13">
+        <f t="shared" si="30"/>
+        <v>0.88563626433642817</v>
+      </c>
+      <c r="P346">
+        <v>898</v>
+      </c>
+    </row>
+    <row r="347" spans="1:16" x14ac:dyDescent="0.3">
+      <c r="A347" t="s">
+        <v>33</v>
+      </c>
+      <c r="B347" s="3">
+        <v>46174</v>
+      </c>
+      <c r="C347">
+        <v>667141</v>
+      </c>
+      <c r="D347">
+        <v>402285</v>
+      </c>
+      <c r="E347">
+        <v>58164</v>
+      </c>
+      <c r="F347">
+        <v>58278</v>
+      </c>
+      <c r="G347">
+        <v>48159</v>
+      </c>
+      <c r="H347">
+        <v>46774</v>
+      </c>
+      <c r="I347">
+        <v>1385</v>
+      </c>
+      <c r="J347">
+        <v>8695</v>
+      </c>
+      <c r="K347" s="11">
+        <f t="shared" si="31"/>
+        <v>0.14919866845121657</v>
+      </c>
+      <c r="L347">
+        <v>1242</v>
+      </c>
+      <c r="M347" s="11">
+        <f t="shared" si="29"/>
+        <v>0.14284071305347901</v>
+      </c>
+      <c r="N347">
+        <v>7453</v>
+      </c>
+      <c r="O347" s="13">
+        <f t="shared" si="30"/>
+        <v>0.85715928694652099</v>
+      </c>
+      <c r="P347">
+        <v>1424</v>
+      </c>
+    </row>
+    <row r="348" spans="1:16" x14ac:dyDescent="0.3">
+      <c r="A348" t="s">
+        <v>34</v>
+      </c>
+      <c r="B348" s="3">
+        <v>46174</v>
+      </c>
+      <c r="C348">
+        <v>5725893</v>
+      </c>
+      <c r="D348">
+        <v>3953146</v>
+      </c>
+      <c r="E348">
+        <v>389059</v>
+      </c>
+      <c r="F348">
+        <v>485612</v>
+      </c>
+      <c r="G348">
+        <v>329935</v>
+      </c>
+      <c r="H348">
+        <v>148663</v>
+      </c>
+      <c r="I348">
+        <v>181272</v>
+      </c>
+      <c r="J348">
+        <v>148661</v>
+      </c>
+      <c r="K348" s="11">
+        <f t="shared" si="31"/>
+        <v>0.30613123234186962</v>
+      </c>
+      <c r="L348">
+        <v>55695</v>
+      </c>
+      <c r="M348" s="11">
+        <f t="shared" si="29"/>
+        <v>0.3746443250079039</v>
+      </c>
+      <c r="N348">
+        <v>92966</v>
+      </c>
+      <c r="O348" s="13">
+        <f t="shared" si="30"/>
+        <v>0.6253556749920961</v>
+      </c>
+      <c r="P348">
+        <v>7016</v>
+      </c>
+    </row>
+    <row r="349" spans="1:16" x14ac:dyDescent="0.3">
+      <c r="A349" t="s">
+        <v>35</v>
+      </c>
+      <c r="B349" s="3">
+        <v>46174</v>
+      </c>
+      <c r="C349">
+        <v>2371666</v>
+      </c>
+      <c r="D349">
+        <v>1493864</v>
+      </c>
+      <c r="E349">
+        <v>241437</v>
+      </c>
+      <c r="F349">
+        <v>224649</v>
+      </c>
+      <c r="G349">
+        <v>148341</v>
+      </c>
+      <c r="H349">
+        <v>116326</v>
+      </c>
+      <c r="I349">
+        <v>32015</v>
+      </c>
+      <c r="J349">
+        <v>47646</v>
+      </c>
+      <c r="K349" s="11">
+        <f t="shared" si="31"/>
+        <v>0.21209086174432115</v>
+      </c>
+      <c r="L349">
+        <v>4851</v>
+      </c>
+      <c r="M349" s="11">
+        <f t="shared" si="29"/>
+        <v>0.10181337363052512</v>
+      </c>
+      <c r="N349">
+        <v>42795</v>
+      </c>
+      <c r="O349" s="13">
+        <f t="shared" si="30"/>
+        <v>0.89818662636947488</v>
+      </c>
+      <c r="P349">
+        <v>28662</v>
+      </c>
+    </row>
+    <row r="350" spans="1:16" x14ac:dyDescent="0.3">
+      <c r="A350" t="s">
+        <v>36</v>
+      </c>
+      <c r="B350" s="3">
+        <v>46174</v>
+      </c>
+      <c r="C350">
+        <v>906485</v>
+      </c>
+      <c r="D350">
+        <v>490215</v>
+      </c>
+      <c r="E350">
+        <v>76780</v>
+      </c>
+      <c r="F350">
+        <v>70775</v>
+      </c>
+      <c r="G350">
+        <v>43772</v>
+      </c>
+      <c r="H350">
+        <v>32095</v>
+      </c>
+      <c r="I350">
+        <v>11677</v>
+      </c>
+      <c r="J350">
+        <v>23676</v>
+      </c>
+      <c r="K350" s="11">
+        <f t="shared" si="31"/>
+        <v>0.33452490286117981</v>
+      </c>
+      <c r="L350">
+        <v>3989</v>
+      </c>
+      <c r="M350" s="11">
+        <f t="shared" si="29"/>
+        <v>0.1684828518330799</v>
+      </c>
+      <c r="N350">
+        <v>19687</v>
+      </c>
+      <c r="O350" s="13">
+        <f t="shared" si="30"/>
+        <v>0.83151714816692013</v>
+      </c>
+      <c r="P350">
+        <v>3327</v>
+      </c>
+    </row>
+    <row r="351" spans="1:16" x14ac:dyDescent="0.3">
+      <c r="A351" t="s">
+        <v>37</v>
+      </c>
+      <c r="B351" s="3">
+        <v>46174</v>
+      </c>
+      <c r="C351">
+        <v>1085802</v>
+      </c>
+      <c r="D351">
+        <v>801926</v>
+      </c>
+      <c r="E351">
+        <v>71073</v>
+      </c>
+      <c r="F351">
+        <v>69711</v>
+      </c>
+      <c r="G351">
+        <v>56588</v>
+      </c>
+      <c r="H351">
+        <v>49326</v>
+      </c>
+      <c r="I351">
+        <v>7262</v>
+      </c>
+      <c r="J351">
+        <v>12907</v>
+      </c>
+      <c r="K351" s="11">
+        <f t="shared" si="31"/>
+        <v>0.18515011978023554</v>
+      </c>
+      <c r="L351">
+        <v>3213</v>
+      </c>
+      <c r="M351" s="11">
+        <f t="shared" si="29"/>
+        <v>0.24893468660416829</v>
+      </c>
+      <c r="N351">
+        <v>9694</v>
+      </c>
+      <c r="O351" s="13">
+        <f t="shared" si="30"/>
+        <v>0.75106531339583171</v>
+      </c>
+      <c r="P351">
+        <v>216</v>
+      </c>
+    </row>
+    <row r="352" spans="1:16" x14ac:dyDescent="0.3">
+      <c r="A352" t="s">
+        <v>38</v>
+      </c>
+      <c r="B352" s="3">
+        <v>46174</v>
+      </c>
+      <c r="C352">
+        <v>2679464</v>
+      </c>
+      <c r="D352">
+        <v>1564955</v>
+      </c>
+      <c r="E352">
+        <v>208151</v>
+      </c>
+      <c r="F352">
+        <v>200071</v>
+      </c>
+      <c r="G352">
+        <v>123365</v>
+      </c>
+      <c r="H352">
+        <v>42253</v>
+      </c>
+      <c r="I352">
+        <v>81112</v>
+      </c>
+      <c r="J352">
+        <v>31696</v>
+      </c>
+      <c r="K352" s="11">
+        <f t="shared" si="31"/>
+        <v>0.15842375956535429</v>
+      </c>
+      <c r="L352">
+        <v>17649</v>
+      </c>
+      <c r="M352" s="11">
+        <f t="shared" si="29"/>
+        <v>0.55682104997476023</v>
+      </c>
+      <c r="N352">
+        <v>14047</v>
+      </c>
+      <c r="O352" s="13">
+        <f t="shared" si="30"/>
+        <v>0.44317895002523977</v>
+      </c>
+      <c r="P352">
+        <v>45010</v>
+      </c>
+    </row>
+    <row r="353" spans="1:16" x14ac:dyDescent="0.3">
+      <c r="A353" t="s">
+        <v>39</v>
+      </c>
+      <c r="B353" s="3">
+        <v>46174</v>
+      </c>
+      <c r="C353">
+        <v>250294</v>
+      </c>
+      <c r="D353">
+        <v>173563</v>
+      </c>
+      <c r="E353">
+        <v>19805</v>
+      </c>
+      <c r="F353">
+        <v>22175</v>
+      </c>
+      <c r="G353">
+        <v>19021</v>
+      </c>
+      <c r="H353">
+        <v>16960</v>
+      </c>
+      <c r="I353">
+        <v>2061</v>
+      </c>
+      <c r="J353">
+        <v>3119</v>
+      </c>
+      <c r="K353" s="11">
+        <f t="shared" si="31"/>
+        <v>0.14065388951521984</v>
+      </c>
+      <c r="L353">
+        <v>1107</v>
+      </c>
+      <c r="M353" s="11">
+        <f t="shared" si="29"/>
+        <v>0.35492144918243029</v>
+      </c>
+      <c r="N353">
+        <v>2012</v>
+      </c>
+      <c r="O353" s="13">
+        <f t="shared" si="30"/>
+        <v>0.64507855081756971</v>
+      </c>
+      <c r="P353">
+        <v>35</v>
+      </c>
+    </row>
+    <row r="354" spans="1:16" x14ac:dyDescent="0.3">
+      <c r="A354" t="s">
+        <v>40</v>
+      </c>
+      <c r="B354" s="3">
+        <v>46174</v>
+      </c>
+      <c r="C354">
+        <v>846524</v>
+      </c>
+      <c r="D354">
+        <v>362404</v>
+      </c>
+      <c r="E354">
+        <v>80048</v>
+      </c>
+      <c r="F354">
+        <v>78480</v>
+      </c>
+      <c r="G354">
+        <v>53406</v>
+      </c>
+      <c r="H354">
+        <v>50350</v>
+      </c>
+      <c r="I354">
+        <v>3056</v>
+      </c>
+      <c r="J354">
+        <v>22443</v>
+      </c>
+      <c r="K354" s="11">
+        <f t="shared" si="31"/>
+        <v>0.28597094801223244</v>
+      </c>
+      <c r="L354">
+        <v>18816</v>
+      </c>
+      <c r="M354" s="11">
+        <f t="shared" si="29"/>
+        <v>0.83839058949338319</v>
+      </c>
+      <c r="N354">
+        <v>3627</v>
+      </c>
+      <c r="O354" s="13">
+        <f t="shared" si="30"/>
+        <v>0.16160941050661676</v>
+      </c>
+      <c r="P354">
+        <v>2631</v>
+      </c>
+    </row>
+    <row r="355" spans="1:16" x14ac:dyDescent="0.3">
+      <c r="A355" t="s">
+        <v>41</v>
+      </c>
+      <c r="B355" s="3">
+        <v>46174</v>
+      </c>
+      <c r="C355">
+        <v>124001</v>
+      </c>
+      <c r="D355">
+        <v>62583</v>
+      </c>
+      <c r="E355">
+        <v>11416</v>
+      </c>
+      <c r="F355">
+        <v>13355</v>
+      </c>
+      <c r="G355">
+        <v>11009</v>
+      </c>
+      <c r="H355">
+        <v>8471</v>
+      </c>
+      <c r="I355">
+        <v>2538</v>
+      </c>
+      <c r="J355">
+        <v>2158</v>
+      </c>
+      <c r="K355" s="11">
+        <f t="shared" si="31"/>
+        <v>0.16158742044178209</v>
+      </c>
+      <c r="L355">
+        <v>410</v>
+      </c>
+      <c r="M355" s="11">
+        <f t="shared" si="29"/>
+        <v>0.18999073215940684</v>
+      </c>
+      <c r="N355">
+        <v>1748</v>
+      </c>
+      <c r="O355" s="13">
+        <f t="shared" si="30"/>
+        <v>0.81000926784059313</v>
+      </c>
+      <c r="P355">
+        <v>188</v>
+      </c>
+    </row>
+    <row r="356" spans="1:16" x14ac:dyDescent="0.3">
+      <c r="A356" t="s">
+        <v>42</v>
+      </c>
+      <c r="B356" s="3">
+        <v>46174</v>
+      </c>
+      <c r="C356">
+        <v>1199546</v>
+      </c>
+      <c r="D356">
+        <v>563216</v>
+      </c>
+      <c r="E356">
+        <v>123726</v>
+      </c>
+      <c r="F356">
+        <v>82604</v>
+      </c>
+      <c r="G356">
+        <v>72918</v>
+      </c>
+      <c r="H356">
+        <v>54847</v>
+      </c>
+      <c r="I356">
+        <v>18071</v>
+      </c>
+      <c r="J356">
+        <v>9484</v>
+      </c>
+      <c r="K356" s="11">
+        <f t="shared" si="31"/>
+        <v>0.11481284199312382</v>
+      </c>
+      <c r="L356">
+        <v>2502</v>
+      </c>
+      <c r="M356" s="11">
+        <f t="shared" si="29"/>
+        <v>0.2638127372416702</v>
+      </c>
+      <c r="N356">
+        <v>6982</v>
+      </c>
+      <c r="O356" s="13">
+        <f t="shared" si="30"/>
+        <v>0.7361872627583298</v>
+      </c>
+      <c r="P356">
+        <v>202</v>
+      </c>
+    </row>
+    <row r="357" spans="1:16" x14ac:dyDescent="0.3">
+      <c r="A357" t="s">
+        <v>43</v>
+      </c>
+      <c r="B357" s="3">
+        <v>46174</v>
+      </c>
+      <c r="C357">
+        <v>3589392</v>
+      </c>
+      <c r="D357">
+        <v>955806</v>
+      </c>
+      <c r="E357">
+        <v>334625</v>
+      </c>
+      <c r="F357">
+        <v>252853</v>
+      </c>
+      <c r="G357">
+        <v>150937</v>
+      </c>
+      <c r="H357">
+        <v>23752</v>
+      </c>
+      <c r="I357">
+        <v>127185</v>
+      </c>
+      <c r="J357">
+        <v>84190</v>
+      </c>
+      <c r="K357" s="11">
+        <f t="shared" si="31"/>
+        <v>0.33296025754094277</v>
+      </c>
+      <c r="L357">
+        <v>24900</v>
+      </c>
+      <c r="M357" s="11">
+        <f t="shared" si="29"/>
+        <v>0.29575959140040387</v>
+      </c>
+      <c r="N357">
+        <v>59290</v>
+      </c>
+      <c r="O357" s="13">
+        <f t="shared" si="30"/>
+        <v>0.70424040859959613</v>
+      </c>
+      <c r="P357">
+        <v>17726</v>
+      </c>
+    </row>
+    <row r="358" spans="1:16" x14ac:dyDescent="0.3">
+      <c r="A358" t="s">
+        <v>44</v>
+      </c>
+      <c r="B358" s="3">
+        <v>46174</v>
+      </c>
+      <c r="C358">
+        <v>288065</v>
+      </c>
+      <c r="D358">
+        <v>161881</v>
+      </c>
+      <c r="E358">
+        <v>25060</v>
+      </c>
+      <c r="F358">
+        <v>28157</v>
+      </c>
+      <c r="G358">
+        <v>15327</v>
+      </c>
+      <c r="H358">
+        <v>9851</v>
+      </c>
+      <c r="I358">
+        <v>5476</v>
+      </c>
+      <c r="J358">
+        <v>8131</v>
+      </c>
+      <c r="K358" s="11">
+        <f t="shared" si="31"/>
+        <v>0.28877366196682885</v>
+      </c>
+      <c r="L358">
+        <v>860</v>
+      </c>
+      <c r="M358" s="11">
+        <f t="shared" si="29"/>
+        <v>0.1057680482105522</v>
+      </c>
+      <c r="N358">
+        <v>7271</v>
+      </c>
+      <c r="O358" s="13">
+        <f t="shared" si="30"/>
+        <v>0.89423195178944781</v>
+      </c>
+      <c r="P358">
+        <v>4699</v>
+      </c>
+    </row>
+    <row r="359" spans="1:16" x14ac:dyDescent="0.3">
+      <c r="A359" t="s">
+        <v>45</v>
+      </c>
+      <c r="B359" s="3">
+        <v>46174</v>
+      </c>
+      <c r="C359">
+        <v>1449118</v>
+      </c>
+      <c r="D359">
+        <v>854859</v>
+      </c>
+      <c r="E359">
+        <v>133466</v>
+      </c>
+      <c r="F359">
+        <v>114317</v>
+      </c>
+      <c r="G359">
+        <v>84529</v>
+      </c>
+      <c r="H359">
+        <v>50442</v>
+      </c>
+      <c r="I359">
+        <v>34087</v>
+      </c>
+      <c r="J359">
+        <v>15189</v>
+      </c>
+      <c r="K359" s="11">
+        <f t="shared" si="31"/>
+        <v>0.13286737755539421</v>
+      </c>
+      <c r="L359">
+        <v>472</v>
+      </c>
+      <c r="M359" s="11">
+        <f t="shared" si="29"/>
+        <v>3.1075120152742115E-2</v>
+      </c>
+      <c r="N359">
+        <v>14717</v>
+      </c>
+      <c r="O359" s="13">
+        <f t="shared" si="30"/>
+        <v>0.96892487984725784</v>
+      </c>
+      <c r="P359">
+        <v>14599</v>
+      </c>
+    </row>
+    <row r="360" spans="1:16" x14ac:dyDescent="0.3">
+      <c r="A360" t="s">
+        <v>46</v>
+      </c>
+      <c r="B360" s="3">
+        <v>46174</v>
+      </c>
+      <c r="C360">
+        <v>139930</v>
+      </c>
+      <c r="D360">
+        <v>89262</v>
+      </c>
+      <c r="E360">
+        <v>10016</v>
+      </c>
+      <c r="F360">
+        <v>9606</v>
+      </c>
+      <c r="G360">
+        <v>7245</v>
+      </c>
+      <c r="H360">
+        <v>6256</v>
+      </c>
+      <c r="I360">
+        <v>989</v>
+      </c>
+      <c r="J360">
+        <v>1387</v>
+      </c>
+      <c r="K360" s="11">
+        <f t="shared" si="31"/>
+        <v>0.14438892358942329</v>
+      </c>
+      <c r="L360">
+        <v>247</v>
+      </c>
+      <c r="M360" s="11">
+        <f t="shared" si="29"/>
+        <v>0.17808219178082191</v>
+      </c>
+      <c r="N360">
+        <v>1140</v>
+      </c>
+      <c r="O360" s="13">
+        <f t="shared" si="30"/>
+        <v>0.82191780821917804</v>
+      </c>
+      <c r="P360">
+        <v>974</v>
+      </c>
+    </row>
+    <row r="361" spans="1:16" x14ac:dyDescent="0.3">
+      <c r="A361" t="s">
+        <v>47</v>
+      </c>
+      <c r="B361" s="3">
+        <v>46174</v>
+      </c>
+      <c r="C361">
+        <v>1718507</v>
+      </c>
+      <c r="D361">
+        <v>970103</v>
+      </c>
+      <c r="E361">
+        <v>148709</v>
+      </c>
+      <c r="F361">
+        <v>122950</v>
+      </c>
+      <c r="G361">
+        <v>105373</v>
+      </c>
+      <c r="H361">
+        <v>98827</v>
+      </c>
+      <c r="I361">
+        <v>6546</v>
+      </c>
+      <c r="J361">
+        <v>15759</v>
+      </c>
+      <c r="K361" s="11">
+        <f t="shared" si="31"/>
+        <v>0.12817405449369662</v>
+      </c>
+      <c r="L361">
+        <v>2129</v>
+      </c>
+      <c r="M361" s="11">
+        <f t="shared" si="29"/>
+        <v>0.13509740465765593</v>
+      </c>
+      <c r="N361">
+        <v>13630</v>
+      </c>
+      <c r="O361" s="13">
+        <f t="shared" si="30"/>
+        <v>0.86490259534234404</v>
+      </c>
+      <c r="P361">
+        <v>1818</v>
+      </c>
+    </row>
+    <row r="362" spans="1:16" x14ac:dyDescent="0.3">
+      <c r="A362" t="s">
+        <v>48</v>
+      </c>
+      <c r="B362" s="3">
+        <v>46174</v>
+      </c>
+      <c r="C362">
+        <v>1010403</v>
+      </c>
+      <c r="D362">
+        <v>579241</v>
+      </c>
+      <c r="E362">
+        <v>65241</v>
+      </c>
+      <c r="F362">
+        <v>71150</v>
+      </c>
+      <c r="G362">
+        <v>51165</v>
+      </c>
+      <c r="H362">
+        <v>32322</v>
+      </c>
+      <c r="I362">
+        <v>18843</v>
+      </c>
+      <c r="J362">
+        <v>15737</v>
+      </c>
+      <c r="K362" s="11">
+        <f t="shared" si="31"/>
+        <v>0.22118060435699227</v>
+      </c>
+      <c r="L362">
+        <v>6339</v>
+      </c>
+      <c r="M362" s="11">
+        <f t="shared" si="29"/>
+        <v>0.40280866747156385</v>
+      </c>
+      <c r="N362">
+        <v>9398</v>
+      </c>
+      <c r="O362" s="13">
+        <f t="shared" si="30"/>
+        <v>0.59719133252843615</v>
+      </c>
+      <c r="P362">
+        <v>4248</v>
+      </c>
+    </row>
+    <row r="363" spans="1:16" x14ac:dyDescent="0.3">
+      <c r="A363" t="s">
+        <v>49</v>
+      </c>
+      <c r="B363" s="3">
+        <v>46174</v>
+      </c>
+      <c r="C363">
+        <v>445428</v>
+      </c>
+      <c r="D363">
+        <v>293276</v>
+      </c>
+      <c r="E363">
+        <v>34778</v>
+      </c>
+      <c r="F363">
+        <v>28388</v>
+      </c>
+      <c r="G363">
+        <v>22441</v>
+      </c>
+      <c r="H363">
+        <v>17237</v>
+      </c>
+      <c r="I363">
+        <v>5204</v>
+      </c>
+      <c r="J363">
+        <v>5673</v>
+      </c>
+      <c r="K363" s="11">
+        <f t="shared" si="31"/>
+        <v>0.19983795970128224</v>
+      </c>
+      <c r="L363">
+        <v>1241</v>
+      </c>
+      <c r="M363" s="11">
+        <f t="shared" si="29"/>
+        <v>0.21875550854926845</v>
+      </c>
+      <c r="N363">
+        <v>4432</v>
+      </c>
+      <c r="O363" s="13">
+        <f t="shared" si="30"/>
+        <v>0.78124449145073149</v>
+      </c>
+      <c r="P363">
+        <v>274</v>
+      </c>
+    </row>
+    <row r="364" spans="1:16" x14ac:dyDescent="0.3">
+      <c r="A364" t="s">
+        <v>50</v>
+      </c>
+      <c r="B364" s="3">
+        <v>46174</v>
+      </c>
+      <c r="C364">
+        <v>53183</v>
+      </c>
+      <c r="D364">
+        <v>19305</v>
+      </c>
+      <c r="E364">
+        <v>4757</v>
+      </c>
+      <c r="F364">
+        <v>5145</v>
+      </c>
+      <c r="G364">
+        <v>2940</v>
+      </c>
+      <c r="H364">
+        <v>1909</v>
+      </c>
+      <c r="I364">
+        <v>1031</v>
+      </c>
+      <c r="J364">
+        <v>1253</v>
+      </c>
+      <c r="K364" s="11">
+        <f t="shared" si="31"/>
+        <v>0.24353741496598638</v>
+      </c>
+      <c r="L364">
+        <v>252</v>
+      </c>
+      <c r="M364" s="11">
+        <f>L364/J364</f>
+        <v>0.2011173184357542</v>
+      </c>
+      <c r="N364">
+        <v>1001</v>
+      </c>
+      <c r="O364" s="13">
+        <f t="shared" si="30"/>
+        <v>0.7988826815642458</v>
+      </c>
+      <c r="P364">
+        <v>952</v>
+      </c>
+    </row>
+    <row r="365" spans="1:16" s="1" customFormat="1" x14ac:dyDescent="0.3">
+      <c r="A365" s="1" t="s">
+        <v>63</v>
+      </c>
+      <c r="B365" s="8">
+        <v>46174</v>
+      </c>
+      <c r="C365" s="1">
+        <f>SUM(C314:C364)</f>
+        <v>65969381</v>
+      </c>
+      <c r="D365" s="1">
+        <f>SUM(D314:D364)</f>
+        <v>38123755</v>
+      </c>
+      <c r="E365" s="1">
+        <f>SUM(E314:E364)</f>
+        <v>5413078</v>
+      </c>
+      <c r="F365" s="1">
+        <f>SUM(F314:F364)</f>
+        <v>5400279</v>
+      </c>
+      <c r="G365" s="1">
+        <f>SUM(G314:G364)</f>
+        <v>3659660</v>
+      </c>
+      <c r="H365" s="1">
+        <f>SUM(H314:H364)</f>
+        <v>2541079</v>
+      </c>
+      <c r="I365" s="1">
+        <f>SUM(I314:I364)</f>
+        <v>1118581</v>
+      </c>
+      <c r="J365" s="1">
+        <f>SUM(J314:J364)</f>
+        <v>1079650</v>
+      </c>
+      <c r="K365" s="9">
+        <f>J365/F365</f>
+        <v>0.19992485573430557</v>
+      </c>
+      <c r="L365" s="1">
+        <v>289986</v>
+      </c>
+      <c r="M365" s="9">
+        <f t="shared" si="29"/>
+        <v>0.26859259945352659</v>
+      </c>
+      <c r="N365" s="1">
+        <f>SUM(N314:N364)</f>
+        <v>789664</v>
+      </c>
+      <c r="O365" s="13">
+        <f>N365/J365</f>
+        <v>0.73140740054647335</v>
+      </c>
+      <c r="P365" s="1">
+        <f>SUM(P314:P364)</f>
+        <v>660969</v>
       </c>
     </row>
   </sheetData>
@@ -18217,7 +20983,7 @@
 
 <file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{7BE017E0-0CCA-4F1E-AF7D-1E1C72BF1483}">
-  <dimension ref="A1:E313"/>
+  <dimension ref="A1:E365"/>
   <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
   <cols>
     <col min="1" max="1" width="17.88671875" bestFit="1" customWidth="1"/>
@@ -18244,7 +21010,7 @@
         <v>154</v>
       </c>
     </row>
-    <row r="2" spans="1:5" x14ac:dyDescent="0.3">
+    <row r="2" spans="1:5" hidden="1" x14ac:dyDescent="0.3">
       <c r="A2" t="s">
         <v>0</v>
       </c>
@@ -18262,7 +21028,7 @@
         <v>85106</v>
       </c>
     </row>
-    <row r="3" spans="1:5" x14ac:dyDescent="0.3">
+    <row r="3" spans="1:5" hidden="1" x14ac:dyDescent="0.3">
       <c r="A3" t="s">
         <v>1</v>
       </c>
@@ -18280,7 +21046,7 @@
         <v>671861</v>
       </c>
     </row>
-    <row r="4" spans="1:5" x14ac:dyDescent="0.3">
+    <row r="4" spans="1:5" hidden="1" x14ac:dyDescent="0.3">
       <c r="A4" t="s">
         <v>2</v>
       </c>
@@ -18298,7 +21064,7 @@
         <v>414424</v>
       </c>
     </row>
-    <row r="5" spans="1:5" x14ac:dyDescent="0.3">
+    <row r="5" spans="1:5" hidden="1" x14ac:dyDescent="0.3">
       <c r="A5" t="s">
         <v>3</v>
       </c>
@@ -18316,7 +21082,7 @@
         <v>734622</v>
       </c>
     </row>
-    <row r="6" spans="1:5" x14ac:dyDescent="0.3">
+    <row r="6" spans="1:5" hidden="1" x14ac:dyDescent="0.3">
       <c r="A6" t="s">
         <v>4</v>
       </c>
@@ -18334,7 +21100,7 @@
         <v>4603626</v>
       </c>
     </row>
-    <row r="7" spans="1:5" x14ac:dyDescent="0.3">
+    <row r="7" spans="1:5" hidden="1" x14ac:dyDescent="0.3">
       <c r="A7" t="s">
         <v>5</v>
       </c>
@@ -18352,7 +21118,7 @@
         <v>524097</v>
       </c>
     </row>
-    <row r="8" spans="1:5" x14ac:dyDescent="0.3">
+    <row r="8" spans="1:5" hidden="1" x14ac:dyDescent="0.3">
       <c r="A8" t="s">
         <v>6</v>
       </c>
@@ -18370,7 +21136,7 @@
         <v>365119</v>
       </c>
     </row>
-    <row r="9" spans="1:5" x14ac:dyDescent="0.3">
+    <row r="9" spans="1:5" hidden="1" x14ac:dyDescent="0.3">
       <c r="A9" t="s">
         <v>7</v>
       </c>
@@ -18388,7 +21154,7 @@
         <v>94241</v>
       </c>
     </row>
-    <row r="10" spans="1:5" x14ac:dyDescent="0.3">
+    <row r="10" spans="1:5" hidden="1" x14ac:dyDescent="0.3">
       <c r="A10" t="s">
         <v>8</v>
       </c>
@@ -18406,7 +21172,7 @@
         <v>106707</v>
       </c>
     </row>
-    <row r="11" spans="1:5" x14ac:dyDescent="0.3">
+    <row r="11" spans="1:5" hidden="1" x14ac:dyDescent="0.3">
       <c r="A11" t="s">
         <v>9</v>
       </c>
@@ -18424,7 +21190,7 @@
         <v>2317039</v>
       </c>
     </row>
-    <row r="12" spans="1:5" x14ac:dyDescent="0.3">
+    <row r="12" spans="1:5" hidden="1" x14ac:dyDescent="0.3">
       <c r="A12" t="s">
         <v>10</v>
       </c>
@@ -18442,7 +21208,7 @@
         <v>1307613</v>
       </c>
     </row>
-    <row r="13" spans="1:5" x14ac:dyDescent="0.3">
+    <row r="13" spans="1:5" hidden="1" x14ac:dyDescent="0.3">
       <c r="A13" t="s">
         <v>11</v>
       </c>
@@ -18460,7 +21226,7 @@
         <v>152977</v>
       </c>
     </row>
-    <row r="14" spans="1:5" x14ac:dyDescent="0.3">
+    <row r="14" spans="1:5" hidden="1" x14ac:dyDescent="0.3">
       <c r="A14" t="s">
         <v>12</v>
       </c>
@@ -18478,7 +21244,7 @@
         <v>329791</v>
       </c>
     </row>
-    <row r="15" spans="1:5" x14ac:dyDescent="0.3">
+    <row r="15" spans="1:5" hidden="1" x14ac:dyDescent="0.3">
       <c r="A15" t="s">
         <v>13</v>
       </c>
@@ -18496,7 +21262,7 @@
         <v>151739</v>
       </c>
     </row>
-    <row r="16" spans="1:5" x14ac:dyDescent="0.3">
+    <row r="16" spans="1:5" hidden="1" x14ac:dyDescent="0.3">
       <c r="A16" t="s">
         <v>14</v>
       </c>
@@ -18514,7 +21280,7 @@
         <v>1351821</v>
       </c>
     </row>
-    <row r="17" spans="1:5" x14ac:dyDescent="0.3">
+    <row r="17" spans="1:5" hidden="1" x14ac:dyDescent="0.3">
       <c r="A17" t="s">
         <v>15</v>
       </c>
@@ -18532,7 +21298,7 @@
         <v>703263</v>
       </c>
     </row>
-    <row r="18" spans="1:5" x14ac:dyDescent="0.3">
+    <row r="18" spans="1:5" hidden="1" x14ac:dyDescent="0.3">
       <c r="A18" t="s">
         <v>16</v>
       </c>
@@ -18550,7 +21316,7 @@
         <v>276016</v>
       </c>
     </row>
-    <row r="19" spans="1:5" x14ac:dyDescent="0.3">
+    <row r="19" spans="1:5" hidden="1" x14ac:dyDescent="0.3">
       <c r="A19" t="s">
         <v>17</v>
       </c>
@@ -18568,7 +21334,7 @@
         <v>601664</v>
       </c>
     </row>
-    <row r="20" spans="1:5" x14ac:dyDescent="0.3">
+    <row r="20" spans="1:5" hidden="1" x14ac:dyDescent="0.3">
       <c r="A20" t="s">
         <v>18</v>
       </c>
@@ -18586,7 +21352,7 @@
         <v>679336</v>
       </c>
     </row>
-    <row r="21" spans="1:5" x14ac:dyDescent="0.3">
+    <row r="21" spans="1:5" hidden="1" x14ac:dyDescent="0.3">
       <c r="A21" t="s">
         <v>19</v>
       </c>
@@ -18604,7 +21370,7 @@
         <v>686697</v>
       </c>
     </row>
-    <row r="22" spans="1:5" x14ac:dyDescent="0.3">
+    <row r="22" spans="1:5" hidden="1" x14ac:dyDescent="0.3">
       <c r="A22" t="s">
         <v>20</v>
       </c>
@@ -18622,7 +21388,7 @@
         <v>668222</v>
       </c>
     </row>
-    <row r="23" spans="1:5" x14ac:dyDescent="0.3">
+    <row r="23" spans="1:5" hidden="1" x14ac:dyDescent="0.3">
       <c r="A23" t="s">
         <v>21</v>
       </c>
@@ -18640,7 +21406,7 @@
         <v>139262</v>
       </c>
     </row>
-    <row r="24" spans="1:5" x14ac:dyDescent="0.3">
+    <row r="24" spans="1:5" hidden="1" x14ac:dyDescent="0.3">
       <c r="A24" t="s">
         <v>22</v>
       </c>
@@ -18658,7 +21424,7 @@
         <v>886131</v>
       </c>
     </row>
-    <row r="25" spans="1:5" x14ac:dyDescent="0.3">
+    <row r="25" spans="1:5" hidden="1" x14ac:dyDescent="0.3">
       <c r="A25" t="s">
         <v>23</v>
       </c>
@@ -18676,7 +21442,7 @@
         <v>600115</v>
       </c>
     </row>
-    <row r="26" spans="1:5" x14ac:dyDescent="0.3">
+    <row r="26" spans="1:5" hidden="1" x14ac:dyDescent="0.3">
       <c r="A26" t="s">
         <v>24</v>
       </c>
@@ -18694,7 +21460,7 @@
         <v>572269</v>
       </c>
     </row>
-    <row r="27" spans="1:5" x14ac:dyDescent="0.3">
+    <row r="27" spans="1:5" hidden="1" x14ac:dyDescent="0.3">
       <c r="A27" t="s">
         <v>25</v>
       </c>
@@ -18712,7 +21478,7 @@
         <v>392964</v>
       </c>
     </row>
-    <row r="28" spans="1:5" x14ac:dyDescent="0.3">
+    <row r="28" spans="1:5" hidden="1" x14ac:dyDescent="0.3">
       <c r="A28" t="s">
         <v>26</v>
       </c>
@@ -18730,7 +21496,7 @@
         <v>89777</v>
       </c>
     </row>
-    <row r="29" spans="1:5" x14ac:dyDescent="0.3">
+    <row r="29" spans="1:5" hidden="1" x14ac:dyDescent="0.3">
       <c r="A29" t="s">
         <v>27</v>
       </c>
@@ -18748,7 +21514,7 @@
         <v>1421278</v>
       </c>
     </row>
-    <row r="30" spans="1:5" x14ac:dyDescent="0.3">
+    <row r="30" spans="1:5" hidden="1" x14ac:dyDescent="0.3">
       <c r="A30" t="s">
         <v>28</v>
       </c>
@@ -18766,7 +21532,7 @@
         <v>50838</v>
       </c>
     </row>
-    <row r="31" spans="1:5" x14ac:dyDescent="0.3">
+    <row r="31" spans="1:5" hidden="1" x14ac:dyDescent="0.3">
       <c r="A31" t="s">
         <v>29</v>
       </c>
@@ -18784,7 +21550,7 @@
         <v>170364</v>
       </c>
     </row>
-    <row r="32" spans="1:5" x14ac:dyDescent="0.3">
+    <row r="32" spans="1:5" hidden="1" x14ac:dyDescent="0.3">
       <c r="A32" t="s">
         <v>30</v>
       </c>
@@ -18802,7 +21568,7 @@
         <v>86109</v>
       </c>
     </row>
-    <row r="33" spans="1:5" x14ac:dyDescent="0.3">
+    <row r="33" spans="1:5" hidden="1" x14ac:dyDescent="0.3">
       <c r="A33" t="s">
         <v>31</v>
       </c>
@@ -18820,7 +21586,7 @@
         <v>805907</v>
       </c>
     </row>
-    <row r="34" spans="1:5" x14ac:dyDescent="0.3">
+    <row r="34" spans="1:5" hidden="1" x14ac:dyDescent="0.3">
       <c r="A34" t="s">
         <v>32</v>
       </c>
@@ -18838,7 +21604,7 @@
         <v>308545</v>
       </c>
     </row>
-    <row r="35" spans="1:5" x14ac:dyDescent="0.3">
+    <row r="35" spans="1:5" hidden="1" x14ac:dyDescent="0.3">
       <c r="A35" t="s">
         <v>33</v>
       </c>
@@ -18856,7 +21622,7 @@
         <v>315744</v>
       </c>
     </row>
-    <row r="36" spans="1:5" x14ac:dyDescent="0.3">
+    <row r="36" spans="1:5" hidden="1" x14ac:dyDescent="0.3">
       <c r="A36" t="s">
         <v>34</v>
       </c>
@@ -18874,7 +21640,7 @@
         <v>2459230</v>
       </c>
     </row>
-    <row r="37" spans="1:5" x14ac:dyDescent="0.3">
+    <row r="37" spans="1:5" hidden="1" x14ac:dyDescent="0.3">
       <c r="A37" t="s">
         <v>35</v>
       </c>
@@ -18892,7 +21658,7 @@
         <v>1174157</v>
       </c>
     </row>
-    <row r="38" spans="1:5" x14ac:dyDescent="0.3">
+    <row r="38" spans="1:5" hidden="1" x14ac:dyDescent="0.3">
       <c r="A38" t="s">
         <v>36</v>
       </c>
@@ -18910,7 +21676,7 @@
         <v>507825</v>
       </c>
     </row>
-    <row r="39" spans="1:5" x14ac:dyDescent="0.3">
+    <row r="39" spans="1:5" hidden="1" x14ac:dyDescent="0.3">
       <c r="A39" t="s">
         <v>37</v>
       </c>
@@ -18928,7 +21694,7 @@
         <v>470891</v>
       </c>
     </row>
-    <row r="40" spans="1:5" x14ac:dyDescent="0.3">
+    <row r="40" spans="1:5" hidden="1" x14ac:dyDescent="0.3">
       <c r="A40" t="s">
         <v>38</v>
       </c>
@@ -18946,7 +21712,7 @@
         <v>1407181</v>
       </c>
     </row>
-    <row r="41" spans="1:5" x14ac:dyDescent="0.3">
+    <row r="41" spans="1:5" hidden="1" x14ac:dyDescent="0.3">
       <c r="A41" t="s">
         <v>39</v>
       </c>
@@ -18964,7 +21730,7 @@
         <v>118453</v>
       </c>
     </row>
-    <row r="42" spans="1:5" x14ac:dyDescent="0.3">
+    <row r="42" spans="1:5" hidden="1" x14ac:dyDescent="0.3">
       <c r="A42" t="s">
         <v>40</v>
       </c>
@@ -18982,7 +21748,7 @@
         <v>605042</v>
       </c>
     </row>
-    <row r="43" spans="1:5" x14ac:dyDescent="0.3">
+    <row r="43" spans="1:5" hidden="1" x14ac:dyDescent="0.3">
       <c r="A43" t="s">
         <v>41</v>
       </c>
@@ -19000,7 +21766,7 @@
         <v>76384</v>
       </c>
     </row>
-    <row r="44" spans="1:5" x14ac:dyDescent="0.3">
+    <row r="44" spans="1:5" hidden="1" x14ac:dyDescent="0.3">
       <c r="A44" t="s">
         <v>42</v>
       </c>
@@ -19018,7 +21784,7 @@
         <v>829861</v>
       </c>
     </row>
-    <row r="45" spans="1:5" x14ac:dyDescent="0.3">
+    <row r="45" spans="1:5" hidden="1" x14ac:dyDescent="0.3">
       <c r="A45" t="s">
         <v>43</v>
       </c>
@@ -19036,7 +21802,7 @@
         <v>3112769</v>
       </c>
     </row>
-    <row r="46" spans="1:5" x14ac:dyDescent="0.3">
+    <row r="46" spans="1:5" hidden="1" x14ac:dyDescent="0.3">
       <c r="A46" t="s">
         <v>44</v>
       </c>
@@ -19054,7 +21820,7 @@
         <v>165721</v>
       </c>
     </row>
-    <row r="47" spans="1:5" x14ac:dyDescent="0.3">
+    <row r="47" spans="1:5" hidden="1" x14ac:dyDescent="0.3">
       <c r="A47" t="s">
         <v>45</v>
       </c>
@@ -19072,7 +21838,7 @@
         <v>800142</v>
       </c>
     </row>
-    <row r="48" spans="1:5" x14ac:dyDescent="0.3">
+    <row r="48" spans="1:5" hidden="1" x14ac:dyDescent="0.3">
       <c r="A48" t="s">
         <v>46</v>
       </c>
@@ -19090,7 +21856,7 @@
         <v>57370</v>
       </c>
     </row>
-    <row r="49" spans="1:5" x14ac:dyDescent="0.3">
+    <row r="49" spans="1:5" hidden="1" x14ac:dyDescent="0.3">
       <c r="A49" t="s">
         <v>47</v>
       </c>
@@ -19108,7 +21874,7 @@
         <v>818165</v>
       </c>
     </row>
-    <row r="50" spans="1:5" x14ac:dyDescent="0.3">
+    <row r="50" spans="1:5" hidden="1" x14ac:dyDescent="0.3">
       <c r="A50" t="s">
         <v>48</v>
       </c>
@@ -19126,7 +21892,7 @@
         <v>536307</v>
       </c>
     </row>
-    <row r="51" spans="1:5" x14ac:dyDescent="0.3">
+    <row r="51" spans="1:5" hidden="1" x14ac:dyDescent="0.3">
       <c r="A51" t="s">
         <v>49</v>
       </c>
@@ -19144,7 +21910,7 @@
         <v>194725</v>
       </c>
     </row>
-    <row r="52" spans="1:5" x14ac:dyDescent="0.3">
+    <row r="52" spans="1:5" hidden="1" x14ac:dyDescent="0.3">
       <c r="A52" t="s">
         <v>50</v>
       </c>
@@ -19162,7 +21928,7 @@
         <v>40269</v>
       </c>
     </row>
-    <row r="53" spans="1:5" x14ac:dyDescent="0.3">
+    <row r="53" spans="1:5" hidden="1" x14ac:dyDescent="0.3">
       <c r="A53" s="1" t="s">
         <v>63</v>
       </c>
@@ -19182,7 +21948,7 @@
         <v>36039776</v>
       </c>
     </row>
-    <row r="54" spans="1:5" x14ac:dyDescent="0.3">
+    <row r="54" spans="1:5" hidden="1" x14ac:dyDescent="0.3">
       <c r="A54" t="s">
         <v>0</v>
       </c>
@@ -19200,7 +21966,7 @@
         <v>84968</v>
       </c>
     </row>
-    <row r="55" spans="1:5" x14ac:dyDescent="0.3">
+    <row r="55" spans="1:5" hidden="1" x14ac:dyDescent="0.3">
       <c r="A55" t="s">
         <v>1</v>
       </c>
@@ -19218,7 +21984,7 @@
         <v>670277</v>
       </c>
     </row>
-    <row r="56" spans="1:5" x14ac:dyDescent="0.3">
+    <row r="56" spans="1:5" hidden="1" x14ac:dyDescent="0.3">
       <c r="A56" t="s">
         <v>2</v>
       </c>
@@ -19236,7 +22002,7 @@
         <v>398948</v>
       </c>
     </row>
-    <row r="57" spans="1:5" x14ac:dyDescent="0.3">
+    <row r="57" spans="1:5" hidden="1" x14ac:dyDescent="0.3">
       <c r="A57" t="s">
         <v>3</v>
       </c>
@@ -19254,7 +22020,7 @@
         <v>728611</v>
       </c>
     </row>
-    <row r="58" spans="1:5" x14ac:dyDescent="0.3">
+    <row r="58" spans="1:5" hidden="1" x14ac:dyDescent="0.3">
       <c r="A58" t="s">
         <v>4</v>
       </c>
@@ -19272,7 +22038,7 @@
         <v>4582795</v>
       </c>
     </row>
-    <row r="59" spans="1:5" x14ac:dyDescent="0.3">
+    <row r="59" spans="1:5" hidden="1" x14ac:dyDescent="0.3">
       <c r="A59" t="s">
         <v>5</v>
       </c>
@@ -19290,7 +22056,7 @@
         <v>524667</v>
       </c>
     </row>
-    <row r="60" spans="1:5" x14ac:dyDescent="0.3">
+    <row r="60" spans="1:5" hidden="1" x14ac:dyDescent="0.3">
       <c r="A60" t="s">
         <v>6</v>
       </c>
@@ -19308,7 +22074,7 @@
         <v>365023</v>
       </c>
     </row>
-    <row r="61" spans="1:5" x14ac:dyDescent="0.3">
+    <row r="61" spans="1:5" hidden="1" x14ac:dyDescent="0.3">
       <c r="A61" t="s">
         <v>7</v>
       </c>
@@ -19326,7 +22092,7 @@
         <v>93257</v>
       </c>
     </row>
-    <row r="62" spans="1:5" x14ac:dyDescent="0.3">
+    <row r="62" spans="1:5" hidden="1" x14ac:dyDescent="0.3">
       <c r="A62" t="s">
         <v>8</v>
       </c>
@@ -19344,7 +22110,7 @@
         <v>106101</v>
       </c>
     </row>
-    <row r="63" spans="1:5" x14ac:dyDescent="0.3">
+    <row r="63" spans="1:5" hidden="1" x14ac:dyDescent="0.3">
       <c r="A63" t="s">
         <v>9</v>
       </c>
@@ -19362,7 +22128,7 @@
         <v>2312874</v>
       </c>
     </row>
-    <row r="64" spans="1:5" x14ac:dyDescent="0.3">
+    <row r="64" spans="1:5" hidden="1" x14ac:dyDescent="0.3">
       <c r="A64" t="s">
         <v>10</v>
       </c>
@@ -19380,7 +22146,7 @@
         <v>1303671</v>
       </c>
     </row>
-    <row r="65" spans="1:5" x14ac:dyDescent="0.3">
+    <row r="65" spans="1:5" hidden="1" x14ac:dyDescent="0.3">
       <c r="A65" t="s">
         <v>11</v>
       </c>
@@ -19398,7 +22164,7 @@
         <v>153346</v>
       </c>
     </row>
-    <row r="66" spans="1:5" x14ac:dyDescent="0.3">
+    <row r="66" spans="1:5" hidden="1" x14ac:dyDescent="0.3">
       <c r="A66" t="s">
         <v>12</v>
       </c>
@@ -19416,7 +22182,7 @@
         <v>329393</v>
       </c>
     </row>
-    <row r="67" spans="1:5" x14ac:dyDescent="0.3">
+    <row r="67" spans="1:5" hidden="1" x14ac:dyDescent="0.3">
       <c r="A67" t="s">
         <v>13</v>
       </c>
@@ -19434,7 +22200,7 @@
         <v>151205</v>
       </c>
     </row>
-    <row r="68" spans="1:5" x14ac:dyDescent="0.3">
+    <row r="68" spans="1:5" hidden="1" x14ac:dyDescent="0.3">
       <c r="A68" t="s">
         <v>14</v>
       </c>
@@ -19452,7 +22218,7 @@
         <v>1347296</v>
       </c>
     </row>
-    <row r="69" spans="1:5" x14ac:dyDescent="0.3">
+    <row r="69" spans="1:5" hidden="1" x14ac:dyDescent="0.3">
       <c r="A69" t="s">
         <v>15</v>
       </c>
@@ -19470,7 +22236,7 @@
         <v>694304</v>
       </c>
     </row>
-    <row r="70" spans="1:5" x14ac:dyDescent="0.3">
+    <row r="70" spans="1:5" hidden="1" x14ac:dyDescent="0.3">
       <c r="A70" t="s">
         <v>16</v>
       </c>
@@ -19488,7 +22254,7 @@
         <v>277116</v>
       </c>
     </row>
-    <row r="71" spans="1:5" x14ac:dyDescent="0.3">
+    <row r="71" spans="1:5" hidden="1" x14ac:dyDescent="0.3">
       <c r="A71" t="s">
         <v>17</v>
       </c>
@@ -19506,7 +22272,7 @@
         <v>599606</v>
       </c>
     </row>
-    <row r="72" spans="1:5" x14ac:dyDescent="0.3">
+    <row r="72" spans="1:5" hidden="1" x14ac:dyDescent="0.3">
       <c r="A72" t="s">
         <v>18</v>
       </c>
@@ -19524,7 +22290,7 @@
         <v>677406</v>
       </c>
     </row>
-    <row r="73" spans="1:5" x14ac:dyDescent="0.3">
+    <row r="73" spans="1:5" hidden="1" x14ac:dyDescent="0.3">
       <c r="A73" t="s">
         <v>19</v>
       </c>
@@ -19542,7 +22308,7 @@
         <v>682951</v>
       </c>
     </row>
-    <row r="74" spans="1:5" x14ac:dyDescent="0.3">
+    <row r="74" spans="1:5" hidden="1" x14ac:dyDescent="0.3">
       <c r="A74" t="s">
         <v>20</v>
       </c>
@@ -19560,7 +22326,7 @@
         <v>665959</v>
       </c>
     </row>
-    <row r="75" spans="1:5" x14ac:dyDescent="0.3">
+    <row r="75" spans="1:5" hidden="1" x14ac:dyDescent="0.3">
       <c r="A75" t="s">
         <v>21</v>
       </c>
@@ -19578,7 +22344,7 @@
         <v>138550</v>
       </c>
     </row>
-    <row r="76" spans="1:5" x14ac:dyDescent="0.3">
+    <row r="76" spans="1:5" hidden="1" x14ac:dyDescent="0.3">
       <c r="A76" t="s">
         <v>22</v>
       </c>
@@ -19596,7 +22362,7 @@
         <v>884441</v>
       </c>
     </row>
-    <row r="77" spans="1:5" x14ac:dyDescent="0.3">
+    <row r="77" spans="1:5" hidden="1" x14ac:dyDescent="0.3">
       <c r="A77" t="s">
         <v>23</v>
       </c>
@@ -19614,7 +22380,7 @@
         <v>596949</v>
       </c>
     </row>
-    <row r="78" spans="1:5" x14ac:dyDescent="0.3">
+    <row r="78" spans="1:5" hidden="1" x14ac:dyDescent="0.3">
       <c r="A78" t="s">
         <v>24</v>
       </c>
@@ -19632,7 +22398,7 @@
         <v>569790</v>
       </c>
     </row>
-    <row r="79" spans="1:5" x14ac:dyDescent="0.3">
+    <row r="79" spans="1:5" hidden="1" x14ac:dyDescent="0.3">
       <c r="A79" t="s">
         <v>25</v>
       </c>
@@ -19650,7 +22416,7 @@
         <v>392722</v>
       </c>
     </row>
-    <row r="80" spans="1:5" x14ac:dyDescent="0.3">
+    <row r="80" spans="1:5" hidden="1" x14ac:dyDescent="0.3">
       <c r="A80" t="s">
         <v>26</v>
       </c>
@@ -19668,7 +22434,7 @@
         <v>89469</v>
       </c>
     </row>
-    <row r="81" spans="1:5" x14ac:dyDescent="0.3">
+    <row r="81" spans="1:5" hidden="1" x14ac:dyDescent="0.3">
       <c r="A81" t="s">
         <v>27</v>
       </c>
@@ -19686,7 +22452,7 @@
         <v>1413056</v>
       </c>
     </row>
-    <row r="82" spans="1:5" x14ac:dyDescent="0.3">
+    <row r="82" spans="1:5" hidden="1" x14ac:dyDescent="0.3">
       <c r="A82" t="s">
         <v>28</v>
       </c>
@@ -19704,7 +22470,7 @@
         <v>50725</v>
       </c>
     </row>
-    <row r="83" spans="1:5" x14ac:dyDescent="0.3">
+    <row r="83" spans="1:5" hidden="1" x14ac:dyDescent="0.3">
       <c r="A83" t="s">
         <v>29</v>
       </c>
@@ -19722,7 +22488,7 @@
         <v>170842</v>
       </c>
     </row>
-    <row r="84" spans="1:5" x14ac:dyDescent="0.3">
+    <row r="84" spans="1:5" hidden="1" x14ac:dyDescent="0.3">
       <c r="A84" t="s">
         <v>30</v>
       </c>
@@ -19740,7 +22506,7 @@
         <v>85603</v>
       </c>
     </row>
-    <row r="85" spans="1:5" x14ac:dyDescent="0.3">
+    <row r="85" spans="1:5" hidden="1" x14ac:dyDescent="0.3">
       <c r="A85" t="s">
         <v>31</v>
       </c>
@@ -19758,7 +22524,7 @@
         <v>801131</v>
       </c>
     </row>
-    <row r="86" spans="1:5" x14ac:dyDescent="0.3">
+    <row r="86" spans="1:5" hidden="1" x14ac:dyDescent="0.3">
       <c r="A86" t="s">
         <v>32</v>
       </c>
@@ -19776,7 +22542,7 @@
         <v>307948</v>
       </c>
     </row>
-    <row r="87" spans="1:5" x14ac:dyDescent="0.3">
+    <row r="87" spans="1:5" hidden="1" x14ac:dyDescent="0.3">
       <c r="A87" t="s">
         <v>33</v>
       </c>
@@ -19794,7 +22560,7 @@
         <v>315938</v>
       </c>
     </row>
-    <row r="88" spans="1:5" x14ac:dyDescent="0.3">
+    <row r="88" spans="1:5" hidden="1" x14ac:dyDescent="0.3">
       <c r="A88" t="s">
         <v>34</v>
       </c>
@@ -19812,7 +22578,7 @@
         <v>2449167</v>
       </c>
     </row>
-    <row r="89" spans="1:5" x14ac:dyDescent="0.3">
+    <row r="89" spans="1:5" hidden="1" x14ac:dyDescent="0.3">
       <c r="A89" t="s">
         <v>35</v>
       </c>
@@ -19830,7 +22596,7 @@
         <v>1163012</v>
       </c>
     </row>
-    <row r="90" spans="1:5" x14ac:dyDescent="0.3">
+    <row r="90" spans="1:5" hidden="1" x14ac:dyDescent="0.3">
       <c r="A90" t="s">
         <v>36</v>
       </c>
@@ -19848,7 +22614,7 @@
         <v>503117</v>
       </c>
     </row>
-    <row r="91" spans="1:5" x14ac:dyDescent="0.3">
+    <row r="91" spans="1:5" hidden="1" x14ac:dyDescent="0.3">
       <c r="A91" t="s">
         <v>37</v>
       </c>
@@ -19866,7 +22632,7 @@
         <v>470685</v>
       </c>
     </row>
-    <row r="92" spans="1:5" x14ac:dyDescent="0.3">
+    <row r="92" spans="1:5" hidden="1" x14ac:dyDescent="0.3">
       <c r="A92" t="s">
         <v>38</v>
       </c>
@@ -19884,7 +22650,7 @@
         <v>1402637</v>
       </c>
     </row>
-    <row r="93" spans="1:5" x14ac:dyDescent="0.3">
+    <row r="93" spans="1:5" hidden="1" x14ac:dyDescent="0.3">
       <c r="A93" t="s">
         <v>39</v>
       </c>
@@ -19902,7 +22668,7 @@
         <v>118532</v>
       </c>
     </row>
-    <row r="94" spans="1:5" x14ac:dyDescent="0.3">
+    <row r="94" spans="1:5" hidden="1" x14ac:dyDescent="0.3">
       <c r="A94" t="s">
         <v>40</v>
       </c>
@@ -19920,7 +22686,7 @@
         <v>603148</v>
       </c>
     </row>
-    <row r="95" spans="1:5" x14ac:dyDescent="0.3">
+    <row r="95" spans="1:5" hidden="1" x14ac:dyDescent="0.3">
       <c r="A95" t="s">
         <v>41</v>
       </c>
@@ -19938,7 +22704,7 @@
         <v>76440</v>
       </c>
     </row>
-    <row r="96" spans="1:5" x14ac:dyDescent="0.3">
+    <row r="96" spans="1:5" hidden="1" x14ac:dyDescent="0.3">
       <c r="A96" t="s">
         <v>42</v>
       </c>
@@ -19956,7 +22722,7 @@
         <v>829627</v>
       </c>
     </row>
-    <row r="97" spans="1:5" x14ac:dyDescent="0.3">
+    <row r="97" spans="1:5" hidden="1" x14ac:dyDescent="0.3">
       <c r="A97" t="s">
         <v>43</v>
       </c>
@@ -19974,7 +22740,7 @@
         <v>3067916</v>
       </c>
     </row>
-    <row r="98" spans="1:5" x14ac:dyDescent="0.3">
+    <row r="98" spans="1:5" hidden="1" x14ac:dyDescent="0.3">
       <c r="A98" t="s">
         <v>44</v>
       </c>
@@ -19992,7 +22758,7 @@
         <v>164522</v>
       </c>
     </row>
-    <row r="99" spans="1:5" x14ac:dyDescent="0.3">
+    <row r="99" spans="1:5" hidden="1" x14ac:dyDescent="0.3">
       <c r="A99" t="s">
         <v>45</v>
       </c>
@@ -20010,7 +22776,7 @@
         <v>797822</v>
       </c>
     </row>
-    <row r="100" spans="1:5" x14ac:dyDescent="0.3">
+    <row r="100" spans="1:5" hidden="1" x14ac:dyDescent="0.3">
       <c r="A100" t="s">
         <v>46</v>
       </c>
@@ -20028,7 +22794,7 @@
         <v>57353</v>
       </c>
     </row>
-    <row r="101" spans="1:5" x14ac:dyDescent="0.3">
+    <row r="101" spans="1:5" hidden="1" x14ac:dyDescent="0.3">
       <c r="A101" t="s">
         <v>47</v>
       </c>
@@ -20046,7 +22812,7 @@
         <v>817682</v>
       </c>
     </row>
-    <row r="102" spans="1:5" x14ac:dyDescent="0.3">
+    <row r="102" spans="1:5" hidden="1" x14ac:dyDescent="0.3">
       <c r="A102" t="s">
         <v>48</v>
       </c>
@@ -20064,7 +22830,7 @@
         <v>536351</v>
       </c>
     </row>
-    <row r="103" spans="1:5" x14ac:dyDescent="0.3">
+    <row r="103" spans="1:5" hidden="1" x14ac:dyDescent="0.3">
       <c r="A103" t="s">
         <v>49</v>
       </c>
@@ -20082,7 +22848,7 @@
         <v>194149</v>
       </c>
     </row>
-    <row r="104" spans="1:5" x14ac:dyDescent="0.3">
+    <row r="104" spans="1:5" hidden="1" x14ac:dyDescent="0.3">
       <c r="A104" t="s">
         <v>50</v>
       </c>
@@ -20100,7 +22866,7 @@
         <v>40680</v>
       </c>
     </row>
-    <row r="105" spans="1:5" x14ac:dyDescent="0.3">
+    <row r="105" spans="1:5" hidden="1" x14ac:dyDescent="0.3">
       <c r="A105" s="1" t="s">
         <v>63</v>
       </c>
@@ -20120,7 +22886,7 @@
         <v>35859778</v>
       </c>
     </row>
-    <row r="106" spans="1:5" x14ac:dyDescent="0.3">
+    <row r="106" spans="1:5" hidden="1" x14ac:dyDescent="0.3">
       <c r="A106" t="s">
         <v>0</v>
       </c>
@@ -20138,7 +22904,7 @@
         <v>85172</v>
       </c>
     </row>
-    <row r="107" spans="1:5" x14ac:dyDescent="0.3">
+    <row r="107" spans="1:5" hidden="1" x14ac:dyDescent="0.3">
       <c r="A107" t="s">
         <v>1</v>
       </c>
@@ -20156,7 +22922,7 @@
         <v>671282</v>
       </c>
     </row>
-    <row r="108" spans="1:5" x14ac:dyDescent="0.3">
+    <row r="108" spans="1:5" hidden="1" x14ac:dyDescent="0.3">
       <c r="A108" t="s">
         <v>2</v>
       </c>
@@ -20174,7 +22940,7 @@
         <v>399359</v>
       </c>
     </row>
-    <row r="109" spans="1:5" x14ac:dyDescent="0.3">
+    <row r="109" spans="1:5" hidden="1" x14ac:dyDescent="0.3">
       <c r="A109" t="s">
         <v>3</v>
       </c>
@@ -20192,7 +22958,7 @@
         <v>719644</v>
       </c>
     </row>
-    <row r="110" spans="1:5" x14ac:dyDescent="0.3">
+    <row r="110" spans="1:5" hidden="1" x14ac:dyDescent="0.3">
       <c r="A110" t="s">
         <v>4</v>
       </c>
@@ -20210,7 +22976,7 @@
         <v>4558107</v>
       </c>
     </row>
-    <row r="111" spans="1:5" x14ac:dyDescent="0.3">
+    <row r="111" spans="1:5" hidden="1" x14ac:dyDescent="0.3">
       <c r="A111" t="s">
         <v>5</v>
       </c>
@@ -20228,7 +22994,7 @@
         <v>524426</v>
       </c>
     </row>
-    <row r="112" spans="1:5" x14ac:dyDescent="0.3">
+    <row r="112" spans="1:5" hidden="1" x14ac:dyDescent="0.3">
       <c r="A112" t="s">
         <v>6</v>
       </c>
@@ -20246,7 +23012,7 @@
         <v>364027</v>
       </c>
     </row>
-    <row r="113" spans="1:5" x14ac:dyDescent="0.3">
+    <row r="113" spans="1:5" hidden="1" x14ac:dyDescent="0.3">
       <c r="A113" t="s">
         <v>7</v>
       </c>
@@ -20264,7 +23030,7 @@
         <v>93708</v>
       </c>
     </row>
-    <row r="114" spans="1:5" x14ac:dyDescent="0.3">
+    <row r="114" spans="1:5" hidden="1" x14ac:dyDescent="0.3">
       <c r="A114" t="s">
         <v>8</v>
       </c>
@@ -20282,7 +23048,7 @@
         <v>105642</v>
       </c>
     </row>
-    <row r="115" spans="1:5" x14ac:dyDescent="0.3">
+    <row r="115" spans="1:5" hidden="1" x14ac:dyDescent="0.3">
       <c r="A115" t="s">
         <v>9</v>
       </c>
@@ -20300,7 +23066,7 @@
         <v>2303879</v>
       </c>
     </row>
-    <row r="116" spans="1:5" x14ac:dyDescent="0.3">
+    <row r="116" spans="1:5" hidden="1" x14ac:dyDescent="0.3">
       <c r="A116" t="s">
         <v>10</v>
       </c>
@@ -20318,7 +23084,7 @@
         <v>1295769</v>
       </c>
     </row>
-    <row r="117" spans="1:5" x14ac:dyDescent="0.3">
+    <row r="117" spans="1:5" hidden="1" x14ac:dyDescent="0.3">
       <c r="A117" t="s">
         <v>11</v>
       </c>
@@ -20336,7 +23102,7 @@
         <v>153572</v>
       </c>
     </row>
-    <row r="118" spans="1:5" x14ac:dyDescent="0.3">
+    <row r="118" spans="1:5" hidden="1" x14ac:dyDescent="0.3">
       <c r="A118" t="s">
         <v>12</v>
       </c>
@@ -20354,7 +23120,7 @@
         <v>331383</v>
       </c>
     </row>
-    <row r="119" spans="1:5" x14ac:dyDescent="0.3">
+    <row r="119" spans="1:5" hidden="1" x14ac:dyDescent="0.3">
       <c r="A119" t="s">
         <v>13</v>
       </c>
@@ -20372,7 +23138,7 @@
         <v>151079</v>
       </c>
     </row>
-    <row r="120" spans="1:5" x14ac:dyDescent="0.3">
+    <row r="120" spans="1:5" hidden="1" x14ac:dyDescent="0.3">
       <c r="A120" t="s">
         <v>14</v>
       </c>
@@ -20390,7 +23156,7 @@
         <v>1345411</v>
       </c>
     </row>
-    <row r="121" spans="1:5" x14ac:dyDescent="0.3">
+    <row r="121" spans="1:5" hidden="1" x14ac:dyDescent="0.3">
       <c r="A121" t="s">
         <v>15</v>
       </c>
@@ -20408,7 +23174,7 @@
         <v>683558</v>
       </c>
     </row>
-    <row r="122" spans="1:5" x14ac:dyDescent="0.3">
+    <row r="122" spans="1:5" hidden="1" x14ac:dyDescent="0.3">
       <c r="A122" t="s">
         <v>16</v>
       </c>
@@ -20426,7 +23192,7 @@
         <v>275564</v>
       </c>
     </row>
-    <row r="123" spans="1:5" x14ac:dyDescent="0.3">
+    <row r="123" spans="1:5" hidden="1" x14ac:dyDescent="0.3">
       <c r="A123" t="s">
         <v>17</v>
       </c>
@@ -20444,7 +23210,7 @@
         <v>586488</v>
       </c>
     </row>
-    <row r="124" spans="1:5" x14ac:dyDescent="0.3">
+    <row r="124" spans="1:5" hidden="1" x14ac:dyDescent="0.3">
       <c r="A124" t="s">
         <v>18</v>
       </c>
@@ -20462,7 +23228,7 @@
         <v>670589</v>
       </c>
     </row>
-    <row r="125" spans="1:5" x14ac:dyDescent="0.3">
+    <row r="125" spans="1:5" hidden="1" x14ac:dyDescent="0.3">
       <c r="A125" t="s">
         <v>19</v>
       </c>
@@ -20480,7 +23246,7 @@
         <v>675642</v>
       </c>
     </row>
-    <row r="126" spans="1:5" x14ac:dyDescent="0.3">
+    <row r="126" spans="1:5" hidden="1" x14ac:dyDescent="0.3">
       <c r="A126" t="s">
         <v>20</v>
       </c>
@@ -20498,7 +23264,7 @@
         <v>664200</v>
       </c>
     </row>
-    <row r="127" spans="1:5" x14ac:dyDescent="0.3">
+    <row r="127" spans="1:5" hidden="1" x14ac:dyDescent="0.3">
       <c r="A127" t="s">
         <v>21</v>
       </c>
@@ -20516,7 +23282,7 @@
         <v>138365</v>
       </c>
     </row>
-    <row r="128" spans="1:5" x14ac:dyDescent="0.3">
+    <row r="128" spans="1:5" hidden="1" x14ac:dyDescent="0.3">
       <c r="A128" t="s">
         <v>22</v>
       </c>
@@ -20534,7 +23300,7 @@
         <v>881875</v>
       </c>
     </row>
-    <row r="129" spans="1:5" x14ac:dyDescent="0.3">
+    <row r="129" spans="1:5" hidden="1" x14ac:dyDescent="0.3">
       <c r="A129" t="s">
         <v>23</v>
       </c>
@@ -20552,7 +23318,7 @@
         <v>595402</v>
       </c>
     </row>
-    <row r="130" spans="1:5" x14ac:dyDescent="0.3">
+    <row r="130" spans="1:5" hidden="1" x14ac:dyDescent="0.3">
       <c r="A130" t="s">
         <v>24</v>
       </c>
@@ -20570,7 +23336,7 @@
         <v>564663</v>
       </c>
     </row>
-    <row r="131" spans="1:5" x14ac:dyDescent="0.3">
+    <row r="131" spans="1:5" hidden="1" x14ac:dyDescent="0.3">
       <c r="A131" t="s">
         <v>25</v>
       </c>
@@ -20588,7 +23354,7 @@
         <v>391962</v>
       </c>
     </row>
-    <row r="132" spans="1:5" x14ac:dyDescent="0.3">
+    <row r="132" spans="1:5" hidden="1" x14ac:dyDescent="0.3">
       <c r="A132" t="s">
         <v>26</v>
       </c>
@@ -20606,7 +23372,7 @@
         <v>89255</v>
       </c>
     </row>
-    <row r="133" spans="1:5" x14ac:dyDescent="0.3">
+    <row r="133" spans="1:5" hidden="1" x14ac:dyDescent="0.3">
       <c r="A133" t="s">
         <v>27</v>
       </c>
@@ -20624,7 +23390,7 @@
         <v>1402085</v>
       </c>
     </row>
-    <row r="134" spans="1:5" x14ac:dyDescent="0.3">
+    <row r="134" spans="1:5" hidden="1" x14ac:dyDescent="0.3">
       <c r="A134" t="s">
         <v>28</v>
       </c>
@@ -20642,7 +23408,7 @@
         <v>50698</v>
       </c>
     </row>
-    <row r="135" spans="1:5" x14ac:dyDescent="0.3">
+    <row r="135" spans="1:5" hidden="1" x14ac:dyDescent="0.3">
       <c r="A135" t="s">
         <v>29</v>
       </c>
@@ -20660,7 +23426,7 @@
         <v>171311</v>
       </c>
     </row>
-    <row r="136" spans="1:5" x14ac:dyDescent="0.3">
+    <row r="136" spans="1:5" hidden="1" x14ac:dyDescent="0.3">
       <c r="A136" t="s">
         <v>30</v>
       </c>
@@ -20678,7 +23444,7 @@
         <v>85181</v>
       </c>
     </row>
-    <row r="137" spans="1:5" x14ac:dyDescent="0.3">
+    <row r="137" spans="1:5" hidden="1" x14ac:dyDescent="0.3">
       <c r="A137" t="s">
         <v>31</v>
       </c>
@@ -20696,7 +23462,7 @@
         <v>801330</v>
       </c>
     </row>
-    <row r="138" spans="1:5" x14ac:dyDescent="0.3">
+    <row r="138" spans="1:5" hidden="1" x14ac:dyDescent="0.3">
       <c r="A138" t="s">
         <v>32</v>
       </c>
@@ -20714,7 +23480,7 @@
         <v>307319</v>
       </c>
     </row>
-    <row r="139" spans="1:5" x14ac:dyDescent="0.3">
+    <row r="139" spans="1:5" hidden="1" x14ac:dyDescent="0.3">
       <c r="A139" t="s">
         <v>33</v>
       </c>
@@ -20732,7 +23498,7 @@
         <v>314810</v>
       </c>
     </row>
-    <row r="140" spans="1:5" x14ac:dyDescent="0.3">
+    <row r="140" spans="1:5" hidden="1" x14ac:dyDescent="0.3">
       <c r="A140" t="s">
         <v>34</v>
       </c>
@@ -20750,7 +23516,7 @@
         <v>2433605</v>
       </c>
     </row>
-    <row r="141" spans="1:5" x14ac:dyDescent="0.3">
+    <row r="141" spans="1:5" hidden="1" x14ac:dyDescent="0.3">
       <c r="A141" t="s">
         <v>35</v>
       </c>
@@ -20768,7 +23534,7 @@
         <v>1153381</v>
       </c>
     </row>
-    <row r="142" spans="1:5" x14ac:dyDescent="0.3">
+    <row r="142" spans="1:5" hidden="1" x14ac:dyDescent="0.3">
       <c r="A142" t="s">
         <v>36</v>
       </c>
@@ -20786,7 +23552,7 @@
         <v>500957</v>
       </c>
     </row>
-    <row r="143" spans="1:5" x14ac:dyDescent="0.3">
+    <row r="143" spans="1:5" hidden="1" x14ac:dyDescent="0.3">
       <c r="A143" t="s">
         <v>37</v>
       </c>
@@ -20804,7 +23570,7 @@
         <v>469532</v>
       </c>
     </row>
-    <row r="144" spans="1:5" x14ac:dyDescent="0.3">
+    <row r="144" spans="1:5" hidden="1" x14ac:dyDescent="0.3">
       <c r="A144" t="s">
         <v>38</v>
       </c>
@@ -20822,7 +23588,7 @@
         <v>1405664</v>
       </c>
     </row>
-    <row r="145" spans="1:5" x14ac:dyDescent="0.3">
+    <row r="145" spans="1:5" hidden="1" x14ac:dyDescent="0.3">
       <c r="A145" t="s">
         <v>39</v>
       </c>
@@ -20840,7 +23606,7 @@
         <v>113265</v>
       </c>
     </row>
-    <row r="146" spans="1:5" x14ac:dyDescent="0.3">
+    <row r="146" spans="1:5" hidden="1" x14ac:dyDescent="0.3">
       <c r="A146" t="s">
         <v>40</v>
       </c>
@@ -20858,7 +23624,7 @@
         <v>599752</v>
       </c>
     </row>
-    <row r="147" spans="1:5" x14ac:dyDescent="0.3">
+    <row r="147" spans="1:5" hidden="1" x14ac:dyDescent="0.3">
       <c r="A147" t="s">
         <v>41</v>
       </c>
@@ -20876,7 +23642,7 @@
         <v>76579</v>
       </c>
     </row>
-    <row r="148" spans="1:5" x14ac:dyDescent="0.3">
+    <row r="148" spans="1:5" hidden="1" x14ac:dyDescent="0.3">
       <c r="A148" t="s">
         <v>42</v>
       </c>
@@ -20894,7 +23660,7 @@
         <v>828632</v>
       </c>
     </row>
-    <row r="149" spans="1:5" x14ac:dyDescent="0.3">
+    <row r="149" spans="1:5" hidden="1" x14ac:dyDescent="0.3">
       <c r="A149" t="s">
         <v>43</v>
       </c>
@@ -20912,7 +23678,7 @@
         <v>3038945</v>
       </c>
     </row>
-    <row r="150" spans="1:5" x14ac:dyDescent="0.3">
+    <row r="150" spans="1:5" hidden="1" x14ac:dyDescent="0.3">
       <c r="A150" t="s">
         <v>44</v>
       </c>
@@ -20930,7 +23696,7 @@
         <v>163819</v>
       </c>
     </row>
-    <row r="151" spans="1:5" x14ac:dyDescent="0.3">
+    <row r="151" spans="1:5" hidden="1" x14ac:dyDescent="0.3">
       <c r="A151" t="s">
         <v>45</v>
       </c>
@@ -20948,7 +23714,7 @@
         <v>793061</v>
       </c>
     </row>
-    <row r="152" spans="1:5" x14ac:dyDescent="0.3">
+    <row r="152" spans="1:5" hidden="1" x14ac:dyDescent="0.3">
       <c r="A152" t="s">
         <v>46</v>
       </c>
@@ -20966,7 +23732,7 @@
         <v>57249</v>
       </c>
     </row>
-    <row r="153" spans="1:5" x14ac:dyDescent="0.3">
+    <row r="153" spans="1:5" hidden="1" x14ac:dyDescent="0.3">
       <c r="A153" t="s">
         <v>47</v>
       </c>
@@ -20984,7 +23750,7 @@
         <v>816314</v>
       </c>
     </row>
-    <row r="154" spans="1:5" x14ac:dyDescent="0.3">
+    <row r="154" spans="1:5" hidden="1" x14ac:dyDescent="0.3">
       <c r="A154" t="s">
         <v>48</v>
       </c>
@@ -21002,7 +23768,7 @@
         <v>536303</v>
       </c>
     </row>
-    <row r="155" spans="1:5" x14ac:dyDescent="0.3">
+    <row r="155" spans="1:5" hidden="1" x14ac:dyDescent="0.3">
       <c r="A155" t="s">
         <v>49</v>
       </c>
@@ -21020,7 +23786,7 @@
         <v>193963</v>
       </c>
     </row>
-    <row r="156" spans="1:5" x14ac:dyDescent="0.3">
+    <row r="156" spans="1:5" hidden="1" x14ac:dyDescent="0.3">
       <c r="A156" t="s">
         <v>50</v>
       </c>
@@ -21038,7 +23804,7 @@
         <v>40000</v>
       </c>
     </row>
-    <row r="157" spans="1:5" x14ac:dyDescent="0.3">
+    <row r="157" spans="1:5" hidden="1" x14ac:dyDescent="0.3">
       <c r="A157" s="1" t="s">
         <v>63</v>
       </c>
@@ -21058,7 +23824,7 @@
         <v>35673778</v>
       </c>
     </row>
-    <row r="158" spans="1:5" x14ac:dyDescent="0.3">
+    <row r="158" spans="1:5" hidden="1" x14ac:dyDescent="0.3">
       <c r="A158" t="s">
         <v>0</v>
       </c>
@@ -21076,7 +23842,7 @@
         <v>84644</v>
       </c>
     </row>
-    <row r="159" spans="1:5" x14ac:dyDescent="0.3">
+    <row r="159" spans="1:5" hidden="1" x14ac:dyDescent="0.3">
       <c r="A159" t="s">
         <v>1</v>
       </c>
@@ -21094,7 +23860,7 @@
         <v>671336</v>
       </c>
     </row>
-    <row r="160" spans="1:5" x14ac:dyDescent="0.3">
+    <row r="160" spans="1:5" hidden="1" x14ac:dyDescent="0.3">
       <c r="A160" t="s">
         <v>2</v>
       </c>
@@ -21112,7 +23878,7 @@
         <v>399211</v>
       </c>
     </row>
-    <row r="161" spans="1:5" x14ac:dyDescent="0.3">
+    <row r="161" spans="1:5" hidden="1" x14ac:dyDescent="0.3">
       <c r="A161" t="s">
         <v>3</v>
       </c>
@@ -21130,7 +23896,7 @@
         <v>717657</v>
       </c>
     </row>
-    <row r="162" spans="1:5" x14ac:dyDescent="0.3">
+    <row r="162" spans="1:5" hidden="1" x14ac:dyDescent="0.3">
       <c r="A162" t="s">
         <v>4</v>
       </c>
@@ -21148,7 +23914,7 @@
         <v>4522491</v>
       </c>
     </row>
-    <row r="163" spans="1:5" x14ac:dyDescent="0.3">
+    <row r="163" spans="1:5" hidden="1" x14ac:dyDescent="0.3">
       <c r="A163" t="s">
         <v>5</v>
       </c>
@@ -21166,7 +23932,7 @@
         <v>524485</v>
       </c>
     </row>
-    <row r="164" spans="1:5" x14ac:dyDescent="0.3">
+    <row r="164" spans="1:5" hidden="1" x14ac:dyDescent="0.3">
       <c r="A164" t="s">
         <v>6</v>
       </c>
@@ -21184,7 +23950,7 @@
         <v>363652</v>
       </c>
     </row>
-    <row r="165" spans="1:5" x14ac:dyDescent="0.3">
+    <row r="165" spans="1:5" hidden="1" x14ac:dyDescent="0.3">
       <c r="A165" t="s">
         <v>7</v>
       </c>
@@ -21202,7 +23968,7 @@
         <v>93214</v>
       </c>
     </row>
-    <row r="166" spans="1:5" x14ac:dyDescent="0.3">
+    <row r="166" spans="1:5" hidden="1" x14ac:dyDescent="0.3">
       <c r="A166" t="s">
         <v>8</v>
       </c>
@@ -21220,7 +23986,7 @@
         <v>105358</v>
       </c>
     </row>
-    <row r="167" spans="1:5" x14ac:dyDescent="0.3">
+    <row r="167" spans="1:5" hidden="1" x14ac:dyDescent="0.3">
       <c r="A167" t="s">
         <v>9</v>
       </c>
@@ -21238,7 +24004,7 @@
         <v>2294379</v>
       </c>
     </row>
-    <row r="168" spans="1:5" x14ac:dyDescent="0.3">
+    <row r="168" spans="1:5" hidden="1" x14ac:dyDescent="0.3">
       <c r="A168" t="s">
         <v>10</v>
       </c>
@@ -21256,7 +24022,7 @@
         <v>1294177</v>
       </c>
     </row>
-    <row r="169" spans="1:5" x14ac:dyDescent="0.3">
+    <row r="169" spans="1:5" hidden="1" x14ac:dyDescent="0.3">
       <c r="A169" t="s">
         <v>11</v>
       </c>
@@ -21274,7 +24040,7 @@
         <v>153757</v>
       </c>
     </row>
-    <row r="170" spans="1:5" x14ac:dyDescent="0.3">
+    <row r="170" spans="1:5" hidden="1" x14ac:dyDescent="0.3">
       <c r="A170" t="s">
         <v>12</v>
       </c>
@@ -21292,7 +24058,7 @@
         <v>332348</v>
       </c>
     </row>
-    <row r="171" spans="1:5" x14ac:dyDescent="0.3">
+    <row r="171" spans="1:5" hidden="1" x14ac:dyDescent="0.3">
       <c r="A171" t="s">
         <v>13</v>
       </c>
@@ -21310,7 +24076,7 @@
         <v>152742</v>
       </c>
     </row>
-    <row r="172" spans="1:5" x14ac:dyDescent="0.3">
+    <row r="172" spans="1:5" hidden="1" x14ac:dyDescent="0.3">
       <c r="A172" t="s">
         <v>14</v>
       </c>
@@ -21328,7 +24094,7 @@
         <v>1340538</v>
       </c>
     </row>
-    <row r="173" spans="1:5" x14ac:dyDescent="0.3">
+    <row r="173" spans="1:5" hidden="1" x14ac:dyDescent="0.3">
       <c r="A173" t="s">
         <v>15</v>
       </c>
@@ -21346,7 +24112,7 @@
         <v>672154</v>
       </c>
     </row>
-    <row r="174" spans="1:5" x14ac:dyDescent="0.3">
+    <row r="174" spans="1:5" hidden="1" x14ac:dyDescent="0.3">
       <c r="A174" t="s">
         <v>16</v>
       </c>
@@ -21364,7 +24130,7 @@
         <v>275752</v>
       </c>
     </row>
-    <row r="175" spans="1:5" x14ac:dyDescent="0.3">
+    <row r="175" spans="1:5" hidden="1" x14ac:dyDescent="0.3">
       <c r="A175" t="s">
         <v>17</v>
       </c>
@@ -21382,7 +24148,7 @@
         <v>576091</v>
       </c>
     </row>
-    <row r="176" spans="1:5" x14ac:dyDescent="0.3">
+    <row r="176" spans="1:5" hidden="1" x14ac:dyDescent="0.3">
       <c r="A176" t="s">
         <v>18</v>
       </c>
@@ -21400,7 +24166,7 @@
         <v>669409</v>
       </c>
     </row>
-    <row r="177" spans="1:5" x14ac:dyDescent="0.3">
+    <row r="177" spans="1:5" hidden="1" x14ac:dyDescent="0.3">
       <c r="A177" t="s">
         <v>19</v>
       </c>
@@ -21418,7 +24184,7 @@
         <v>669209</v>
       </c>
     </row>
-    <row r="178" spans="1:5" x14ac:dyDescent="0.3">
+    <row r="178" spans="1:5" hidden="1" x14ac:dyDescent="0.3">
       <c r="A178" t="s">
         <v>20</v>
       </c>
@@ -21436,7 +24202,7 @@
         <v>664957</v>
       </c>
     </row>
-    <row r="179" spans="1:5" x14ac:dyDescent="0.3">
+    <row r="179" spans="1:5" hidden="1" x14ac:dyDescent="0.3">
       <c r="A179" t="s">
         <v>21</v>
       </c>
@@ -21454,7 +24220,7 @@
         <v>138277</v>
       </c>
     </row>
-    <row r="180" spans="1:5" x14ac:dyDescent="0.3">
+    <row r="180" spans="1:5" hidden="1" x14ac:dyDescent="0.3">
       <c r="A180" t="s">
         <v>22</v>
       </c>
@@ -21472,7 +24238,7 @@
         <v>882051</v>
       </c>
     </row>
-    <row r="181" spans="1:5" x14ac:dyDescent="0.3">
+    <row r="181" spans="1:5" hidden="1" x14ac:dyDescent="0.3">
       <c r="A181" t="s">
         <v>23</v>
       </c>
@@ -21490,7 +24256,7 @@
         <v>595558</v>
       </c>
     </row>
-    <row r="182" spans="1:5" x14ac:dyDescent="0.3">
+    <row r="182" spans="1:5" hidden="1" x14ac:dyDescent="0.3">
       <c r="A182" t="s">
         <v>24</v>
       </c>
@@ -21508,7 +24274,7 @@
         <v>567261</v>
       </c>
     </row>
-    <row r="183" spans="1:5" x14ac:dyDescent="0.3">
+    <row r="183" spans="1:5" hidden="1" x14ac:dyDescent="0.3">
       <c r="A183" t="s">
         <v>25</v>
       </c>
@@ -21526,7 +24292,7 @@
         <v>390776</v>
       </c>
     </row>
-    <row r="184" spans="1:5" x14ac:dyDescent="0.3">
+    <row r="184" spans="1:5" hidden="1" x14ac:dyDescent="0.3">
       <c r="A184" t="s">
         <v>26</v>
       </c>
@@ -21544,7 +24310,7 @@
         <v>89325</v>
       </c>
     </row>
-    <row r="185" spans="1:5" x14ac:dyDescent="0.3">
+    <row r="185" spans="1:5" hidden="1" x14ac:dyDescent="0.3">
       <c r="A185" t="s">
         <v>27</v>
       </c>
@@ -21562,7 +24328,7 @@
         <v>1392899</v>
       </c>
     </row>
-    <row r="186" spans="1:5" x14ac:dyDescent="0.3">
+    <row r="186" spans="1:5" hidden="1" x14ac:dyDescent="0.3">
       <c r="A186" t="s">
         <v>28</v>
       </c>
@@ -21580,7 +24346,7 @@
         <v>50731</v>
       </c>
     </row>
-    <row r="187" spans="1:5" x14ac:dyDescent="0.3">
+    <row r="187" spans="1:5" hidden="1" x14ac:dyDescent="0.3">
       <c r="A187" t="s">
         <v>29</v>
       </c>
@@ -21598,7 +24364,7 @@
         <v>171752</v>
       </c>
     </row>
-    <row r="188" spans="1:5" x14ac:dyDescent="0.3">
+    <row r="188" spans="1:5" hidden="1" x14ac:dyDescent="0.3">
       <c r="A188" t="s">
         <v>30</v>
       </c>
@@ -21616,7 +24382,7 @@
         <v>85149</v>
       </c>
     </row>
-    <row r="189" spans="1:5" x14ac:dyDescent="0.3">
+    <row r="189" spans="1:5" hidden="1" x14ac:dyDescent="0.3">
       <c r="A189" t="s">
         <v>31</v>
       </c>
@@ -21634,7 +24400,7 @@
         <v>801978</v>
       </c>
     </row>
-    <row r="190" spans="1:5" x14ac:dyDescent="0.3">
+    <row r="190" spans="1:5" hidden="1" x14ac:dyDescent="0.3">
       <c r="A190" t="s">
         <v>32</v>
       </c>
@@ -21652,7 +24418,7 @@
         <v>307046</v>
       </c>
     </row>
-    <row r="191" spans="1:5" x14ac:dyDescent="0.3">
+    <row r="191" spans="1:5" hidden="1" x14ac:dyDescent="0.3">
       <c r="A191" t="s">
         <v>33</v>
       </c>
@@ -21670,7 +24436,7 @@
         <v>326058</v>
       </c>
     </row>
-    <row r="192" spans="1:5" x14ac:dyDescent="0.3">
+    <row r="192" spans="1:5" hidden="1" x14ac:dyDescent="0.3">
       <c r="A192" t="s">
         <v>34</v>
       </c>
@@ -21688,7 +24454,7 @@
         <v>2434237</v>
       </c>
     </row>
-    <row r="193" spans="1:5" x14ac:dyDescent="0.3">
+    <row r="193" spans="1:5" hidden="1" x14ac:dyDescent="0.3">
       <c r="A193" t="s">
         <v>35</v>
       </c>
@@ -21706,7 +24472,7 @@
         <v>1142311</v>
       </c>
     </row>
-    <row r="194" spans="1:5" x14ac:dyDescent="0.3">
+    <row r="194" spans="1:5" hidden="1" x14ac:dyDescent="0.3">
       <c r="A194" t="s">
         <v>36</v>
       </c>
@@ -21724,7 +24490,7 @@
         <v>501776</v>
       </c>
     </row>
-    <row r="195" spans="1:5" x14ac:dyDescent="0.3">
+    <row r="195" spans="1:5" hidden="1" x14ac:dyDescent="0.3">
       <c r="A195" t="s">
         <v>37</v>
       </c>
@@ -21742,7 +24508,7 @@
         <v>469480</v>
       </c>
     </row>
-    <row r="196" spans="1:5" x14ac:dyDescent="0.3">
+    <row r="196" spans="1:5" hidden="1" x14ac:dyDescent="0.3">
       <c r="A196" t="s">
         <v>38</v>
       </c>
@@ -21760,7 +24526,7 @@
         <v>1407178</v>
       </c>
     </row>
-    <row r="197" spans="1:5" x14ac:dyDescent="0.3">
+    <row r="197" spans="1:5" hidden="1" x14ac:dyDescent="0.3">
       <c r="A197" t="s">
         <v>39</v>
       </c>
@@ -21778,7 +24544,7 @@
         <v>117228</v>
       </c>
     </row>
-    <row r="198" spans="1:5" x14ac:dyDescent="0.3">
+    <row r="198" spans="1:5" hidden="1" x14ac:dyDescent="0.3">
       <c r="A198" t="s">
         <v>40</v>
       </c>
@@ -21796,7 +24562,7 @@
         <v>597283</v>
       </c>
     </row>
-    <row r="199" spans="1:5" x14ac:dyDescent="0.3">
+    <row r="199" spans="1:5" hidden="1" x14ac:dyDescent="0.3">
       <c r="A199" t="s">
         <v>41</v>
       </c>
@@ -21814,7 +24580,7 @@
         <v>77344</v>
       </c>
     </row>
-    <row r="200" spans="1:5" x14ac:dyDescent="0.3">
+    <row r="200" spans="1:5" hidden="1" x14ac:dyDescent="0.3">
       <c r="A200" t="s">
         <v>42</v>
       </c>
@@ -21832,7 +24598,7 @@
         <v>821979</v>
       </c>
     </row>
-    <row r="201" spans="1:5" x14ac:dyDescent="0.3">
+    <row r="201" spans="1:5" hidden="1" x14ac:dyDescent="0.3">
       <c r="A201" t="s">
         <v>43</v>
       </c>
@@ -21850,7 +24616,7 @@
         <v>3028185</v>
       </c>
     </row>
-    <row r="202" spans="1:5" x14ac:dyDescent="0.3">
+    <row r="202" spans="1:5" hidden="1" x14ac:dyDescent="0.3">
       <c r="A202" t="s">
         <v>44</v>
       </c>
@@ -21868,7 +24634,7 @@
         <v>163026</v>
       </c>
     </row>
-    <row r="203" spans="1:5" x14ac:dyDescent="0.3">
+    <row r="203" spans="1:5" hidden="1" x14ac:dyDescent="0.3">
       <c r="A203" t="s">
         <v>45</v>
       </c>
@@ -21886,7 +24652,7 @@
         <v>791972</v>
       </c>
     </row>
-    <row r="204" spans="1:5" x14ac:dyDescent="0.3">
+    <row r="204" spans="1:5" hidden="1" x14ac:dyDescent="0.3">
       <c r="A204" t="s">
         <v>46</v>
       </c>
@@ -21904,7 +24670,7 @@
         <v>56962</v>
       </c>
     </row>
-    <row r="205" spans="1:5" x14ac:dyDescent="0.3">
+    <row r="205" spans="1:5" hidden="1" x14ac:dyDescent="0.3">
       <c r="A205" t="s">
         <v>47</v>
       </c>
@@ -21922,7 +24688,7 @@
         <v>815121</v>
       </c>
     </row>
-    <row r="206" spans="1:5" x14ac:dyDescent="0.3">
+    <row r="206" spans="1:5" hidden="1" x14ac:dyDescent="0.3">
       <c r="A206" t="s">
         <v>48</v>
       </c>
@@ -21940,7 +24706,7 @@
         <v>535481</v>
       </c>
     </row>
-    <row r="207" spans="1:5" x14ac:dyDescent="0.3">
+    <row r="207" spans="1:5" hidden="1" x14ac:dyDescent="0.3">
       <c r="A207" t="s">
         <v>49</v>
       </c>
@@ -21958,7 +24724,7 @@
         <v>193025</v>
       </c>
     </row>
-    <row r="208" spans="1:5" x14ac:dyDescent="0.3">
+    <row r="208" spans="1:5" hidden="1" x14ac:dyDescent="0.3">
       <c r="A208" t="s">
         <v>50</v>
       </c>
@@ -21976,7 +24742,7 @@
         <v>41865</v>
       </c>
     </row>
-    <row r="209" spans="1:5" x14ac:dyDescent="0.3">
+    <row r="209" spans="1:5" hidden="1" x14ac:dyDescent="0.3">
       <c r="A209" s="1" t="s">
         <v>63</v>
       </c>
@@ -21996,7 +24762,7 @@
         <v>35570875</v>
       </c>
     </row>
-    <row r="210" spans="1:5" x14ac:dyDescent="0.3">
+    <row r="210" spans="1:5" hidden="1" x14ac:dyDescent="0.3">
       <c r="A210" t="s">
         <v>0</v>
       </c>
@@ -22014,7 +24780,7 @@
         <v>84559</v>
       </c>
     </row>
-    <row r="211" spans="1:5" x14ac:dyDescent="0.3">
+    <row r="211" spans="1:5" hidden="1" x14ac:dyDescent="0.3">
       <c r="A211" t="s">
         <v>1</v>
       </c>
@@ -22032,7 +24798,7 @@
         <v>670794</v>
       </c>
     </row>
-    <row r="212" spans="1:5" x14ac:dyDescent="0.3">
+    <row r="212" spans="1:5" hidden="1" x14ac:dyDescent="0.3">
       <c r="A212" t="s">
         <v>2</v>
       </c>
@@ -22050,7 +24816,7 @@
         <v>398851</v>
       </c>
     </row>
-    <row r="213" spans="1:5" x14ac:dyDescent="0.3">
+    <row r="213" spans="1:5" hidden="1" x14ac:dyDescent="0.3">
       <c r="A213" t="s">
         <v>3</v>
       </c>
@@ -22068,7 +24834,7 @@
         <v>713597</v>
       </c>
     </row>
-    <row r="214" spans="1:5" x14ac:dyDescent="0.3">
+    <row r="214" spans="1:5" hidden="1" x14ac:dyDescent="0.3">
       <c r="A214" t="s">
         <v>4</v>
       </c>
@@ -22086,7 +24852,7 @@
         <v>4487712</v>
       </c>
     </row>
-    <row r="215" spans="1:5" x14ac:dyDescent="0.3">
+    <row r="215" spans="1:5" hidden="1" x14ac:dyDescent="0.3">
       <c r="A215" t="s">
         <v>5</v>
       </c>
@@ -22104,7 +24870,7 @@
         <v>526518</v>
       </c>
     </row>
-    <row r="216" spans="1:5" x14ac:dyDescent="0.3">
+    <row r="216" spans="1:5" hidden="1" x14ac:dyDescent="0.3">
       <c r="A216" t="s">
         <v>6</v>
       </c>
@@ -22122,7 +24888,7 @@
         <v>363019</v>
       </c>
     </row>
-    <row r="217" spans="1:5" x14ac:dyDescent="0.3">
+    <row r="217" spans="1:5" hidden="1" x14ac:dyDescent="0.3">
       <c r="A217" t="s">
         <v>7</v>
       </c>
@@ -22140,7 +24906,7 @@
         <v>92804</v>
       </c>
     </row>
-    <row r="218" spans="1:5" x14ac:dyDescent="0.3">
+    <row r="218" spans="1:5" hidden="1" x14ac:dyDescent="0.3">
       <c r="A218" t="s">
         <v>8</v>
       </c>
@@ -22158,7 +24924,7 @@
         <v>104633</v>
       </c>
     </row>
-    <row r="219" spans="1:5" x14ac:dyDescent="0.3">
+    <row r="219" spans="1:5" hidden="1" x14ac:dyDescent="0.3">
       <c r="A219" t="s">
         <v>9</v>
       </c>
@@ -22176,7 +24942,7 @@
         <v>2294707</v>
       </c>
     </row>
-    <row r="220" spans="1:5" x14ac:dyDescent="0.3">
+    <row r="220" spans="1:5" hidden="1" x14ac:dyDescent="0.3">
       <c r="A220" t="s">
         <v>10</v>
       </c>
@@ -22194,7 +24960,7 @@
         <v>1289530</v>
       </c>
     </row>
-    <row r="221" spans="1:5" x14ac:dyDescent="0.3">
+    <row r="221" spans="1:5" hidden="1" x14ac:dyDescent="0.3">
       <c r="A221" t="s">
         <v>11</v>
       </c>
@@ -22212,7 +24978,7 @@
         <v>154830</v>
       </c>
     </row>
-    <row r="222" spans="1:5" x14ac:dyDescent="0.3">
+    <row r="222" spans="1:5" hidden="1" x14ac:dyDescent="0.3">
       <c r="A222" t="s">
         <v>12</v>
       </c>
@@ -22230,7 +24996,7 @@
         <v>331978</v>
       </c>
     </row>
-    <row r="223" spans="1:5" x14ac:dyDescent="0.3">
+    <row r="223" spans="1:5" hidden="1" x14ac:dyDescent="0.3">
       <c r="A223" t="s">
         <v>13</v>
       </c>
@@ -22248,7 +25014,7 @@
         <v>151728</v>
       </c>
     </row>
-    <row r="224" spans="1:5" x14ac:dyDescent="0.3">
+    <row r="224" spans="1:5" hidden="1" x14ac:dyDescent="0.3">
       <c r="A224" t="s">
         <v>14</v>
       </c>
@@ -22266,7 +25032,7 @@
         <v>1335551</v>
       </c>
     </row>
-    <row r="225" spans="1:5" x14ac:dyDescent="0.3">
+    <row r="225" spans="1:5" hidden="1" x14ac:dyDescent="0.3">
       <c r="A225" t="s">
         <v>15</v>
       </c>
@@ -22284,7 +25050,7 @@
         <v>659235</v>
       </c>
     </row>
-    <row r="226" spans="1:5" x14ac:dyDescent="0.3">
+    <row r="226" spans="1:5" hidden="1" x14ac:dyDescent="0.3">
       <c r="A226" t="s">
         <v>16</v>
       </c>
@@ -22302,7 +25068,7 @@
         <v>270959</v>
       </c>
     </row>
-    <row r="227" spans="1:5" x14ac:dyDescent="0.3">
+    <row r="227" spans="1:5" hidden="1" x14ac:dyDescent="0.3">
       <c r="A227" t="s">
         <v>17</v>
       </c>
@@ -22320,7 +25086,7 @@
         <v>566149</v>
       </c>
     </row>
-    <row r="228" spans="1:5" x14ac:dyDescent="0.3">
+    <row r="228" spans="1:5" hidden="1" x14ac:dyDescent="0.3">
       <c r="A228" t="s">
         <v>18</v>
       </c>
@@ -22338,7 +25104,7 @@
         <v>646884</v>
       </c>
     </row>
-    <row r="229" spans="1:5" x14ac:dyDescent="0.3">
+    <row r="229" spans="1:5" hidden="1" x14ac:dyDescent="0.3">
       <c r="A229" t="s">
         <v>19</v>
       </c>
@@ -22356,7 +25122,7 @@
         <v>662258</v>
       </c>
     </row>
-    <row r="230" spans="1:5" x14ac:dyDescent="0.3">
+    <row r="230" spans="1:5" hidden="1" x14ac:dyDescent="0.3">
       <c r="A230" t="s">
         <v>20</v>
       </c>
@@ -22374,7 +25140,7 @@
         <v>663770</v>
       </c>
     </row>
-    <row r="231" spans="1:5" x14ac:dyDescent="0.3">
+    <row r="231" spans="1:5" hidden="1" x14ac:dyDescent="0.3">
       <c r="A231" t="s">
         <v>21</v>
       </c>
@@ -22392,7 +25158,7 @@
         <v>138048</v>
       </c>
     </row>
-    <row r="232" spans="1:5" x14ac:dyDescent="0.3">
+    <row r="232" spans="1:5" hidden="1" x14ac:dyDescent="0.3">
       <c r="A232" t="s">
         <v>22</v>
       </c>
@@ -22410,7 +25176,7 @@
         <v>873412</v>
       </c>
     </row>
-    <row r="233" spans="1:5" x14ac:dyDescent="0.3">
+    <row r="233" spans="1:5" hidden="1" x14ac:dyDescent="0.3">
       <c r="A233" t="s">
         <v>23</v>
       </c>
@@ -22428,7 +25194,7 @@
         <v>594879</v>
       </c>
     </row>
-    <row r="234" spans="1:5" x14ac:dyDescent="0.3">
+    <row r="234" spans="1:5" hidden="1" x14ac:dyDescent="0.3">
       <c r="A234" t="s">
         <v>24</v>
       </c>
@@ -22446,7 +25212,7 @@
         <v>566397</v>
       </c>
     </row>
-    <row r="235" spans="1:5" x14ac:dyDescent="0.3">
+    <row r="235" spans="1:5" hidden="1" x14ac:dyDescent="0.3">
       <c r="A235" t="s">
         <v>25</v>
       </c>
@@ -22464,7 +25230,7 @@
         <v>389580</v>
       </c>
     </row>
-    <row r="236" spans="1:5" x14ac:dyDescent="0.3">
+    <row r="236" spans="1:5" hidden="1" x14ac:dyDescent="0.3">
       <c r="A236" t="s">
         <v>26</v>
       </c>
@@ -22482,7 +25248,7 @@
         <v>87088</v>
       </c>
     </row>
-    <row r="237" spans="1:5" x14ac:dyDescent="0.3">
+    <row r="237" spans="1:5" hidden="1" x14ac:dyDescent="0.3">
       <c r="A237" t="s">
         <v>27</v>
       </c>
@@ -22500,7 +25266,7 @@
         <v>1380297</v>
       </c>
     </row>
-    <row r="238" spans="1:5" x14ac:dyDescent="0.3">
+    <row r="238" spans="1:5" hidden="1" x14ac:dyDescent="0.3">
       <c r="A238" t="s">
         <v>28</v>
       </c>
@@ -22518,7 +25284,7 @@
         <v>50654</v>
       </c>
     </row>
-    <row r="239" spans="1:5" x14ac:dyDescent="0.3">
+    <row r="239" spans="1:5" hidden="1" x14ac:dyDescent="0.3">
       <c r="A239" t="s">
         <v>29</v>
       </c>
@@ -22536,7 +25302,7 @@
         <v>169659</v>
       </c>
     </row>
-    <row r="240" spans="1:5" x14ac:dyDescent="0.3">
+    <row r="240" spans="1:5" hidden="1" x14ac:dyDescent="0.3">
       <c r="A240" t="s">
         <v>30</v>
       </c>
@@ -22554,7 +25320,7 @@
         <v>84991</v>
       </c>
     </row>
-    <row r="241" spans="1:5" x14ac:dyDescent="0.3">
+    <row r="241" spans="1:5" hidden="1" x14ac:dyDescent="0.3">
       <c r="A241" t="s">
         <v>31</v>
       </c>
@@ -22572,7 +25338,7 @@
         <v>808680</v>
       </c>
     </row>
-    <row r="242" spans="1:5" x14ac:dyDescent="0.3">
+    <row r="242" spans="1:5" hidden="1" x14ac:dyDescent="0.3">
       <c r="A242" t="s">
         <v>32</v>
       </c>
@@ -22590,7 +25356,7 @@
         <v>306682</v>
       </c>
     </row>
-    <row r="243" spans="1:5" x14ac:dyDescent="0.3">
+    <row r="243" spans="1:5" hidden="1" x14ac:dyDescent="0.3">
       <c r="A243" t="s">
         <v>33</v>
       </c>
@@ -22608,7 +25374,7 @@
         <v>312777</v>
       </c>
     </row>
-    <row r="244" spans="1:5" x14ac:dyDescent="0.3">
+    <row r="244" spans="1:5" hidden="1" x14ac:dyDescent="0.3">
       <c r="A244" t="s">
         <v>34</v>
       </c>
@@ -22626,7 +25392,7 @@
         <v>2429359</v>
       </c>
     </row>
-    <row r="245" spans="1:5" x14ac:dyDescent="0.3">
+    <row r="245" spans="1:5" hidden="1" x14ac:dyDescent="0.3">
       <c r="A245" t="s">
         <v>35</v>
       </c>
@@ -22644,7 +25410,7 @@
         <v>1129766</v>
       </c>
     </row>
-    <row r="246" spans="1:5" x14ac:dyDescent="0.3">
+    <row r="246" spans="1:5" hidden="1" x14ac:dyDescent="0.3">
       <c r="A246" t="s">
         <v>36</v>
       </c>
@@ -22662,7 +25428,7 @@
         <v>502677</v>
       </c>
     </row>
-    <row r="247" spans="1:5" x14ac:dyDescent="0.3">
+    <row r="247" spans="1:5" hidden="1" x14ac:dyDescent="0.3">
       <c r="A247" t="s">
         <v>37</v>
       </c>
@@ -22680,7 +25446,7 @@
         <v>467994</v>
       </c>
     </row>
-    <row r="248" spans="1:5" x14ac:dyDescent="0.3">
+    <row r="248" spans="1:5" hidden="1" x14ac:dyDescent="0.3">
       <c r="A248" t="s">
         <v>38</v>
       </c>
@@ -22698,7 +25464,7 @@
         <v>1400429</v>
       </c>
     </row>
-    <row r="249" spans="1:5" x14ac:dyDescent="0.3">
+    <row r="249" spans="1:5" hidden="1" x14ac:dyDescent="0.3">
       <c r="A249" t="s">
         <v>39</v>
       </c>
@@ -22716,7 +25482,7 @@
         <v>116498</v>
       </c>
     </row>
-    <row r="250" spans="1:5" x14ac:dyDescent="0.3">
+    <row r="250" spans="1:5" hidden="1" x14ac:dyDescent="0.3">
       <c r="A250" t="s">
         <v>40</v>
       </c>
@@ -22734,7 +25500,7 @@
         <v>597302</v>
       </c>
     </row>
-    <row r="251" spans="1:5" x14ac:dyDescent="0.3">
+    <row r="251" spans="1:5" hidden="1" x14ac:dyDescent="0.3">
       <c r="A251" t="s">
         <v>41</v>
       </c>
@@ -22752,7 +25518,7 @@
         <v>76398</v>
       </c>
     </row>
-    <row r="252" spans="1:5" x14ac:dyDescent="0.3">
+    <row r="252" spans="1:5" hidden="1" x14ac:dyDescent="0.3">
       <c r="A252" t="s">
         <v>42</v>
       </c>
@@ -22770,7 +25536,7 @@
         <v>822309</v>
       </c>
     </row>
-    <row r="253" spans="1:5" x14ac:dyDescent="0.3">
+    <row r="253" spans="1:5" hidden="1" x14ac:dyDescent="0.3">
       <c r="A253" t="s">
         <v>43</v>
       </c>
@@ -22788,7 +25554,7 @@
         <v>3016772</v>
       </c>
     </row>
-    <row r="254" spans="1:5" x14ac:dyDescent="0.3">
+    <row r="254" spans="1:5" hidden="1" x14ac:dyDescent="0.3">
       <c r="A254" t="s">
         <v>44</v>
       </c>
@@ -22806,7 +25572,7 @@
         <v>161719</v>
       </c>
     </row>
-    <row r="255" spans="1:5" x14ac:dyDescent="0.3">
+    <row r="255" spans="1:5" hidden="1" x14ac:dyDescent="0.3">
       <c r="A255" t="s">
         <v>45</v>
       </c>
@@ -22824,7 +25590,7 @@
         <v>789449</v>
       </c>
     </row>
-    <row r="256" spans="1:5" x14ac:dyDescent="0.3">
+    <row r="256" spans="1:5" hidden="1" x14ac:dyDescent="0.3">
       <c r="A256" t="s">
         <v>46</v>
       </c>
@@ -22842,7 +25608,7 @@
         <v>56723</v>
       </c>
     </row>
-    <row r="257" spans="1:5" x14ac:dyDescent="0.3">
+    <row r="257" spans="1:5" hidden="1" x14ac:dyDescent="0.3">
       <c r="A257" t="s">
         <v>47</v>
       </c>
@@ -22860,7 +25626,7 @@
         <v>814620</v>
       </c>
     </row>
-    <row r="258" spans="1:5" x14ac:dyDescent="0.3">
+    <row r="258" spans="1:5" hidden="1" x14ac:dyDescent="0.3">
       <c r="A258" t="s">
         <v>48</v>
       </c>
@@ -22878,7 +25644,7 @@
         <v>532571</v>
       </c>
     </row>
-    <row r="259" spans="1:5" x14ac:dyDescent="0.3">
+    <row r="259" spans="1:5" hidden="1" x14ac:dyDescent="0.3">
       <c r="A259" t="s">
         <v>49</v>
       </c>
@@ -22896,7 +25662,7 @@
         <v>192819</v>
       </c>
     </row>
-    <row r="260" spans="1:5" x14ac:dyDescent="0.3">
+    <row r="260" spans="1:5" hidden="1" x14ac:dyDescent="0.3">
       <c r="A260" t="s">
         <v>50</v>
       </c>
@@ -22914,7 +25680,7 @@
         <v>40835</v>
       </c>
     </row>
-    <row r="261" spans="1:5" x14ac:dyDescent="0.3">
+    <row r="261" spans="1:5" hidden="1" x14ac:dyDescent="0.3">
       <c r="A261" s="1" t="s">
         <v>63</v>
       </c>
@@ -22934,7 +25700,7 @@
         <v>35381450</v>
       </c>
     </row>
-    <row r="262" spans="1:5" x14ac:dyDescent="0.3">
+    <row r="262" spans="1:5" hidden="1" x14ac:dyDescent="0.3">
       <c r="A262" t="s">
         <v>0</v>
       </c>
@@ -22952,7 +25718,7 @@
         <v>83949</v>
       </c>
     </row>
-    <row r="263" spans="1:5" x14ac:dyDescent="0.3">
+    <row r="263" spans="1:5" hidden="1" x14ac:dyDescent="0.3">
       <c r="A263" t="s">
         <v>1</v>
       </c>
@@ -22970,7 +25736,7 @@
         <v>669932</v>
       </c>
     </row>
-    <row r="264" spans="1:5" x14ac:dyDescent="0.3">
+    <row r="264" spans="1:5" hidden="1" x14ac:dyDescent="0.3">
       <c r="A264" t="s">
         <v>2</v>
       </c>
@@ -22988,7 +25754,7 @@
         <v>398924</v>
       </c>
     </row>
-    <row r="265" spans="1:5" x14ac:dyDescent="0.3">
+    <row r="265" spans="1:5" hidden="1" x14ac:dyDescent="0.3">
       <c r="A265" t="s">
         <v>3</v>
       </c>
@@ -23006,7 +25772,7 @@
         <v>708061</v>
       </c>
     </row>
-    <row r="266" spans="1:5" x14ac:dyDescent="0.3">
+    <row r="266" spans="1:5" hidden="1" x14ac:dyDescent="0.3">
       <c r="A266" t="s">
         <v>4</v>
       </c>
@@ -23024,7 +25790,7 @@
         <v>4475827</v>
       </c>
     </row>
-    <row r="267" spans="1:5" x14ac:dyDescent="0.3">
+    <row r="267" spans="1:5" hidden="1" x14ac:dyDescent="0.3">
       <c r="A267" t="s">
         <v>5</v>
       </c>
@@ -23042,7 +25808,7 @@
         <v>525632</v>
       </c>
     </row>
-    <row r="268" spans="1:5" x14ac:dyDescent="0.3">
+    <row r="268" spans="1:5" hidden="1" x14ac:dyDescent="0.3">
       <c r="A268" t="s">
         <v>6</v>
       </c>
@@ -23060,7 +25826,7 @@
         <v>362348</v>
       </c>
     </row>
-    <row r="269" spans="1:5" x14ac:dyDescent="0.3">
+    <row r="269" spans="1:5" hidden="1" x14ac:dyDescent="0.3">
       <c r="A269" t="s">
         <v>7</v>
       </c>
@@ -23078,7 +25844,7 @@
         <v>92488</v>
       </c>
     </row>
-    <row r="270" spans="1:5" x14ac:dyDescent="0.3">
+    <row r="270" spans="1:5" hidden="1" x14ac:dyDescent="0.3">
       <c r="A270" t="s">
         <v>8</v>
       </c>
@@ -23096,7 +25862,7 @@
         <v>104153</v>
       </c>
     </row>
-    <row r="271" spans="1:5" x14ac:dyDescent="0.3">
+    <row r="271" spans="1:5" hidden="1" x14ac:dyDescent="0.3">
       <c r="A271" t="s">
         <v>9</v>
       </c>
@@ -23114,7 +25880,7 @@
         <v>2295570</v>
       </c>
     </row>
-    <row r="272" spans="1:5" x14ac:dyDescent="0.3">
+    <row r="272" spans="1:5" hidden="1" x14ac:dyDescent="0.3">
       <c r="A272" t="s">
         <v>10</v>
       </c>
@@ -23132,7 +25898,7 @@
         <v>1280972</v>
       </c>
     </row>
-    <row r="273" spans="1:5" x14ac:dyDescent="0.3">
+    <row r="273" spans="1:5" hidden="1" x14ac:dyDescent="0.3">
       <c r="A273" t="s">
         <v>11</v>
       </c>
@@ -23150,7 +25916,7 @@
         <v>155133</v>
       </c>
     </row>
-    <row r="274" spans="1:5" x14ac:dyDescent="0.3">
+    <row r="274" spans="1:5" hidden="1" x14ac:dyDescent="0.3">
       <c r="A274" t="s">
         <v>12</v>
       </c>
@@ -23168,7 +25934,7 @@
         <v>332377</v>
       </c>
     </row>
-    <row r="275" spans="1:5" x14ac:dyDescent="0.3">
+    <row r="275" spans="1:5" hidden="1" x14ac:dyDescent="0.3">
       <c r="A275" t="s">
         <v>13</v>
       </c>
@@ -23186,7 +25952,7 @@
         <v>150385</v>
       </c>
     </row>
-    <row r="276" spans="1:5" x14ac:dyDescent="0.3">
+    <row r="276" spans="1:5" hidden="1" x14ac:dyDescent="0.3">
       <c r="A276" t="s">
         <v>14</v>
       </c>
@@ -23204,7 +25970,7 @@
         <v>1328026</v>
       </c>
     </row>
-    <row r="277" spans="1:5" x14ac:dyDescent="0.3">
+    <row r="277" spans="1:5" hidden="1" x14ac:dyDescent="0.3">
       <c r="A277" t="s">
         <v>15</v>
       </c>
@@ -23222,7 +25988,7 @@
         <v>652866</v>
       </c>
     </row>
-    <row r="278" spans="1:5" x14ac:dyDescent="0.3">
+    <row r="278" spans="1:5" hidden="1" x14ac:dyDescent="0.3">
       <c r="A278" t="s">
         <v>16</v>
       </c>
@@ -23240,7 +26006,7 @@
         <v>274957</v>
       </c>
     </row>
-    <row r="279" spans="1:5" x14ac:dyDescent="0.3">
+    <row r="279" spans="1:5" hidden="1" x14ac:dyDescent="0.3">
       <c r="A279" t="s">
         <v>17</v>
       </c>
@@ -23258,7 +26024,7 @@
         <v>556007</v>
       </c>
     </row>
-    <row r="280" spans="1:5" x14ac:dyDescent="0.3">
+    <row r="280" spans="1:5" hidden="1" x14ac:dyDescent="0.3">
       <c r="A280" t="s">
         <v>18</v>
       </c>
@@ -23276,7 +26042,7 @@
         <v>638708</v>
       </c>
     </row>
-    <row r="281" spans="1:5" x14ac:dyDescent="0.3">
+    <row r="281" spans="1:5" hidden="1" x14ac:dyDescent="0.3">
       <c r="A281" t="s">
         <v>19</v>
       </c>
@@ -23294,7 +26060,7 @@
         <v>660760</v>
       </c>
     </row>
-    <row r="282" spans="1:5" x14ac:dyDescent="0.3">
+    <row r="282" spans="1:5" hidden="1" x14ac:dyDescent="0.3">
       <c r="A282" t="s">
         <v>20</v>
       </c>
@@ -23312,7 +26078,7 @@
         <v>660977</v>
       </c>
     </row>
-    <row r="283" spans="1:5" x14ac:dyDescent="0.3">
+    <row r="283" spans="1:5" hidden="1" x14ac:dyDescent="0.3">
       <c r="A283" t="s">
         <v>21</v>
       </c>
@@ -23330,7 +26096,7 @@
         <v>137374</v>
       </c>
     </row>
-    <row r="284" spans="1:5" x14ac:dyDescent="0.3">
+    <row r="284" spans="1:5" hidden="1" x14ac:dyDescent="0.3">
       <c r="A284" t="s">
         <v>22</v>
       </c>
@@ -23348,7 +26114,7 @@
         <v>869562</v>
       </c>
     </row>
-    <row r="285" spans="1:5" x14ac:dyDescent="0.3">
+    <row r="285" spans="1:5" hidden="1" x14ac:dyDescent="0.3">
       <c r="A285" t="s">
         <v>23</v>
       </c>
@@ -23366,7 +26132,7 @@
         <v>594187</v>
       </c>
     </row>
-    <row r="286" spans="1:5" x14ac:dyDescent="0.3">
+    <row r="286" spans="1:5" hidden="1" x14ac:dyDescent="0.3">
       <c r="A286" t="s">
         <v>24</v>
       </c>
@@ -23384,7 +26150,7 @@
         <v>564952</v>
       </c>
     </row>
-    <row r="287" spans="1:5" x14ac:dyDescent="0.3">
+    <row r="287" spans="1:5" hidden="1" x14ac:dyDescent="0.3">
       <c r="A287" t="s">
         <v>25</v>
       </c>
@@ -23402,7 +26168,7 @@
         <v>388775</v>
       </c>
     </row>
-    <row r="288" spans="1:5" x14ac:dyDescent="0.3">
+    <row r="288" spans="1:5" hidden="1" x14ac:dyDescent="0.3">
       <c r="A288" t="s">
         <v>26</v>
       </c>
@@ -23420,7 +26186,7 @@
         <v>88236</v>
       </c>
     </row>
-    <row r="289" spans="1:5" x14ac:dyDescent="0.3">
+    <row r="289" spans="1:5" hidden="1" x14ac:dyDescent="0.3">
       <c r="A289" t="s">
         <v>27</v>
       </c>
@@ -23438,7 +26204,7 @@
         <v>1367683</v>
       </c>
     </row>
-    <row r="290" spans="1:5" x14ac:dyDescent="0.3">
+    <row r="290" spans="1:5" hidden="1" x14ac:dyDescent="0.3">
       <c r="A290" t="s">
         <v>28</v>
       </c>
@@ -23456,7 +26222,7 @@
         <v>50400</v>
       </c>
     </row>
-    <row r="291" spans="1:5" x14ac:dyDescent="0.3">
+    <row r="291" spans="1:5" hidden="1" x14ac:dyDescent="0.3">
       <c r="A291" t="s">
         <v>29</v>
       </c>
@@ -23474,7 +26240,7 @@
         <v>170356</v>
       </c>
     </row>
-    <row r="292" spans="1:5" x14ac:dyDescent="0.3">
+    <row r="292" spans="1:5" hidden="1" x14ac:dyDescent="0.3">
       <c r="A292" t="s">
         <v>30</v>
       </c>
@@ -23492,7 +26258,7 @@
         <v>84348</v>
       </c>
     </row>
-    <row r="293" spans="1:5" x14ac:dyDescent="0.3">
+    <row r="293" spans="1:5" hidden="1" x14ac:dyDescent="0.3">
       <c r="A293" t="s">
         <v>31</v>
       </c>
@@ -23510,7 +26276,7 @@
         <v>808040</v>
       </c>
     </row>
-    <row r="294" spans="1:5" x14ac:dyDescent="0.3">
+    <row r="294" spans="1:5" hidden="1" x14ac:dyDescent="0.3">
       <c r="A294" t="s">
         <v>32</v>
       </c>
@@ -23528,7 +26294,7 @@
         <v>304626</v>
       </c>
     </row>
-    <row r="295" spans="1:5" x14ac:dyDescent="0.3">
+    <row r="295" spans="1:5" hidden="1" x14ac:dyDescent="0.3">
       <c r="A295" t="s">
         <v>33</v>
       </c>
@@ -23546,7 +26312,7 @@
         <v>310197</v>
       </c>
     </row>
-    <row r="296" spans="1:5" x14ac:dyDescent="0.3">
+    <row r="296" spans="1:5" hidden="1" x14ac:dyDescent="0.3">
       <c r="A296" t="s">
         <v>34</v>
       </c>
@@ -23564,7 +26330,7 @@
         <v>2419322</v>
       </c>
     </row>
-    <row r="297" spans="1:5" x14ac:dyDescent="0.3">
+    <row r="297" spans="1:5" hidden="1" x14ac:dyDescent="0.3">
       <c r="A297" t="s">
         <v>35</v>
       </c>
@@ -23582,7 +26348,7 @@
         <v>1116767</v>
       </c>
     </row>
-    <row r="298" spans="1:5" x14ac:dyDescent="0.3">
+    <row r="298" spans="1:5" hidden="1" x14ac:dyDescent="0.3">
       <c r="A298" t="s">
         <v>36</v>
       </c>
@@ -23600,7 +26366,7 @@
         <v>502400</v>
       </c>
     </row>
-    <row r="299" spans="1:5" x14ac:dyDescent="0.3">
+    <row r="299" spans="1:5" hidden="1" x14ac:dyDescent="0.3">
       <c r="A299" t="s">
         <v>37</v>
       </c>
@@ -23618,7 +26384,7 @@
         <v>466435</v>
       </c>
     </row>
-    <row r="300" spans="1:5" x14ac:dyDescent="0.3">
+    <row r="300" spans="1:5" hidden="1" x14ac:dyDescent="0.3">
       <c r="A300" t="s">
         <v>38</v>
       </c>
@@ -23636,7 +26402,7 @@
         <v>1395097</v>
       </c>
     </row>
-    <row r="301" spans="1:5" x14ac:dyDescent="0.3">
+    <row r="301" spans="1:5" hidden="1" x14ac:dyDescent="0.3">
       <c r="A301" t="s">
         <v>39</v>
       </c>
@@ -23654,7 +26420,7 @@
         <v>115519</v>
       </c>
     </row>
-    <row r="302" spans="1:5" x14ac:dyDescent="0.3">
+    <row r="302" spans="1:5" hidden="1" x14ac:dyDescent="0.3">
       <c r="A302" t="s">
         <v>40</v>
       </c>
@@ -23672,7 +26438,7 @@
         <v>594617</v>
       </c>
     </row>
-    <row r="303" spans="1:5" x14ac:dyDescent="0.3">
+    <row r="303" spans="1:5" hidden="1" x14ac:dyDescent="0.3">
       <c r="A303" t="s">
         <v>41</v>
       </c>
@@ -23690,7 +26456,7 @@
         <v>76023</v>
       </c>
     </row>
-    <row r="304" spans="1:5" x14ac:dyDescent="0.3">
+    <row r="304" spans="1:5" hidden="1" x14ac:dyDescent="0.3">
       <c r="A304" t="s">
         <v>42</v>
       </c>
@@ -23708,7 +26474,7 @@
         <v>821893</v>
       </c>
     </row>
-    <row r="305" spans="1:5" x14ac:dyDescent="0.3">
+    <row r="305" spans="1:5" hidden="1" x14ac:dyDescent="0.3">
       <c r="A305" t="s">
         <v>43</v>
       </c>
@@ -23726,7 +26492,7 @@
         <v>2985689</v>
       </c>
     </row>
-    <row r="306" spans="1:5" x14ac:dyDescent="0.3">
+    <row r="306" spans="1:5" hidden="1" x14ac:dyDescent="0.3">
       <c r="A306" t="s">
         <v>44</v>
       </c>
@@ -23744,7 +26510,7 @@
         <v>161287</v>
       </c>
     </row>
-    <row r="307" spans="1:5" x14ac:dyDescent="0.3">
+    <row r="307" spans="1:5" hidden="1" x14ac:dyDescent="0.3">
       <c r="A307" t="s">
         <v>45</v>
       </c>
@@ -23762,7 +26528,7 @@
         <v>784578</v>
       </c>
     </row>
-    <row r="308" spans="1:5" x14ac:dyDescent="0.3">
+    <row r="308" spans="1:5" hidden="1" x14ac:dyDescent="0.3">
       <c r="A308" t="s">
         <v>46</v>
       </c>
@@ -23780,7 +26546,7 @@
         <v>56159</v>
       </c>
     </row>
-    <row r="309" spans="1:5" x14ac:dyDescent="0.3">
+    <row r="309" spans="1:5" hidden="1" x14ac:dyDescent="0.3">
       <c r="A309" t="s">
         <v>47</v>
       </c>
@@ -23798,7 +26564,7 @@
         <v>813048</v>
       </c>
     </row>
-    <row r="310" spans="1:5" x14ac:dyDescent="0.3">
+    <row r="310" spans="1:5" hidden="1" x14ac:dyDescent="0.3">
       <c r="A310" t="s">
         <v>48</v>
       </c>
@@ -23816,7 +26582,7 @@
         <v>529923</v>
       </c>
     </row>
-    <row r="311" spans="1:5" x14ac:dyDescent="0.3">
+    <row r="311" spans="1:5" hidden="1" x14ac:dyDescent="0.3">
       <c r="A311" t="s">
         <v>49</v>
       </c>
@@ -23834,7 +26600,7 @@
         <v>192420</v>
       </c>
     </row>
-    <row r="312" spans="1:5" x14ac:dyDescent="0.3">
+    <row r="312" spans="1:5" hidden="1" x14ac:dyDescent="0.3">
       <c r="A312" t="s">
         <v>50</v>
       </c>
@@ -23852,7 +26618,7 @@
         <v>40472</v>
       </c>
     </row>
-    <row r="313" spans="1:5" x14ac:dyDescent="0.3">
+    <row r="313" spans="1:5" hidden="1" x14ac:dyDescent="0.3">
       <c r="A313" s="1" t="s">
         <v>63</v>
       </c>
@@ -23870,6 +26636,944 @@
       <c r="E313" s="1">
         <f>SUM(E262:E312)</f>
         <v>35218437</v>
+      </c>
+    </row>
+    <row r="314" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="A314" t="s">
+        <v>0</v>
+      </c>
+      <c r="B314" s="3">
+        <v>46174</v>
+      </c>
+      <c r="C314">
+        <v>12386</v>
+      </c>
+      <c r="D314">
+        <f>E314-C314</f>
+        <v>71137</v>
+      </c>
+      <c r="E314">
+        <v>83523</v>
+      </c>
+    </row>
+    <row r="315" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="A315" t="s">
+        <v>1</v>
+      </c>
+      <c r="B315" s="3">
+        <v>46174</v>
+      </c>
+      <c r="C315">
+        <v>198983</v>
+      </c>
+      <c r="D315">
+        <f t="shared" ref="D315:D365" si="6">E315-C315</f>
+        <v>469667</v>
+      </c>
+      <c r="E315">
+        <v>668650</v>
+      </c>
+    </row>
+    <row r="316" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="A316" t="s">
+        <v>2</v>
+      </c>
+      <c r="B316" s="3">
+        <v>46174</v>
+      </c>
+      <c r="C316">
+        <v>79062</v>
+      </c>
+      <c r="D316">
+        <f t="shared" si="6"/>
+        <v>319265</v>
+      </c>
+      <c r="E316">
+        <v>398327</v>
+      </c>
+    </row>
+    <row r="317" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="A317" t="s">
+        <v>3</v>
+      </c>
+      <c r="B317" s="3">
+        <v>46174</v>
+      </c>
+      <c r="C317">
+        <v>110993</v>
+      </c>
+      <c r="D317">
+        <f t="shared" si="6"/>
+        <v>593147</v>
+      </c>
+      <c r="E317">
+        <v>704140</v>
+      </c>
+    </row>
+    <row r="318" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="A318" t="s">
+        <v>4</v>
+      </c>
+      <c r="B318" s="3">
+        <v>46174</v>
+      </c>
+      <c r="C318">
+        <v>1262711</v>
+      </c>
+      <c r="D318">
+        <f t="shared" si="6"/>
+        <v>3181056</v>
+      </c>
+      <c r="E318">
+        <v>4443767</v>
+      </c>
+    </row>
+    <row r="319" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="A319" t="s">
+        <v>5</v>
+      </c>
+      <c r="B319" s="3">
+        <v>46174</v>
+      </c>
+      <c r="C319">
+        <v>136739</v>
+      </c>
+      <c r="D319">
+        <f t="shared" si="6"/>
+        <v>389379</v>
+      </c>
+      <c r="E319">
+        <v>526118</v>
+      </c>
+    </row>
+    <row r="320" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="A320" t="s">
+        <v>6</v>
+      </c>
+      <c r="B320" s="3">
+        <v>46174</v>
+      </c>
+      <c r="C320">
+        <v>25264</v>
+      </c>
+      <c r="D320">
+        <f t="shared" si="6"/>
+        <v>336367</v>
+      </c>
+      <c r="E320">
+        <v>361631</v>
+      </c>
+    </row>
+    <row r="321" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="A321" t="s">
+        <v>7</v>
+      </c>
+      <c r="B321" s="3">
+        <v>46174</v>
+      </c>
+      <c r="C321">
+        <v>15700</v>
+      </c>
+      <c r="D321">
+        <f t="shared" si="6"/>
+        <v>76651</v>
+      </c>
+      <c r="E321">
+        <v>92351</v>
+      </c>
+    </row>
+    <row r="322" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="A322" t="s">
+        <v>8</v>
+      </c>
+      <c r="B322" s="3">
+        <v>46174</v>
+      </c>
+      <c r="C322">
+        <v>13608</v>
+      </c>
+      <c r="D322">
+        <f t="shared" si="6"/>
+        <v>90300</v>
+      </c>
+      <c r="E322">
+        <v>103908</v>
+      </c>
+    </row>
+    <row r="323" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="A323" t="s">
+        <v>9</v>
+      </c>
+      <c r="B323" s="3">
+        <v>46174</v>
+      </c>
+      <c r="C323">
+        <v>168719</v>
+      </c>
+      <c r="D323">
+        <f t="shared" si="6"/>
+        <v>2115277</v>
+      </c>
+      <c r="E323">
+        <v>2283996</v>
+      </c>
+    </row>
+    <row r="324" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="A324" t="s">
+        <v>10</v>
+      </c>
+      <c r="B324" s="3">
+        <v>46174</v>
+      </c>
+      <c r="C324">
+        <v>173147</v>
+      </c>
+      <c r="D324">
+        <f t="shared" si="6"/>
+        <v>1099330</v>
+      </c>
+      <c r="E324">
+        <v>1272477</v>
+      </c>
+    </row>
+    <row r="325" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="A325" t="s">
+        <v>11</v>
+      </c>
+      <c r="B325" s="3">
+        <v>46174</v>
+      </c>
+      <c r="C325">
+        <v>26604</v>
+      </c>
+      <c r="D325">
+        <f t="shared" si="6"/>
+        <v>128908</v>
+      </c>
+      <c r="E325">
+        <v>155512</v>
+      </c>
+    </row>
+    <row r="326" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="A326" t="s">
+        <v>12</v>
+      </c>
+      <c r="B326" s="3">
+        <v>46174</v>
+      </c>
+      <c r="C326">
+        <v>82377</v>
+      </c>
+      <c r="D326">
+        <f t="shared" si="6"/>
+        <v>249616</v>
+      </c>
+      <c r="E326">
+        <v>331993</v>
+      </c>
+    </row>
+    <row r="327" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="A327" t="s">
+        <v>13</v>
+      </c>
+      <c r="B327" s="3">
+        <v>46174</v>
+      </c>
+      <c r="C327">
+        <v>19076</v>
+      </c>
+      <c r="D327">
+        <f t="shared" si="6"/>
+        <v>129437</v>
+      </c>
+      <c r="E327">
+        <v>148513</v>
+      </c>
+    </row>
+    <row r="328" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="A328" t="s">
+        <v>14</v>
+      </c>
+      <c r="B328" s="3">
+        <v>46174</v>
+      </c>
+      <c r="C328">
+        <v>366385</v>
+      </c>
+      <c r="D328">
+        <f t="shared" si="6"/>
+        <v>951645</v>
+      </c>
+      <c r="E328">
+        <v>1318030</v>
+      </c>
+    </row>
+    <row r="329" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="A329" t="s">
+        <v>15</v>
+      </c>
+      <c r="B329" s="3">
+        <v>46174</v>
+      </c>
+      <c r="C329">
+        <v>115864</v>
+      </c>
+      <c r="D329">
+        <f t="shared" si="6"/>
+        <v>527963</v>
+      </c>
+      <c r="E329">
+        <v>643827</v>
+      </c>
+    </row>
+    <row r="330" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="A330" t="s">
+        <v>16</v>
+      </c>
+      <c r="B330" s="3">
+        <v>46174</v>
+      </c>
+      <c r="C330">
+        <v>70846</v>
+      </c>
+      <c r="D330">
+        <f t="shared" si="6"/>
+        <v>203019</v>
+      </c>
+      <c r="E330">
+        <v>273865</v>
+      </c>
+    </row>
+    <row r="331" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="A331" t="s">
+        <v>17</v>
+      </c>
+      <c r="B331" s="3">
+        <v>46174</v>
+      </c>
+      <c r="C331">
+        <v>116675</v>
+      </c>
+      <c r="D331">
+        <f t="shared" si="6"/>
+        <v>433166</v>
+      </c>
+      <c r="E331">
+        <v>549841</v>
+      </c>
+    </row>
+    <row r="332" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="A332" t="s">
+        <v>18</v>
+      </c>
+      <c r="B332" s="3">
+        <v>46174</v>
+      </c>
+      <c r="C332">
+        <v>127551</v>
+      </c>
+      <c r="D332">
+        <f t="shared" si="6"/>
+        <v>505515</v>
+      </c>
+      <c r="E332">
+        <v>633066</v>
+      </c>
+    </row>
+    <row r="333" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="A333" t="s">
+        <v>19</v>
+      </c>
+      <c r="B333" s="3">
+        <v>46174</v>
+      </c>
+      <c r="C333">
+        <v>173179</v>
+      </c>
+      <c r="D333">
+        <f t="shared" si="6"/>
+        <v>483954</v>
+      </c>
+      <c r="E333">
+        <v>657133</v>
+      </c>
+    </row>
+    <row r="334" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="A334" t="s">
+        <v>20</v>
+      </c>
+      <c r="B334" s="3">
+        <v>46174</v>
+      </c>
+      <c r="C334">
+        <v>198016</v>
+      </c>
+      <c r="D334">
+        <f t="shared" si="6"/>
+        <v>466844</v>
+      </c>
+      <c r="E334">
+        <v>664860</v>
+      </c>
+    </row>
+    <row r="335" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="A335" t="s">
+        <v>21</v>
+      </c>
+      <c r="B335" s="3">
+        <v>46174</v>
+      </c>
+      <c r="C335">
+        <v>19642</v>
+      </c>
+      <c r="D335">
+        <f t="shared" si="6"/>
+        <v>117619</v>
+      </c>
+      <c r="E335">
+        <v>137261</v>
+      </c>
+    </row>
+    <row r="336" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="A336" t="s">
+        <v>22</v>
+      </c>
+      <c r="B336" s="3">
+        <v>46174</v>
+      </c>
+      <c r="C336">
+        <v>160963</v>
+      </c>
+      <c r="D336">
+        <f t="shared" si="6"/>
+        <v>703626</v>
+      </c>
+      <c r="E336">
+        <v>864589</v>
+      </c>
+    </row>
+    <row r="337" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="A337" t="s">
+        <v>23</v>
+      </c>
+      <c r="B337" s="3">
+        <v>46174</v>
+      </c>
+      <c r="C337">
+        <v>3799</v>
+      </c>
+      <c r="D337">
+        <f t="shared" si="6"/>
+        <v>589396</v>
+      </c>
+      <c r="E337">
+        <v>593195</v>
+      </c>
+    </row>
+    <row r="338" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="A338" t="s">
+        <v>24</v>
+      </c>
+      <c r="B338" s="3">
+        <v>46174</v>
+      </c>
+      <c r="C338">
+        <v>135031</v>
+      </c>
+      <c r="D338">
+        <f t="shared" si="6"/>
+        <v>430502</v>
+      </c>
+      <c r="E338">
+        <v>565533</v>
+      </c>
+    </row>
+    <row r="339" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="A339" t="s">
+        <v>25</v>
+      </c>
+      <c r="B339" s="3">
+        <v>46174</v>
+      </c>
+      <c r="C339">
+        <v>83465</v>
+      </c>
+      <c r="D339">
+        <f t="shared" si="6"/>
+        <v>305037</v>
+      </c>
+      <c r="E339">
+        <v>388502</v>
+      </c>
+    </row>
+    <row r="340" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="A340" t="s">
+        <v>26</v>
+      </c>
+      <c r="B340" s="3">
+        <v>46174</v>
+      </c>
+      <c r="C340">
+        <v>20729</v>
+      </c>
+      <c r="D340">
+        <f t="shared" si="6"/>
+        <v>68504</v>
+      </c>
+      <c r="E340">
+        <v>89233</v>
+      </c>
+    </row>
+    <row r="341" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="A341" t="s">
+        <v>27</v>
+      </c>
+      <c r="B341" s="3">
+        <v>46174</v>
+      </c>
+      <c r="C341">
+        <v>350234</v>
+      </c>
+      <c r="D341">
+        <f t="shared" si="6"/>
+        <v>1007867</v>
+      </c>
+      <c r="E341">
+        <v>1358101</v>
+      </c>
+    </row>
+    <row r="342" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="A342" t="s">
+        <v>28</v>
+      </c>
+      <c r="B342" s="3">
+        <v>46174</v>
+      </c>
+      <c r="C342">
+        <v>5405</v>
+      </c>
+      <c r="D342">
+        <f t="shared" si="6"/>
+        <v>45348</v>
+      </c>
+      <c r="E342">
+        <v>50753</v>
+      </c>
+    </row>
+    <row r="343" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="A343" t="s">
+        <v>29</v>
+      </c>
+      <c r="B343" s="3">
+        <v>46174</v>
+      </c>
+      <c r="C343">
+        <v>36971</v>
+      </c>
+      <c r="D343">
+        <f t="shared" si="6"/>
+        <v>132659</v>
+      </c>
+      <c r="E343">
+        <v>169630</v>
+      </c>
+    </row>
+    <row r="344" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="A344" t="s">
+        <v>30</v>
+      </c>
+      <c r="B344" s="3">
+        <v>46174</v>
+      </c>
+      <c r="C344">
+        <v>18667</v>
+      </c>
+      <c r="D344">
+        <f t="shared" si="6"/>
+        <v>65334</v>
+      </c>
+      <c r="E344">
+        <v>84001</v>
+      </c>
+    </row>
+    <row r="345" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="A345" t="s">
+        <v>31</v>
+      </c>
+      <c r="B345" s="3">
+        <v>46174</v>
+      </c>
+      <c r="C345">
+        <v>261947</v>
+      </c>
+      <c r="D345">
+        <f t="shared" si="6"/>
+        <v>537315</v>
+      </c>
+      <c r="E345">
+        <v>799262</v>
+      </c>
+    </row>
+    <row r="346" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="A346" t="s">
+        <v>32</v>
+      </c>
+      <c r="B346" s="3">
+        <v>46174</v>
+      </c>
+      <c r="C346">
+        <v>42333</v>
+      </c>
+      <c r="D346">
+        <f t="shared" si="6"/>
+        <v>261824</v>
+      </c>
+      <c r="E346">
+        <v>304157</v>
+      </c>
+    </row>
+    <row r="347" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="A347" t="s">
+        <v>33</v>
+      </c>
+      <c r="B347" s="3">
+        <v>46174</v>
+      </c>
+      <c r="C347">
+        <v>44476</v>
+      </c>
+      <c r="D347">
+        <f t="shared" si="6"/>
+        <v>264856</v>
+      </c>
+      <c r="E347">
+        <v>309332</v>
+      </c>
+    </row>
+    <row r="348" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="A348" t="s">
+        <v>34</v>
+      </c>
+      <c r="B348" s="3">
+        <v>46174</v>
+      </c>
+      <c r="C348">
+        <v>654759</v>
+      </c>
+      <c r="D348">
+        <f t="shared" si="6"/>
+        <v>1772747</v>
+      </c>
+      <c r="E348">
+        <v>2427506</v>
+      </c>
+    </row>
+    <row r="349" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="A349" t="s">
+        <v>35</v>
+      </c>
+      <c r="B349" s="3">
+        <v>46174</v>
+      </c>
+      <c r="C349">
+        <v>226186</v>
+      </c>
+      <c r="D349">
+        <f t="shared" si="6"/>
+        <v>877802</v>
+      </c>
+      <c r="E349">
+        <v>1103988</v>
+      </c>
+    </row>
+    <row r="350" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="A350" t="s">
+        <v>36</v>
+      </c>
+      <c r="B350" s="3">
+        <v>46174</v>
+      </c>
+      <c r="C350">
+        <v>86250</v>
+      </c>
+      <c r="D350">
+        <f t="shared" si="6"/>
+        <v>416270</v>
+      </c>
+      <c r="E350">
+        <v>502520</v>
+      </c>
+    </row>
+    <row r="351" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="A351" t="s">
+        <v>37</v>
+      </c>
+      <c r="B351" s="3">
+        <v>46174</v>
+      </c>
+      <c r="C351">
+        <v>179056</v>
+      </c>
+      <c r="D351">
+        <f t="shared" si="6"/>
+        <v>283876</v>
+      </c>
+      <c r="E351">
+        <v>462932</v>
+      </c>
+    </row>
+    <row r="352" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="A352" t="s">
+        <v>38</v>
+      </c>
+      <c r="B352" s="3">
+        <v>46174</v>
+      </c>
+      <c r="C352">
+        <v>273448</v>
+      </c>
+      <c r="D352">
+        <f t="shared" si="6"/>
+        <v>1114509</v>
+      </c>
+      <c r="E352">
+        <v>1387957</v>
+      </c>
+    </row>
+    <row r="353" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="A353" t="s">
+        <v>39</v>
+      </c>
+      <c r="B353" s="3">
+        <v>46174</v>
+      </c>
+      <c r="C353">
+        <v>33569</v>
+      </c>
+      <c r="D353">
+        <f t="shared" si="6"/>
+        <v>76731</v>
+      </c>
+      <c r="E353">
+        <v>110300</v>
+      </c>
+    </row>
+    <row r="354" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="A354" t="s">
+        <v>40</v>
+      </c>
+      <c r="B354" s="3">
+        <v>46174</v>
+      </c>
+      <c r="C354">
+        <v>111528</v>
+      </c>
+      <c r="D354">
+        <f t="shared" si="6"/>
+        <v>484120</v>
+      </c>
+      <c r="E354">
+        <v>595648</v>
+      </c>
+    </row>
+    <row r="355" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="A355" t="s">
+        <v>41</v>
+      </c>
+      <c r="B355" s="3">
+        <v>46174</v>
+      </c>
+      <c r="C355">
+        <v>14320</v>
+      </c>
+      <c r="D355">
+        <f t="shared" si="6"/>
+        <v>61418</v>
+      </c>
+      <c r="E355">
+        <v>75738</v>
+      </c>
+    </row>
+    <row r="356" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="A356" t="s">
+        <v>42</v>
+      </c>
+      <c r="B356" s="3">
+        <v>46174</v>
+      </c>
+      <c r="C356">
+        <v>184461</v>
+      </c>
+      <c r="D356">
+        <f t="shared" si="6"/>
+        <v>636330</v>
+      </c>
+      <c r="E356">
+        <v>820791</v>
+      </c>
+    </row>
+    <row r="357" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="A357" t="s">
+        <v>43</v>
+      </c>
+      <c r="B357" s="3">
+        <v>46174</v>
+      </c>
+      <c r="C357">
+        <v>326167</v>
+      </c>
+      <c r="D357">
+        <f t="shared" si="6"/>
+        <v>2633586</v>
+      </c>
+      <c r="E357">
+        <v>2959753</v>
+      </c>
+    </row>
+    <row r="358" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="A358" t="s">
+        <v>44</v>
+      </c>
+      <c r="B358" s="3">
+        <v>46174</v>
+      </c>
+      <c r="C358">
+        <v>33714</v>
+      </c>
+      <c r="D358">
+        <f t="shared" si="6"/>
+        <v>126184</v>
+      </c>
+      <c r="E358">
+        <v>159898</v>
+      </c>
+    </row>
+    <row r="359" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="A359" t="s">
+        <v>45</v>
+      </c>
+      <c r="B359" s="3">
+        <v>46174</v>
+      </c>
+      <c r="C359">
+        <v>186050</v>
+      </c>
+      <c r="D359">
+        <f t="shared" si="6"/>
+        <v>594259</v>
+      </c>
+      <c r="E359">
+        <v>780309</v>
+      </c>
+    </row>
+    <row r="360" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="A360" t="s">
+        <v>46</v>
+      </c>
+      <c r="B360" s="3">
+        <v>46174</v>
+      </c>
+      <c r="C360">
+        <v>5562</v>
+      </c>
+      <c r="D360">
+        <f t="shared" si="6"/>
+        <v>50668</v>
+      </c>
+      <c r="E360">
+        <v>56230</v>
+      </c>
+    </row>
+    <row r="361" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="A361" t="s">
+        <v>47</v>
+      </c>
+      <c r="B361" s="3">
+        <v>46174</v>
+      </c>
+      <c r="C361">
+        <v>62680</v>
+      </c>
+      <c r="D361">
+        <f t="shared" si="6"/>
+        <v>748404</v>
+      </c>
+      <c r="E361">
+        <v>811084</v>
+      </c>
+    </row>
+    <row r="362" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="A362" t="s">
+        <v>48</v>
+      </c>
+      <c r="B362" s="3">
+        <v>46174</v>
+      </c>
+      <c r="C362">
+        <v>96980</v>
+      </c>
+      <c r="D362">
+        <f t="shared" si="6"/>
+        <v>431162</v>
+      </c>
+      <c r="E362">
+        <v>528142</v>
+      </c>
+    </row>
+    <row r="363" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="A363" t="s">
+        <v>49</v>
+      </c>
+      <c r="B363" s="3">
+        <v>46174</v>
+      </c>
+      <c r="C363">
+        <v>39579</v>
+      </c>
+      <c r="D363">
+        <f t="shared" si="6"/>
+        <v>152152</v>
+      </c>
+      <c r="E363">
+        <v>191731</v>
+      </c>
+    </row>
+    <row r="364" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="A364" t="s">
+        <v>50</v>
+      </c>
+      <c r="B364" s="3">
+        <v>46174</v>
+      </c>
+      <c r="C364">
+        <v>6152</v>
+      </c>
+      <c r="D364">
+        <f t="shared" si="6"/>
+        <v>33878</v>
+      </c>
+      <c r="E364">
+        <v>40030</v>
+      </c>
+    </row>
+    <row r="365" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="A365" t="s">
+        <v>63</v>
+      </c>
+      <c r="B365" s="3">
+        <v>46174</v>
+      </c>
+      <c r="C365">
+        <f>SUM(C314:C364)</f>
+        <v>7198008</v>
+      </c>
+      <c r="D365">
+        <f t="shared" si="6"/>
+        <v>27845626</v>
+      </c>
+      <c r="E365">
+        <f>SUM(E314:E364)</f>
+        <v>35043634</v>
       </c>
     </row>
   </sheetData>
@@ -24850,7 +28554,7 @@
 
 <file path=xl/worksheets/sheet5.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{AF918180-16E9-4134-A7AF-5A3A237EE9A0}">
-  <dimension ref="A1:C41"/>
+  <dimension ref="A1:C46"/>
   <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
   <cols>
     <col min="1" max="1" width="18.6640625" bestFit="1" customWidth="1"/>
@@ -24910,7 +28614,7 @@
         <v>46023</v>
       </c>
       <c r="C5" s="2">
-        <v>37740</v>
+        <v>36176</v>
       </c>
     </row>
     <row r="6" spans="1:3" x14ac:dyDescent="0.3">
@@ -24922,7 +28626,7 @@
       </c>
       <c r="C6" s="2">
         <f>SUM(C2:C5)</f>
-        <v>1852758</v>
+        <v>1851194</v>
       </c>
     </row>
     <row r="7" spans="1:3" x14ac:dyDescent="0.3">
@@ -25021,7 +28725,7 @@
         <v>46082</v>
       </c>
       <c r="C15" s="2">
-        <v>41545</v>
+        <v>41078</v>
       </c>
     </row>
     <row r="16" spans="1:3" x14ac:dyDescent="0.3">
@@ -25076,7 +28780,7 @@
         <v>46113</v>
       </c>
       <c r="C20" s="2">
-        <v>44383</v>
+        <v>43865</v>
       </c>
     </row>
     <row r="21" spans="1:3" x14ac:dyDescent="0.3">
@@ -25128,7 +28832,7 @@
         <v>46143</v>
       </c>
       <c r="C25" s="2">
-        <v>45681</v>
+        <v>45108</v>
       </c>
     </row>
     <row r="26" spans="1:3" x14ac:dyDescent="0.3">
@@ -25177,7 +28881,7 @@
         <v>46174</v>
       </c>
       <c r="C30" s="2">
-        <v>46454</v>
+        <v>45804</v>
       </c>
     </row>
     <row r="31" spans="1:3" x14ac:dyDescent="0.3">
@@ -25226,7 +28930,7 @@
         <v>46204</v>
       </c>
       <c r="C35" s="2">
-        <v>45972</v>
+        <v>45140</v>
       </c>
     </row>
     <row r="36" spans="1:3" x14ac:dyDescent="0.3">
@@ -25274,6 +28978,9 @@
       <c r="B40" s="3">
         <v>46235</v>
       </c>
+      <c r="C40" s="2">
+        <v>43953</v>
+      </c>
     </row>
     <row r="41" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A41" t="s">
@@ -25281,6 +28988,52 @@
       </c>
       <c r="B41" s="3">
         <v>46235</v>
+      </c>
+    </row>
+    <row r="42" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A42" t="s">
+        <v>7</v>
+      </c>
+      <c r="B42" s="3">
+        <v>46266</v>
+      </c>
+    </row>
+    <row r="43" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A43" t="s">
+        <v>23</v>
+      </c>
+      <c r="B43" s="3">
+        <v>46266</v>
+      </c>
+      <c r="C43" s="2">
+        <v>85353</v>
+      </c>
+    </row>
+    <row r="44" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A44" t="s">
+        <v>34</v>
+      </c>
+      <c r="B44" s="3">
+        <v>46266</v>
+      </c>
+      <c r="C44" s="2">
+        <v>1371273</v>
+      </c>
+    </row>
+    <row r="45" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A45" t="s">
+        <v>37</v>
+      </c>
+      <c r="B45" s="3">
+        <v>46266</v>
+      </c>
+    </row>
+    <row r="46" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A46" t="s">
+        <v>63</v>
+      </c>
+      <c r="B46" s="3">
+        <v>46266</v>
       </c>
     </row>
   </sheetData>
